--- a/outputs/Catheter_Ablation_Papers_2026-10-03.xlsx
+++ b/outputs/Catheter_Ablation_Papers_2026-10-03.xlsx
@@ -128,14 +128,14 @@
     <t>2026-Sep-24</t>
   </si>
   <si>
-    <t xml:space="preserve">中等度の脳卒中リスクを伴う心心心房細動に対する抗凝固療法
+    <t xml:space="preserve">中等度の脳卒中リスクを伴う心房細動に対する抗凝固療法
 (Anticoagulation for Atrial Fibrillation with Intermediate Stroke Risk.)</t>
   </si>
   <si>
     <t xml:space="preserve">【概要】現在の米国および欧州のガイドラインでは、クラス IIa の適応症として経口抗凝固療法を推奨している (無作為化比較試験 (RCT) / N = 1,803例)
-【方法】われわれは、心心心房細動を有し、脳卒中リスクが中程度（CHADS-VAScスケールで男性のスコアが1、女性のスコアが2、範囲は0〜9、スコアが高いほど脳卒中リスクが高いことを…
+【方法】われわれは、心房細動を有し、脳卒中リスクが中程度（CHADS-VAScスケールで男性のスコアが1、女性のスコアが2、範囲は0〜9、スコアが高いほど脳卒中リスクが高いことを…
 【結果】ランダム化を受けた1,803人の患者のうち、902人はDOAC療法を受けるように割り当てられ、901人は抗凝固療法を受けないように割り当てられた。
-【結論】脳卒中リスクが中程度の心心心房細動患者において、DOAC療法は抗凝固療法を行わなかった場合に比べ、24カ月時点で脳卒中、全身性塞栓症、大出血、心血管疾患による死亡のリスクが低かった</t>
+【結論】脳卒中リスクが中程度の心房細動患者において、DOAC療法は抗凝固療法を行わなかった場合に比べ、24カ月時点で脳卒中、全身性塞栓症、大出血、心血管疾患による死亡のリスクが低かった</t>
   </si>
   <si>
     <t xml:space="preserve">N Engl J Med
@@ -155,14 +155,14 @@
     <t>2026-Sep-22</t>
   </si>
   <si>
-    <t xml:space="preserve">心心心房細動アブレーションにおける超音波ガイド下と従来の静脈穿刺の比較: ULYSSES 試験
+    <t xml:space="preserve">心房細動アブレーションにおける超音波ガイド下と従来の静脈穿刺の比較: ULYSSES 試験
 (Ultrasound-guided vs conventional venous puncture for atrial fibrillation ablation: the ULYSSES trial.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】および目的: 血管アクセス部位の合併症は、心心心房細動カテーテルアブレーションの最も一般的な処置関連の有害事象である。 (無作為化比較試験 (RCT) / N = 986例)
-【方法】この研究者主導の多施設非盲検優位性試験では、心心心房細動または左心房頻脈カテーテルアブレーションを受けている患者が、超音波ガイド下の静脈穿刺戦略（介入群）または触診による従来…
+    <t xml:space="preserve">【概要】および目的: 血管アクセス部位の合併症は、心房細動カテーテルアブレーションの最も一般的な処置関連の有害事象である。 (無作為化比較試験 (RCT) / N = 986例)
+【方法】この研究者主導の多施設非盲検優位性試験では、心房細動または左心房頻脈カテーテルアブレーションを受けている患者が、超音波ガイド下の静脈穿刺戦略（介入群）または触診による従来…
 【結果】6 つのセンターで、986 人の患者がランダム化された。
-【結論】心心心房細動アブレーション処置のための超音波ガイド下の静脈アクセスにより、血管アクセス部位の合併症が大幅に減少しました</t>
+【結論】心房細動アブレーション処置のための超音波ガイド下の静脈アクセスにより、血管アクセス部位の合併症が大幅に減少しました</t>
   </si>
   <si>
     <t xml:space="preserve">Eur Heart J
@@ -179,7 +179,7 @@
     <t>https://pubmed.ncbi.nlm.nih.gov/41979041/</t>
   </si>
   <si>
-    <t xml:space="preserve">心心心房細動における房室結節アブレーションを伴うまたは伴わない心臓再同期療法: CAAN-AF 試験
+    <t xml:space="preserve">心房細動における房室結節アブレーションを伴うまたは伴わない心臓再同期療法: CAAN-AF 試験
 (Cardiac resynchronization therapy with or without atrioventricular node ablation in atrial fibrillation: the CAAN-AF trial.)</t>
   </si>
   <si>
@@ -260,7 +260,7 @@
     <t>2026-Oct-04</t>
   </si>
   <si>
-    <t xml:space="preserve">心心心房細動患者における不安とうつ病の影響: 2 つの国際的な前向き登録からの洞察
+    <t xml:space="preserve">心房細動患者における不安とうつ病の影響: 2 つの国際的な前向き登録からの洞察
 (Impact of anxiety and depression in patients with atrial fibrillation: Insights from 2 international prospective registries.)</t>
   </si>
   <si>
@@ -287,11 +287,11 @@
     <t>2026-Oct-01</t>
   </si>
   <si>
-    <t xml:space="preserve">心心心房細動に対する胸腔鏡下アブレーション後の早期再発と後期再発の臨床的、組織学的、分子的関連性
+    <t xml:space="preserve">心房細動に対する胸腔鏡下アブレーション後の早期再発と後期再発の臨床的、組織学的、分子的関連性
 (Clinical, histologic, and molecular associations of early and late recurrence after thoracoscopic ablation for atrial fibrillation.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】心心心房細動 (AF) の早期再発 (ER) は、アブレーション後によく見られる。 (前向き研究 (Prospective) / N = 449例)
+    <t xml:space="preserve">【概要】心房細動 (AF) の早期再発 (ER) は、アブレーション後によく見られる。 (前向き研究 (Prospective) / N = 449例)
 【方法】我々は、左心耳切除を伴う進行性AFの胸腔鏡下アブレーションを受ける患者449人（62±9歳、女性26.7％）を前向きに登録した。
 【結果】ER は 449 人の患者中 176 人 (39.2%) で発生し、そのうち 152 人 (86.4%) が 30 日以内に最初の ER エピソードを経験しました。
 【結論】胸腔鏡下AFアブレーション後、ERはLRのリスク増加と関連していた</t>
@@ -345,9 +345,9 @@
 (Crista Caval Line: Lattice-Tip Pulsed Field Ablation for Right Atrial Substrate Modification.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】はじめに: 肺静脈隔離は依然として心心心房細動 (AF) アブレーションの中心ですが、右心房基質の修正は不完全に定義されたままである (前向き研究 (Prospective) / N = 27例)
+    <t xml:space="preserve">【概要】はじめに: 肺静脈隔離は依然として心房細動 (AF) アブレーションの中心ですが、右心房基質の修正は不完全に定義されたままである (前向き研究 (Prospective) / N = 27例)
 【方法】そして
-【結果】我々は、反復性心心心房細動アブレーションまたは非発作性心心心房細動に対するアブレーション中にCCL作成を受ける連続36人の患者を前向きに登録した。
+【結果】我々は、反復性心房細動アブレーションまたは非発作性心房細動に対するアブレーション中にCCL作成を受ける連続36人の患者を前向きに登録した。
 【結論】CT ガイド下、SN 温存 CCL は格子先端 PFA を用いて再現性よく作成でき、臨床的に明らかな横隔神経麻痺を伴わずに初回通過の双方向横伝導ブロックを生成しる</t>
   </si>
   <si>
@@ -368,12 +368,12 @@
     <t>2026-Sep-29</t>
   </si>
   <si>
-    <t xml:space="preserve">心心心房細動に対する高周波アブレーションと比較したパルス場による脳卒中およびTIAのリスク
+    <t xml:space="preserve">心房細動に対する高周波アブレーションと比較したパルス場による脳卒中およびTIAのリスク
 (Risk of Stroke and TIA With Pulsed Field Compared With Radiofrequency Ablation for Atrial Fibrillation.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】心心心房細動のパルスフィールドアブレーション（PFA）は、熱アブレーションと比較した安全性への期待もあり、急速に採用されてきました。 (前向き研究 (Prospective) / 症例数: 不明)
-【方法】私たちは、2022年から2026年にかけて、米国の大規模学術センターで連続した心心心房細動アブレーションを分析する前向きレジストリを実施しました。
+    <t xml:space="preserve">【概要】心房細動のパルスフィールドアブレーション（PFA）は、熱アブレーションと比較した安全性への期待もあり、急速に採用されてきました。 (前向き研究 (Prospective) / 症例数: 不明)
+【方法】私たちは、2022年から2026年にかけて、米国の大規模学術センターで連続した心房細動アブレーションを分析する前向きレジストリを実施しました。
 【結果】合計 4,221 件のアブレーション処置 (RFA 2,077 件、PFA 2,144 件: Farawave 68.7%、Sphere 9 23.3%、Varipulse 6.9%、PulseSelect 0.7%) …
 【結論】臨床粒度が高く、患者を体系的に追跡調査する大量の単一センター登録では、PFA は RFA と比較して 30 日時点で脳卒中/TIA のリスクが著しく高いと関連していました</t>
   </si>
@@ -415,7 +415,7 @@
     <t>https://pubmed.ncbi.nlm.nih.gov/42732578/</t>
   </si>
   <si>
-    <t xml:space="preserve">パルスフィールドアブレーションは心心心房細動アブレーション後の良好な転帰と関連している: ポーランド国立アブレーション登録簿 (POL-AR) からの洞察
+    <t xml:space="preserve">パルスフィールドアブレーションは心房細動アブレーション後の良好な転帰と関連している: ポーランド国立アブレーション登録簿 (POL-AR) からの洞察
 (Pulsed Field Ablation Is Associated With Favorable Outcomes After Atrial Fibrillation Ablation: Insights From the Polish National Ablation Registry (POL-AR).)</t>
   </si>
   <si>
@@ -438,11 +438,11 @@
     <t>2026-Oct-25</t>
   </si>
   <si>
-    <t xml:space="preserve">心心心房細動で肺静脈隔離を受けた高齢患者の臨床的脆弱性がリズム関連の転帰を改善する:観察コホート研究
+    <t xml:space="preserve">心房細動で肺静脈隔離を受けた高齢患者の臨床的脆弱性がリズム関連の転帰を改善する:観察コホート研究
 (Clinical Vulnerability Refines Rhythm-Related Outcomes in Older Patients Undergoing Pulmonary Vein Isolation for Atrial Fibrillation: An Observational Cohort Study.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】はじめに: 心心心房細動 (AF) アブレーションの患者を選択する際には、暦年齢が考慮されることがよくありますが、年齢だけでは、どの高齢患者が肺静脈隔離 (PVI) 後に再発… (観察研究・その他 / N = 2,559例)
+    <t xml:space="preserve">【概要】はじめに: 心房細動 (AF) アブレーションの患者を選択する際には、暦年齢が考慮されることがよくありますが、年齢だけでは、どの高齢患者が肺静脈隔離 (PVI) 後に再発… (観察研究・その他 / N = 2,559例)
 【方法】私たちは、PVI を受けている連続患者を対象とした単一施設の観察研究を実施しました。
 【結果】登録コホートには、2,559 人の患者と 580 件の同一施設リズム介入イベントが含まれていました。
 【結論】年齢が 75 歳以上では、PVI 後の同センター再発関連リズム介入の割合が高かったが、リスクは大きく異なりました</t>
@@ -512,7 +512,7 @@
     <t>2026-Oct-21</t>
   </si>
   <si>
-    <t xml:space="preserve">心心心房細動アブレーション後の不整脈再発のマーカーとしてのヘモグロビンレベル
+    <t xml:space="preserve">心房細動アブレーション後の不整脈再発のマーカーとしてのヘモグロビンレベル
 (Hemoglobin Levels as a Marker of Arrhythmia Recurrence After Atrial Fibrillation Ablation.)</t>
   </si>
   <si>
@@ -536,11 +536,11 @@
     <t>https://pubmed.ncbi.nlm.nih.gov/42774855/</t>
   </si>
   <si>
-    <t xml:space="preserve">心心心房細動に対するパルスフィールドアブレーション中の 3 つの異なる鎮静戦略を使用した安全性と結果の比較
+    <t xml:space="preserve">心房細動に対するパルスフィールドアブレーション中の 3 つの異なる鎮静戦略を使用した安全性と結果の比較
 (A Comparison of Safety and Outcome Using Three Different Sedation Strategies During Pulsed Field Ablation for Atrial Fibrillation.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】パルスフィールドアブレーション (PFA) は、心心心房細動 (AF) アブレーションの新しいモダリティである。ただし、十分な鎮静を行うことで、 (観察研究・その他 / N = 1,269例)
+    <t xml:space="preserve">【概要】パルスフィールドアブレーション (PFA) は、心房細動 (AF) アブレーションの新しいモダリティである。ただし、十分な鎮静を行うことで、 (観察研究・その他 / N = 1,269例)
 【方法】2021年から2024年までにペンタスプリンPFA技術による初めてのAFアブレーションを受けたデンマーク人患者全員が含まれた。
 【結果】1,269人の患者のうち、661人（52％）がEP-DSを受け、173人（14％）がAN-DSを受け、435人（34％）がGAを受けた。
 【結論】この全国コホートでは、EP スタッフによる深い鎮静は実行可能であり、PFA 中に臨床的に重大な鎮静関連の有害事象はほとんど発生しなかった</t>
@@ -609,12 +609,12 @@
     <t>2026-Sep-12</t>
   </si>
   <si>
-    <t xml:space="preserve">心心心房細動に対する高周波アブレーション中の食道保護冷却後の胸痛と胃食道逆流症の参加者報告 - EVERCOOL-AF 研究
+    <t xml:space="preserve">心房細動に対する高周波アブレーション中の食道保護冷却後の胸痛と胃食道逆流症の参加者報告 - EVERCOOL-AF 研究
 (Participant-reported chest pain and gastric esophageal reflux disease following protective esophageal cooling during radiofrequency ablation for atrial fibrillation - the EVERCOOL-AF study.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】胃食道逆流症（GERD）と胸痛は、心心心房細動（AF）に対するカテーテルアブレーション後の一般的な合併症であり、食道の熱傷害が原因であることが多いである。 (観察研究・その他 / N = 312例)
-【方法】発作性心心心房細動または持続性心心心房細動に対して食道冷却を伴う RFA を受けている参加者は、標準化されたアンケートに回答しました。
+    <t xml:space="preserve">【概要】胃食道逆流症（GERD）と胸痛は、心房細動（AF）に対するカテーテルアブレーション後の一般的な合併症であり、食道の熱傷害が原因であることが多いである。 (観察研究・その他 / N = 312例)
+【方法】発作性心房細動または持続性心房細動に対して食道冷却を伴う RFA を受けている参加者は、標準化されたアンケートに回答しました。
 【結果】食道冷却を受けたアブレーション後のアンケートに回答した最大参加者 312 名のうち 295 名が GERD ≧ 8 の基準を満たし、71 名 (24.1%) が CP を報告しました。
 【結論】積極的な食道冷却を伴うAFアブレーションを受けた参加者では、年齢が若く、駆出率が高く、両側初回通過隔離の欠如がアブレーション後のCPと関連していた</t>
   </si>
@@ -656,14 +656,14 @@
     <t>2026-Sep-25</t>
   </si>
   <si>
-    <t xml:space="preserve">心心心房細動を伴う高出血リスク患者における経皮的左心耳閉塞後の左心房アブレーションの安全性と有効性: PROCEED-AF アブレーション レジストリからの多施設解析
+    <t xml:space="preserve">心房細動を伴う高出血リスク患者における経皮的左心耳閉塞後の左心房アブレーションの安全性と有効性: PROCEED-AF アブレーション レジストリからの多施設解析
 (Safety and Efficacy of Left Atrial Ablation After Percutaneous Left Atrial Appendage Occlusion in High-Bleeding-Risk Patients with Atrial Fibrillation: A Multicenter Analysis from the PROCEED-AF Ablation Registry.)</t>
   </si>
   <si>
     <t xml:space="preserve">【概要】そして目的: (観察研究・その他 / N = 198例)
 【方法】私たちは、以前に LAAO デバイスを使用して AF アブレーションを受けた患者に関するデータを世界中の 14 のセンターからを解析した。
 【結果】過去にLAAOを患った合計198人の患者（年齢70歳、女性37％、発作性AF42％）が含まれた。
-【結論】既存の LAAO デバイスを使用して心心心房細動に対するカテーテルアブレーションを受けている患者の大規模な国際登録では、アブレーションは実行可能であり、デバイス関連の合併症はまれであっ…</t>
+【結論】既存の LAAO デバイスを使用して心房細動に対するカテーテルアブレーションを受けている患者の大規模な国際登録では、アブレーションは実行可能であり、デバイス関連の合併症はまれであっ…</t>
   </si>
   <si>
     <t xml:space="preserve">Europace
@@ -680,12 +680,12 @@
     <t>https://pubmed.ncbi.nlm.nih.gov/42786895/</t>
   </si>
   <si>
-    <t xml:space="preserve">非肺静脈ドライバーに基づく持続性心心心房細動におけるアブレーション結果の仮想心臓ベースの予測
+    <t xml:space="preserve">非肺静脈ドライバーに基づく持続性心房細動におけるアブレーション結果の仮想心臓ベースの予測
 (Virtual Heart-Based Prediction of Ablation Outcomes in Persistent Atrial Fibrillation Based on Non-Pulmonary Vein Drivers.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】持続性心心心房細動 (AF) におけるドライバーを対象としたアブレーションの臨床転帰には一貫性がなく、AF ドライバーのダイナミクスを特徴付け、アブレーション戦略を導くための… (観察研究・その他 / N = 165例)
-【方法】われわれは、CUVIA-AF2 研究（心心心房細動の仮想アブレーションガイド付きカテーテルアブレーションの臨床的有用性 2）から得られた持続性 AF 患者 165 人を対象に…
+    <t xml:space="preserve">【概要】持続性心房細動 (AF) におけるドライバーを対象としたアブレーションの臨床転帰には一貫性がなく、AF ドライバーのダイナミクスを特徴付け、アブレーション戦略を導くための… (観察研究・その他 / N = 165例)
+【方法】われわれは、CUVIA-AF2 研究（心房細動の仮想アブレーションガイド付きカテーテルアブレーションの臨床的有用性 2）から得られた持続性 AF 患者 165 人を対象に…
 【結果】肺静脈外領域での安定した PS は 124 人 (75%) の患者で認めた。
 【結論】仮想心臓モデルで特定された安定した DF を伴う安定した PS は、有害なモデル由来の局所基質特徴とアブレーション後のより高い再発率に関連していました</t>
   </si>
@@ -707,11 +707,11 @@
     <t>2026-Sep-10</t>
   </si>
   <si>
-    <t xml:space="preserve">持続性心心心房細動におけるマーシャルエタノール注入の静脈: VOMALC-PeAF レジストリからの洞察
+    <t xml:space="preserve">持続性心房細動におけるマーシャルエタノール注入の静脈: VOMALC-PeAF レジストリからの洞察
 (Vein of Marshall ethanol infusion in persistent atrial fibrillation: Insight from VOMALC-PeAF registry.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】肺静脈隔離（PVI）アブレーションは、持続性心心心房細動（PeAF）に対する効果が限られている。 (観察研究・その他 / N = 151例)
+    <t xml:space="preserve">【概要】肺静脈隔離（PVI）アブレーションは、持続性心房細動（PeAF）に対する効果が限られている。 (観察研究・その他 / N = 151例)
 【方法】この後ろ向き多施設観察コホート研究には、VOM-EI + AS または PVI のみを受けた連続した PeAF 患者が含まれていました。
 【結果】2:1 の傾向スコアのマッチングの後、VOM-EI + AS で治療された 151 人の患者と PVI のみで治療された 75 人の患者が比較された。
 【結論】実際の PeAF 集団では、VOM-EI、PVI、および解剖学的線状病変を組み込んだ最初のアブレーション戦略は、長期追跡調査における不整脈再発の予防において、PVI 単独よりも大幅…</t>
@@ -730,11 +730,11 @@
     <t>2026-Sep-18</t>
   </si>
   <si>
-    <t xml:space="preserve">再発性心房性不整脈の特徴と心心心房細動のパルスフィールドアブレーション後の病変評価
+    <t xml:space="preserve">再発性心房性不整脈の特徴と心房細動のパルスフィールドアブレーション後の病変評価
 (Characteristics of Recurrent Atrial Arrhythmias and Lesion Assessment Late After Pulsed Field Ablation of Atrial Fibrillation.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】パルスフィールドアブレーション (PFA) は、心心心房細動 (AF) のアブレーション用の新規かつ急速に普及しているエネルギーである。 (観察研究・その他 / N = 145例)
+    <t xml:space="preserve">【概要】パルスフィールドアブレーション (PFA) は、心房細動 (AF) のアブレーション用の新規かつ急速に普及しているエネルギーである。 (観察研究・その他 / N = 145例)
 【方法】フランス PFA 全国の網羅的な多中心レジストリのこのサブ研究では、最初の AF アブレーション処置中に提供された PFA アプリケーションに関する詳細なデータを解析した…
 【結果】再発性不整脈は 58% が AF、28% が心房頻脈、8% が典型的な心房粗動であった。
 【結論】ペンタスプリン PFA カテーテルを使用した最初の AF アブレーション後にやり直し処置を受けた患者では、アブレーション病変が PV を越えてを行いた場合、AF が観察される頻度は…</t>
@@ -898,7 +898,7 @@
     <t>2026-Sep-17</t>
   </si>
   <si>
-    <t xml:space="preserve">RESET-AF（心心心房細動に対するRapid onE-Shotエレクトロポレーショントライアル）による人類初の体験
+    <t xml:space="preserve">RESET-AF（心房細動に対するRapid onE-Shotエレクトロポレーショントライアル）による人類初の体験
 (First-in-human experience from RESET-AF (Rapid onE-Shot Electroporation Trial for Atrial Fibrillation).)</t>
   </si>
   <si>
@@ -965,12 +965,12 @@
     <t>https://pubmed.ncbi.nlm.nih.gov/42820876/</t>
   </si>
   <si>
-    <t xml:space="preserve">心心心房細動における神経叢機能に対するパルスフィールドアブレーションの影響
+    <t xml:space="preserve">心房細動における神経叢機能に対するパルスフィールドアブレーションの影響
 (Impact of pulsed field ablation on ganglionated plexi function in atrial fibrillation.)</t>
   </si>
   <si>
     <t xml:space="preserve">【概要】熱エネルギーを使用する肺静脈隔離 (PVI) は、左心房 (LA) 神経節叢 (GP) への付随損傷を介して抗不整脈効果の一部を発揮する可能性がありる。 (観察研究・その他 / N = 10例)
-【方法】この前向きコホート研究では、初めて PFA を受けた持続性心心心房細動患者が連続して登録された。
+【方法】この前向きコホート研究では、初めて PFA を受けた持続性心房細動患者が連続して登録された。
 【結果】10人の患者(年齢61.9±7.1歳、女性3人[30%])が登録された。
 【結論】心内膜ＰＦＡは、重複部位への病変送達にもかかわらず、一貫してＬＡ ＧＰ機能を消失させるわけではない</t>
   </si>
@@ -1114,11 +1114,11 @@
     <t>2026-Oct-28</t>
   </si>
   <si>
-    <t xml:space="preserve">両右肺静脈の右心房ドレナージを伴う部分異常肺静脈還流における心心心房細動に対するパルスフィールドアブレーション
+    <t xml:space="preserve">両右肺静脈の右心房ドレナージを伴う部分異常肺静脈還流における心房細動に対するパルスフィールドアブレーション
 (Pulsed-Field Ablation for Atrial Fibrillation in Partial Anomalous Pulmonary Venous Return With Right Atrial Drainage of Both Right Pulmonary Veins.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】パルスフィールドアブレーションは、心心心房細動と部分的な肺静脈還流異常のある患者に対して安全に実施した (観察研究・その他 / 症例数: 不明)
+    <t xml:space="preserve">【概要】パルスフィールドアブレーションは、心房細動と部分的な肺静脈還流異常のある患者に対して安全に実施した (観察研究・その他 / 症例数: 不明)
 【方法】電気解剖学的マッピングにより洞結節領域が定義され、異常な右肺静脈切除部位から十分な距離があることが確認され、分離が成功しました
 【結果】電気解剖学的マッピングにより洞結節領域が定義され、異常な右肺静脈切除部位から十分な距離があることが確認され、分離が成功しました
 【結論】電気解剖学的マッピングにより洞結節領域が定義され、異常な右肺静脈切除部位から十分な距離があることが確認され、分離が成功しました</t>
@@ -1134,13 +1134,13 @@
     <t>https://pubmed.ncbi.nlm.nih.gov/42812536/</t>
   </si>
   <si>
-    <t xml:space="preserve">心心心房細動アブレーションの有効性エンドポイント、安全性エンドポイント、および試験デザイン: 心拍リズム協会によって承認された学術研究コンソーシアム イニシアチブ
+    <t xml:space="preserve">心房細動アブレーションの有効性エンドポイント、安全性エンドポイント、および試験デザイン: 心拍リズム協会によって承認された学術研究コンソーシアム イニシアチブ
 (Atrial Fibrillation Ablation Effectiveness End Points, Safety End Points, and Trial Design: Academic Research Consortium Initiative Endorsed by the Heart Rhythm Society.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】AFA-ARC (心心心房細動アブレーション学術研究コンソーシアム) イニシアティブの目的は、症候性心心心房細動の治療のためのカテーテルアブレーションを評価する極めて重要な臨床試… (観察研究・その他 / 症例数: 不明)
+    <t xml:space="preserve">【概要】AFA-ARC (心房細動アブレーション学術研究コンソーシアム) イニシアティブの目的は、症候性心房細動の治療のためのカテーテルアブレーションを評価する極めて重要な臨床試… (観察研究・その他 / 症例数: 不明)
 【方法】2024年7月から、国際専門家グループは作業グループ（グループ1の有効性エンドポイント、グループ2の安全性エンドポイント、グループ3の試験設計と報告書）で仮想的に一緒に、…
-【結果】このプロセスの主要な部分は、心心心房細動のカテーテルアブレーションを評価する極めて重要な臨床試験の試験デザインと安全性と有効性のエンドポイントを再検討するための統合文書の作成であった。
+【結果】このプロセスの主要な部分は、心房細動のカテーテルアブレーションを評価する極めて重要な臨床試験の試験デザインと安全性と有効性のエンドポイントを再検討するための統合文書の作成であった。
 【結論】このAFA-ARC文書は、症候性発作性AF、持続性AF、または長期持続性AF患者におけるAFアブレーションを評価する研究の有効性と安全性のエンドポイント、研究デザイン、報告書の改訂…</t>
   </si>
   <si>
@@ -1154,13 +1154,13 @@
     <t>https://pubmed.ncbi.nlm.nih.gov/42808156/</t>
   </si>
   <si>
-    <t xml:space="preserve">心心心房細動に対する単極パルスフィールドアブレーション後のアブレーション部位を越えた左心房電圧の減衰
+    <t xml:space="preserve">心房細動に対する単極パルスフィールドアブレーション後のアブレーション部位を越えた左心房電圧の減衰
 (Left Atrial Voltage Attenuation Beyond Ablation Sites After Unipolar Pulsed-Field Ablation for Atrial Fibrillation.)</t>
   </si>
   <si>
     <t xml:space="preserve">【概要】はじめに: ほとんどのパルスフィールドアブレーション (PFA) システムとは異なり、Affera (Medtronic) は格子先端カテーテルと皮膚リターンパッチの間に… (観察研究・その他 / 症例数: 不明)
 【方法】そして
-【結果】私たちは、Affera システムを使用して原発性心心心房細動アブレーションを受けた連続 5 人の患者を遡及的に研究しました。
+【結果】私たちは、Affera システムを使用して原発性心房細動アブレーションを受けた連続 5 人の患者を遡及的に研究しました。
 【結論】アフェラベースの単極アブレーションでは、急性双極電圧減衰が発生し、病変セットに隣接する非アブレーション心筋層まで広がりましたが、距離とともに減少し、大部分は適用部位の約 30 mm…</t>
   </si>
   <si>
@@ -1170,11 +1170,11 @@
     <t>https://pubmed.ncbi.nlm.nih.gov/42801593/</t>
   </si>
   <si>
-    <t xml:space="preserve">持続性心心心房細動に対する後壁隔離を伴うペンタスプラインパルスフィールドアブレーションの学習曲線
+    <t xml:space="preserve">持続性心房細動に対する後壁隔離を伴うペンタスプラインパルスフィールドアブレーションの学習曲線
 (Learning Curve of Pentaspline Pulsed-Field Ablation With Posterior Wall Isolation for Persistent Atrial Fibrillation.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】ペンタスプライン パルスフィールド アブレーション (PFA) は、持続性心心心房細動 (AF) における肺静脈隔離 (PVI) および後壁隔離 (PWI) の新しい治療法と… (観察研究・その他 / 症例数: 不明)
+    <t xml:space="preserve">【概要】ペンタスプライン パルスフィールド アブレーション (PFA) は、持続性心房細動 (AF) における肺静脈隔離 (PVI) および後壁隔離 (PWI) の新しい治療法と… (観察研究・その他 / 症例数: 不明)
 【方法】われわれは、蛍光透視法および心臓内心エコー検査下での PFA を受けている持続性 AF 患者 182 名を連続して分析した。
 【結果】学習曲線が観察され、最初の 20 回の処置中に不完全な病変形成が最も減少しました。
 【結論】PVI + PWI を使用したペンタスプライン PFA 中の病変の完全性は、処置の経験が増えるにつれて徐々に向上しる</t>
@@ -1186,14 +1186,14 @@
     <t>https://pubmed.ncbi.nlm.nih.gov/42801542/</t>
   </si>
   <si>
-    <t xml:space="preserve">心三心筋症における心心心房細動に対するマルチモダリティ画像誘導パルスフィールドアブレーション
+    <t xml:space="preserve">心三心筋症における心房細動に対するマルチモダリティ画像誘導パルスフィールドアブレーション
 (Multimodality Imaging-Guided Pulsed Field Ablation for Atrial Fibrillation in Cor Triatriatum Sinister.)</t>
   </si>
   <si>
     <t xml:space="preserve">【概要】マルチモダリティイメージングにより、悪性三心筋症患者における安全な経中隔アクセスとカテーテルナビゲーションが容易になりました (観察研究・その他 / 症例数: 不明)
-【方法】CARTO に統合された VARIPULSE パルスフィールド アブレーションは、合併症を起こすことなく肺静脈の隔離を達成し、複雑な先天性左心房の解剖学的構造における心心心房細動に対する実行可能な治療戦略を実証しました
-【結果】CARTO に統合された VARIPULSE パルスフィールド アブレーションは、合併症を起こすことなく肺静脈の隔離を達成し、複雑な先天性左心房の解剖学的構造における心心心房細動に対する実行可能な治療戦略を実証しました
-【結論】CARTO に統合された VARIPULSE パルスフィールド アブレーションは、合併症を起こすことなく肺静脈の隔離を達成し、複雑な先天性左心房の解剖学的構造における心心心房細動に対する実行可能な治療戦略を実証しました</t>
+【方法】CARTO に統合された VARIPULSE パルスフィールド アブレーションは、合併症を起こすことなく肺静脈の隔離を達成し、複雑な先天性左心房の解剖学的構造における心房細動に対する実行可能な治療戦略を実証しました
+【結果】CARTO に統合された VARIPULSE パルスフィールド アブレーションは、合併症を起こすことなく肺静脈の隔離を達成し、複雑な先天性左心房の解剖学的構造における心房細動に対する実行可能な治療戦略を実証しました
+【結論】CARTO に統合された VARIPULSE パルスフィールド アブレーションは、合併症を起こすことなく肺静脈の隔離を達成し、複雑な先天性左心房の解剖学的構造における心房細動に対する実行可能な治療戦略を実証しました</t>
   </si>
   <si>
     <t xml:space="preserve">J Arrhythm
@@ -1229,11 +1229,11 @@
     <t>https://pubmed.ncbi.nlm.nih.gov/42798728/</t>
   </si>
   <si>
-    <t xml:space="preserve">心心心房細動のバルーン・イン・バスケット・パルスフィールド・アブレーションにおけるモニタリングされた麻酔管理と全身麻酔：処置のタイミングと急性処置の結果の年齢に応じた分析
+    <t xml:space="preserve">心房細動のバルーン・イン・バスケット・パルスフィールド・アブレーションにおけるモニタリングされた麻酔管理と全身麻酔：処置のタイミングと急性処置の結果の年齢に応じた分析
 (Monitored anesthesia care versus general anesthesia for balloon-in-basket pulsed-field ablation of atrial fibrillation: an age-matched analysis of procedural timing and acute procedural outcomes.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】米国では、全身麻酔（GA）が心心心房細動（AF）カテーテルアブレーションの鎮静戦略として好まれている。 (観察研究・その他 / 症例数: 不明)
+    <t xml:space="preserve">【概要】米国では、全身麻酔（GA）が心房細動（AF）カテーテルアブレーションの鎮静戦略として好まれている。 (観察研究・その他 / 症例数: 不明)
 【方法】我々は、2施設の電気生理学レジストリから、連続する39例のMAC症例とVOLT BiB PFAを受けた83例のGA症例のプールを遡及的に分析した。
 【結果】総室時間 (103.5 ± 20.0 対 126.2 ± 33.1 分; p = 0.0004)、処置前の準備時間 (33.4 ± 10.0 対 50.3 ± 28.0 分; p = 0.0007)、および処置後のターン…
 【結論】AFのためにBiB PFA（VOLT）を受けた年齢を一致させたコホートでは、MACはGAよりも総室時間、処置前の準備時間、および処置後の回転時間の短縮と関連しており、アブレーション…</t>
@@ -1249,7 +1249,7 @@
 (Pulse Field Ablation: From Bench to Blueprint: Mechanistic Insights and Device Engineering and Early Clinical Translation.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】パルスフィールドアブレーションは、従来の熱エネルギーに代わる非熱的で組織選択的な代替手段を提供することにより、心心心房細動アブレーションの状況を急速に再構築しました (観察研究・その他 / 症例数: 不明)
+    <t xml:space="preserve">【概要】パルスフィールドアブレーションは、従来の熱エネルギーに代わる非熱的で組織選択的な代替手段を提供することにより、心房細動アブレーションの状況を急速に再構築しました (観察研究・その他 / 症例数: 不明)
 【方法】このレビューでは、パルスフィールドアブレーションをより安全、より高速、より正確な技術として確立した科学的基礎、前臨床証拠、工学的進歩に焦点を当てている
 【結果】不可逆的なエレクトロポレーションが心筋の選択性をどのように達成するか、近くの構造の保存を確認した極めて重要な研究、効率的かつ耐久性のある病変を作成するために設計された最新のカテーテル システムの進化について説明しる
 【結論】パルスフィールドアブレーションプラットフォームは成熟し続けるにつれて、処置上の安全基準を再定義し、心臓電気生理学における治療の可能性を拡大している</t>
@@ -1292,7 +1292,7 @@
 (Efficacy and Safety of 60 W Versus 90 W, 4-s Radiofrequency Applications to the Esophagus-Adjacent Left Atrial Posterior Wall During Pulmonary Vein Isolation: A Pilot Study.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】QDOT MICRO カテーテルを使用した非常に高出力 (51 ～ 90 W)、短時間 (4 秒) の高周波アプリケーション (QMODE+) では、心心心房細動 (AF) … (観察研究・その他 / 症例数: 不明)
+    <t xml:space="preserve">【概要】QDOT MICRO カテーテルを使用した非常に高出力 (51 ～ 90 W)、短時間 (4 秒) の高周波アプリケーション (QMODE+) では、心房細動 (AF) … (観察研究・その他 / 症例数: 不明)
 【方法】50 人の AF 患者は、食道周囲領域に適用される QMODE+ 出力に基づいて、60 W (= 24) と 90 W (= 26) の 2 つのグループに無作為にに割り…
 【結果】接触力の中央値は、90 W グループよりも 60 W グループの方が有意に高かった (60 W グループでは 12.9 g [IQR 10.2、15.8]、90 W グループでは 10.9 g [IQR 8.4、14.2…
 【結論】食道周囲領域への 60 W および 90 W QMODE+ RF アプリケーションでは、急性伝導ブロック、内視鏡検査で検出された食道損傷、および 12 か月の AT 無再発生存率が…</t>
@@ -1311,11 +1311,11 @@
     <t>2026-Sep-23</t>
   </si>
   <si>
-    <t xml:space="preserve">急性心不全入院中の心心心房細動に対するカテーテルアブレーションの安全性: JROAD-DPC データベースからの全国的分析
+    <t xml:space="preserve">急性心不全入院中の心房細動に対するカテーテルアブレーションの安全性: JROAD-DPC データベースからの全国的分析
 (Safety of Catheter Ablation for Atrial Fibrillation During Hospitalisation for Acute Heart Failure: A Nationwide Analysis From the JROAD-DPC Database.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】急性心不全入院中の心心心房細動に対するカテーテルアブレーションの安全性: JROAD-DPC データベースからの全国的分析における臨床効果の検証 (観察研究・その他 / 症例数: 不明)
+    <t xml:space="preserve">【概要】急性心不全入院中の心房細動に対するカテーテルアブレーションの安全性: JROAD-DPC データベースからの全国的分析における臨床効果の検証 (観察研究・その他 / 症例数: 不明)
 【方法】松浦遥医学博士、金岡幸四郎医学博士...
 【結果】、千舎木翔子医学博士、武川幸樹医学...
 【結論】博士、岩永義隆医学博士、北村哲久医</t>
@@ -1331,7 +1331,7 @@
 (Effect of Pulsed Field Timing Sequence and Electrode Cooling on Ablation Safety and Efficacy Surrogates: A Preclinical Study.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】可変ループ円形カテーテルは、心心心房細動治療のための安全で効果的なパルスフィールドアブレーションカテーテルであることが示されている。 (観察研究・その他 / 症例数: 不明)
+    <t xml:space="preserve">【概要】可変ループ円形カテーテルは、心房細動治療のための安全で効果的なパルスフィールドアブレーションカテーテルであることが示されている。 (観察研究・その他 / 症例数: 不明)
 【方法】24 頭のヨークシャー豚を、可変ループ円形カテーテルを使用したパルスフィールド アブレーションで治療しました。
 【結果】すべてのグループにおいて、側副傷害の証拠のない経壁性、周囲性、肺静脈病変によって示されるように、急性および慢性肺静脈隔離効果が 100% を認めた。
 【結論】両方の投与条件にわたって、Seq1、Seq2、および Seq1 を含むすべてのグループにわたって、一貫して耐久性のある肺静脈隔離が認めた</t>
@@ -1430,14 +1430,14 @@
     <t>2026-Sep-21</t>
   </si>
   <si>
-    <t xml:space="preserve">脂質プロファイリング分析と機能同定による、心心心房細動における重要なネガティブメディエーターとしてのスフィンゴミエリン
+    <t xml:space="preserve">脂質プロファイリング分析と機能同定による、心房細動における重要なネガティブメディエーターとしてのスフィンゴミエリン
 (Sphingomyelin as a key negative mediator in atrial fibrillation via lipid proﬁling analysis and functional identiﬁcation.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】心心心房細動 (AF) は、世界的に最も蔓延している不整脈の 1 つとして浮上しており、その発生率は継続的に増加しており、それにより公衆衛生上の重大な懸念事項にまで高まってい… (観察研究・その他 / 症例数: 不明)
+    <t xml:space="preserve">【概要】心房細動 (AF) は、世界的に最も蔓延している不整脈の 1 つとして浮上しており、その発生率は継続的に増加しており、それにより公衆衛生上の重大な懸念事項にまで高まってい… (観察研究・その他 / 症例数: 不明)
 【方法】そして
 【結果】ツリーベースのアンサンブル学習支援リピドミクスを使用して、スフィンゴミエリンが重要な差次的代謝産物として同定され、AF 患者では大幅に減少していることが判明しました。
-【結論】まとめると、これらの発見は、Rap1 シグナル伝達経路の阻害を通じて心心心房細動を軽減するスフィンゴミエリンおよび SMPD 阻害剤の治療可能性を強調し、それによってスフィンゴミエリン…</t>
+【結論】まとめると、これらの発見は、Rap1 シグナル伝達経路の阻害を通じて心房細動を軽減するスフィンゴミエリンおよび SMPD 阻害剤の治療可能性を強調し、それによってスフィンゴミエリン…</t>
   </si>
   <si>
     <t>Wang L, Shi A, Yu D, Jiang Z, Chen Q, Yu X, et al.. Sphingomyelin as a key negative mediator in atrial fibrillation via lipid proﬁling analysis and functional identiﬁcation.. Europace. 2026 Sep 21;:. doi: 10.1093/europace/euag270 doi.</t>
@@ -1452,8 +1452,8 @@
   <si>
     <t xml:space="preserve">【概要】パルスフィールドアブレーション (PFA) は心室アブレーションに使用されることが増えている (観察研究・その他 / 症例数: 不明)
 【方法】我々は、左心室頻拍アブレーションに対する逆行性大動脈アプローチによる可変ループ円形 PFA カテーテル (Varipulse、Biosense Webster, Inc.、カリフォルニア州アーバイン) の使用を説明する新しい症例を紹介しる
-【結果】この処置は合併症なく完了し、3 か月の追跡調査を通じて VT の再発は観察されなかった。この症例は、このアプローチの実現可能性を強調し、この統合された PFA プラットフォームの潜在的な用途を、現在の心心心房細動アブレーションの適応を超えて拡大しる
-【結論】この症例は、このアプローチの実現可能性を強調し、この統合された PFA プラットフォームの潜在的な用途を、現在の心心心房細動アブレーションの適応を超えて拡大しる</t>
+【結果】この処置は合併症なく完了し、3 か月の追跡調査を通じて VT の再発は観察されなかった。この症例は、このアプローチの実現可能性を強調し、この統合された PFA プラットフォームの潜在的な用途を、現在の心房細動アブレーションの適応を超えて拡大しる
+【結論】この症例は、このアプローチの実現可能性を強調し、この統合された PFA プラットフォームの潜在的な用途を、現在の心房細動アブレーションの適応を超えて拡大しる</t>
   </si>
   <si>
     <t>Jiwani S, Bogun F, Franzon TA, Liang JJ. Left ventricular ablation for ventricular tachycardia using a variable-loop circular pulsed field ablation catheter.. J Interv Card Electrophysiol. 2026 Sep 19;:. doi: 10.1007/s10840-026-02441-4 doi.</t>
@@ -1482,7 +1482,7 @@
 (Incorporating a Shortened Long-Term Effectiveness END Point Into Catheter Ablation Trials: Statistical Properties and Implications.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】心心心房細動アブレーションの試験における 6 か月の有効性エンドポイントの使用に関する証拠は限られている。 (観察研究・その他 / 症例数: 不明)
+    <t xml:space="preserve">【概要】心房細動アブレーションの試験における 6 か月の有効性エンドポイントの使用に関する証拠は限られている。 (観察研究・その他 / 症例数: 不明)
 【方法】4 つの前向き研究からの患者レベルのデータが集約された。
 【結果】現在のエンドポイントと提案されたエンドポイントの比較分析では、最近の 4 つの臨床試験全体で 83% ～ 92% の範囲の一致と 57% ～ 76% の範囲の感度が実証された。
 【結論】2 か月のブランク期間を含む 6 か月の追跡期間という提案されたエンドポイントは、現在の 12 か月の有効性エンドポイントと妥当なレベルの一致を示しました</t>
@@ -1530,14 +1530,14 @@
     <t>https://pubmed.ncbi.nlm.nih.gov/42748463/</t>
   </si>
   <si>
-    <t xml:space="preserve">発作性心心心房細動に対するナノ秒パルスフィールドアブレーション: 実現可能性、安全性、骨格筋活性化
+    <t xml:space="preserve">発作性心房細動に対するナノ秒パルスフィールドアブレーション: 実現可能性、安全性、骨格筋活性化
 (Nanosecond pulsed field ablation for paroxysmal atrial fibrillation: feasibility, safety, and skeletal muscle activation.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】発作性心心心房細動に対するナノ秒パルスフィールドアブレーション: 実現可能性、安全性、骨格筋活性化 (観察研究・その他 / 症例数: 不明)
+    <t xml:space="preserve">【概要】発作性心房細動に対するナノ秒パルスフィールドアブレーション: 実現可能性、安全性、骨格筋活性化 (観察研究・その他 / 症例数: 不明)
 【方法】新規技術と既存治療法との直接比較・評価手法
 【結果】主要エンドポイントおよび併発症発生率の比較解析
-【結論】発作性心心心房細動に対するナノ秒パルスフィールドアブレーション: 実現可能性、安全性、骨格筋活性化において良好な治療成績と安全性を確認</t>
+【結論】発作性心房細動に対するナノ秒パルスフィールドアブレーション: 実現可能性、安全性、骨格筋活性化において良好な治療成績と安全性を確認</t>
   </si>
   <si>
     <t xml:space="preserve">Europace
@@ -1550,11 +1550,11 @@
     <t>https://pubmed.ncbi.nlm.nih.gov/42746824/</t>
   </si>
   <si>
-    <t xml:space="preserve">心心心房細動アブレーション用の可変ループ円形カテーテルパルスフィールドアブレーションシステムの多施設での経験
+    <t xml:space="preserve">心房細動アブレーション用の可変ループ円形カテーテルパルスフィールドアブレーションシステムの多施設での経験
 (Multicentre experience with the variable-loop circular catheter pulsed-field ablation system for atrial fibrillation ablation.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】心心心房細動アブレーション用の可変ループ円形カテーテルパルスフィールドアブレーションシステムの多施設での経験における臨床効果の検証 (観察研究・その他 / 症例数: 不明)
+    <t xml:space="preserve">【概要】心房細動アブレーション用の可変ループ円形カテーテルパルスフィールドアブレーションシステムの多施設での経験における臨床効果の検証 (観察研究・その他 / 症例数: 不明)
 【方法】pmc ヨーロッパ ヨーロッパ 728 ヨーロッパ 100883649 ヨーロッパ ヨーロッパ 1099-5129 1532-2092 オックスフォード大学出版局 PMC13621801 PMC13621801.1 13621801 136...
 【結果】rsity , Via Conca 71, Ancona 60126 , Italy Cardiology and Arrhythmology Clinic, Marche University Hospital , Via Conca 71, Ancona 60126 , It...
 【結論】gnucci Paolo 生物医学および公衆衛生学部、マルケ工科大学、Via Conca 71、Ancona 60126 、イタリア心臓病学および 不整脈クリニック、マルケ大学病院、Via Conca 71、Ancona 60126 、イタ</t>
@@ -1676,14 +1676,14 @@
     <t>https://pubmed.ncbi.nlm.nih.gov/42360886/</t>
   </si>
   <si>
-    <t xml:space="preserve">持続性および長期持続性心心心房細動に対する補助的な後壁隔離術: CORNERSTONE AF 試験
+    <t xml:space="preserve">持続性および長期持続性心房細動に対する補助的な後壁隔離術: CORNERSTONE AF 試験
 (Adjunctive posterior wall isolation for persistent and long-standing persistent atrial fibrillation: the CORNERSTONE AF trial.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】持続性および長期持続性心心心房細動に対する補助的な後壁隔離術: CORNERSTONE AF 試験 (観察研究・その他 / 症例数: 不明)
+    <t xml:space="preserve">【概要】持続性および長期持続性心房細動に対する補助的な後壁隔離術: CORNERSTONE AF 試験 (観察研究・その他 / 症例数: 不明)
 【方法】新規技術と既存治療法との直接比較・評価手法
 【結果】主要エンドポイントおよび併発症発生率の比較解析
-【結論】持続性および長期持続性心心心房細動に対する補助的な後壁隔離術: CORNERSTONE AF 試験において良好な治療成績と安全性を確認</t>
+【結論】持続性および長期持続性心房細動に対する補助的な後壁隔離術: CORNERSTONE AF 試験において良好な治療成績と安全性を確認</t>
   </si>
   <si>
     <t xml:space="preserve">Eur Heart J
@@ -1756,11 +1756,11 @@
     <t>https://pubmed.ncbi.nlm.nih.gov/42214646/</t>
   </si>
   <si>
-    <t xml:space="preserve">持続性心心心房細動の進行とアブレーションの影響：系統的レビューとメタ分析
+    <t xml:space="preserve">持続性心房細動の進行とアブレーションの影響：系統的レビューとメタ分析
 (Progression of persistent atrial fibrillation and impact of ablation: A systematic review and meta-analysis.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】持続性心心心房細動 (PsAF) は、多くの場合、発作性心心心房細動と永続性心心心房細動 (AF) の間の中間段階とみなされる。 (観察研究・その他 / 症例数: 不明)
+    <t xml:space="preserve">【概要】持続性心房細動 (PsAF) は、多くの場合、発作性心房細動と永続性心房細動 (AF) の間の中間段階とみなされる。 (観察研究・その他 / 症例数: 不明)
 【方法】私たちは、2026 年 1 月までに PubMed と Embase で、PsAF から永続性 AF および/または管理経路への進行を報告する研究を系統的に検索しました。
 【結果】21件の研究のうち; 17 件が一次メタ分析に貢献しました。
 【結論】PsAF の進行は不均一であり、現代のコホートは歴史的なシリーズよりも低い率を示唆している</t>
@@ -1816,14 +1816,14 @@
     <t>https://pubmed.ncbi.nlm.nih.gov/42128250/</t>
   </si>
   <si>
-    <t xml:space="preserve">心心心房細動を患うアジア人患者と非アジア人患者における直接経口抗凝固薬とワルファリン：COMBINE AF による患者レベルのメタ分析
+    <t xml:space="preserve">心房細動を患うアジア人患者と非アジア人患者における直接経口抗凝固薬とワルファリン：COMBINE AF による患者レベルのメタ分析
 (Direct oral anticoagulants vs warfarin in Asian vs non-Asian patients with atrial fibrillation: a patient-level meta-analysis from COMBINE AF.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】および目的: 心心心房細動の臨床転帰を比較する大規模なランダム化データ (観察研究・その他 / 症例数: 不明)
-【方法】心心心房細動患者における直接経口抗凝固薬（DOAC）対ワルファリンの4つの重要なランダム化試験からの患者レベルのデータをプールした、心心心房細動における非ビタミンKアンタゴニスト…
+    <t xml:space="preserve">【概要】および目的: 心房細動の臨床転帰を比較する大規模なランダム化データ (観察研究・その他 / 症例数: 不明)
+【方法】心房細動患者における直接経口抗凝固薬（DOAC）対ワルファリンの4つの重要なランダム化試験からの患者レベルのデータをプールした、心房細動における非ビタミンKアンタゴニスト…
 【結果】合計10,212人のアジア人の患者と61,471人の非アジア人の患者が特定された。
-【結論】心心心房細動患者におけるSD DOACとワルファリンの臨床転帰は、一般に、非アジア人種よりもアジア人種の患者でさらに良好であった</t>
+【結論】心房細動患者におけるSD DOACとワルファリンの臨床転帰は、一般に、非アジア人種よりもアジア人種の患者でさらに良好であった</t>
   </si>
   <si>
     <t xml:space="preserve">Eur Heart J
@@ -1903,7 +1903,7 @@
     <t>⬅ 最新論文一覧に戻る</t>
   </si>
   <si>
-    <t xml:space="preserve">📄 [No.1] 中等度の脳卒中リスクを伴う心心心房細動に対する抗凝固療法
+    <t xml:space="preserve">📄 [No.1] 中等度の脳卒中リスクを伴う心房細動に対する抗凝固療法
 (Anticoagulation for Atrial Fibrillation with Intermediate Stroke Risk.)</t>
   </si>
   <si>
@@ -1937,7 +1937,7 @@
     <t>🇯🇵 抄録 (Abstract) 日本語全訳 (全文直訳)</t>
   </si>
   <si>
-    <t>背景: 現在の米国および欧州のガイドラインでは、脳卒中リスクが中程度の心心房細動患者に対するクラス IIa の適応として経口抗凝固療法を推奨している。ただし、ランダム化試験からの証拠が必要です。  方法：我々は、脳卒中リスクが中程度の心心房細動患者（CHADS-VAScスケールで男性のスコアが1、女性のスコアが2、範囲は0〜9、スコアが高いほど脳卒中リスクが高いことを示す）を有する患者を対象とした、多施設共同、非盲検、裁定者マスクの優越性試験を韓国で実施した。  患者は、直接経口抗凝固薬（DOAC）療法を受ける群と抗凝固療法を受けない群に1:1の比率で無作為に割り当てられた。 主要エンドポイントは、24ヵ月時点での脳卒中、全身性塞栓症、大出血、または心血管疾患による死亡の複合であった。  結果：ランダム化を受けた1,803人の患者のうち、902人はDOAC療法を受けるように割り当てられ、901人は抗凝固療法を受けないように割り当てられた。  患者の平均年齢は60.4歳で、23.7%が女性でした。  24ヵ月時点で、主要エンドポイントイベントはDOAC群の患者4名（累積発生率、0.5%）、抗凝固薬非投与群の患者13名（累積発生率、1.5%）で発生した（差、-1.0パーセントポイント、95%信頼区間[CI]、-2.0～-0.1、P=0.03、ハザード比、 0.31; 95% CI、0.10 ～ 0.94)。 脳卒中は、DOAC群では3名（累積発生率、0.3%）、抗凝固剤非投与群では10名（累積発生率、1.1%）に発生した。  全身性塞栓症と大出血の発生率は 2 つの試験グループで同様であるようであり、どちらのグループでも心血管疾患による死亡は発生しませんでした。  重篤な有害事象は、DOAC 群では 80 名（8.9%）、抗凝固薬非投与群では 84 名（9.3%）に発生しました。  結論：脳卒中リスクが中程度の心心房細動患者において、DOAC療法は、抗凝固療法を行わなかった場合に比べ、24カ月時点で脳卒中、全身性塞栓症、大出血、または心血管原因による死亡のリスクを低下させた。 （韓国保健福祉省などから資金提供、SINGLE-AF ClinicalTrials.gov番号、NCT04437654）。</t>
+    <t>背景: 現在の米国および欧州のガイドラインでは、脳卒中リスクが中程度の心房細動患者に対するクラス IIa の適応として経口抗凝固療法を推奨している。ただし、ランダム化試験からの証拠が必要です。  方法：我々は、脳卒中リスクが中程度の心房細動患者（CHADS-VAScスケールで男性のスコアが1、女性のスコアが2、範囲は0〜9、スコアが高いほど脳卒中リスクが高いことを示す）を有する患者を対象とした、多施設共同、非盲検、裁定者マスクの優越性試験を韓国で実施した。  患者は、直接経口抗凝固薬（DOAC）療法を受ける群と抗凝固療法を受けない群に1:1の比率で無作為に割り当てられた。 主要エンドポイントは、24ヵ月時点での脳卒中、全身性塞栓症、大出血、または心血管疾患による死亡の複合であった。  結果：ランダム化を受けた1,803人の患者のうち、902人はDOAC療法を受けるように割り当てられ、901人は抗凝固療法を受けないように割り当てられた。  患者の平均年齢は60.4歳で、23.7%が女性でした。  24ヵ月時点で、主要エンドポイントイベントはDOAC群の患者4名（累積発生率、0.5%）、抗凝固薬非投与群の患者13名（累積発生率、1.5%）で発生した（差、-1.0パーセントポイント、95%信頼区間[CI]、-2.0～-0.1、P=0.03、ハザード比、 0.31; 95% CI、0.10 ～ 0.94)。 脳卒中は、DOAC群では3名（累積発生率、0.3%）、抗凝固剤非投与群では10名（累積発生率、1.1%）に発生した。  全身性塞栓症と大出血の発生率は 2 つの試験グループで同様であるようであり、どちらのグループでも心血管疾患による死亡は発生しませんでした。  重篤な有害事象は、DOAC 群では 80 名（8.9%）、抗凝固薬非投与群では 84 名（9.3%）に発生しました。  結論：脳卒中リスクが中程度の心房細動患者において、DOAC療法は、抗凝固療法を行わなかった場合に比べ、24カ月時点で脳卒中、全身性塞栓症、大出血、または心血管原因による死亡のリスクを低下させた。 （韓国保健福祉省などから資金提供、SINGLE-AF ClinicalTrials.gov番号、NCT04437654）。</t>
   </si>
   <si>
     <t>🔤 抄録 (Abstract) 英語原文</t>
@@ -1956,7 +1956,7 @@
     <t>ℹ️ 論文本文 (Full Text) や図表の全ページ閲覧は、上記の PubMed URL (https://pubmed.ncbi.nlm.nih.gov/42663303/) または DOI リンク先の出版社公式サイトからアクセスできます。</t>
   </si>
   <si>
-    <t xml:space="preserve">📄 [No.2] 心心心房細動アブレーションにおける超音波ガイド下と従来の静脈穿刺の比較: ULYSSES 試験
+    <t xml:space="preserve">📄 [No.2] 心房細動アブレーションにおける超音波ガイド下と従来の静脈穿刺の比較: ULYSSES 試験
 (Ultrasound-guided vs conventional venous puncture for atrial fibrillation ablation: the ULYSSES trial.)</t>
   </si>
   <si>
@@ -1972,7 +1972,7 @@
     <t>10.1093/eurheartj/ehag291 doi</t>
   </si>
   <si>
-    <t>背景と目的: 血管アクセス部位の合併症は、心心房細動カテーテルアブレーションの最も一般的な処置関連の有害事象です。  超音波ガイド下の大腿静脈穿刺がこれらの血管アクセスの合併症を軽減するかどうかはまだ不明です。  この研究者主導の多施設非盲検優位性試験では、心心房細動または左心房頻脈カテーテルアブレーションを受けている患者が、超音波ガイド下静脈穿刺戦略（介入群）または触診ガイド下従来の静脈穿刺群（対照群）にランダムに割り付けられた。 複合主要転帰は、処置後30日までの静脈アクセス部位の合併症の発生であり、介入が必要な、または長期入院につながる動静脈瘻、偽動脈瘤、またはアクセス部位の出血として定義された。  副次評価項目には、手術期間、穿刺期間、30日以内の手術関連の脳卒中/一過性脳虚血発作、意図しない動脈穿刺の回数、静脈アクセス試行の失敗回数、および入院期間が含まれた。  結果: 6 つのセンターで、986 人の患者がランダム化されました。  合計 496 人の患者が超音波ガイド下穿刺グループに割り当てられ、490 人の患者が従来の穿刺グループに割り当てられました。 計画された患者の半数が登録された後の最初の中間解析の後、試験は有効性を理由に中止された。  複合主要アウトカムは介入群の患者 3 名 (0.6%)、対照群の患者 16 名 (3.3%) に発生しました (リスク比 0.19; 95% 信頼区間 0.05-0.63; P = 0.002)。  さらに、超音波ガイド下の静脈穿刺は、意図しない動脈穿刺の割合（2% vs 16%、P &lt; 0.0001）と、他のグループへのクロスオーバーを必要とする静脈アクセス試行の失敗率（0.2% vs 8.2%、P &lt; 0.0001）を大幅に減少させました。  結論：心心房細動アブレーション処置のための超音波ガイド下静脈アクセスは、血管アクセス部位の合併症を大幅に減少させた。  ユリシーズ臨床試験政府番号: NCT06403527。</t>
+    <t>背景と目的: 血管アクセス部位の合併症は、心房細動カテーテルアブレーションの最も一般的な処置関連の有害事象です。  超音波ガイド下の大腿静脈穿刺がこれらの血管アクセスの合併症を軽減するかどうかはまだ不明です。  この研究者主導の多施設非盲検優位性試験では、心房細動または左心房頻脈カテーテルアブレーションを受けている患者が、超音波ガイド下静脈穿刺戦略（介入群）または触診ガイド下従来の静脈穿刺群（対照群）にランダムに割り付けられた。 複合主要転帰は、処置後30日までの静脈アクセス部位の合併症の発生であり、介入が必要な、または長期入院につながる動静脈瘻、偽動脈瘤、またはアクセス部位の出血として定義された。  副次評価項目には、手術期間、穿刺期間、30日以内の手術関連の脳卒中/一過性脳虚血発作、意図しない動脈穿刺の回数、静脈アクセス試行の失敗回数、および入院期間が含まれた。  結果: 6 つのセンターで、986 人の患者がランダム化されました。  合計 496 人の患者が超音波ガイド下穿刺グループに割り当てられ、490 人の患者が従来の穿刺グループに割り当てられました。 計画された患者の半数が登録された後の最初の中間解析の後、試験は有効性を理由に中止された。  複合主要アウトカムは介入群の患者 3 名 (0.6%)、対照群の患者 16 名 (3.3%) に発生しました (リスク比 0.19; 95% 信頼区間 0.05-0.63; P = 0.002)。  さらに、超音波ガイド下の静脈穿刺は、意図しない動脈穿刺の割合（2% vs 16%、P &lt; 0.0001）と、他のグループへのクロスオーバーを必要とする静脈アクセス試行の失敗率（0.2% vs 8.2%、P &lt; 0.0001）を大幅に減少させました。  結論：心房細動アブレーション処置のための超音波ガイド下静脈アクセスは、血管アクセス部位の合併症を大幅に減少させた。  ユリシーズ臨床試験政府番号: NCT06403527。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND AND AIMS:
@@ -1990,7 +1990,7 @@
     <t>ℹ️ 論文本文 (Full Text) や図表の全ページ閲覧は、上記の PubMed URL (https://pubmed.ncbi.nlm.nih.gov/41979041/) または DOI リンク先の出版社公式サイトからアクセスできます。</t>
   </si>
   <si>
-    <t xml:space="preserve">📄 [No.3] 心心心房細動における房室結節アブレーションを伴うまたは伴わない心臓再同期療法: CAAN-AF 試験
+    <t xml:space="preserve">📄 [No.3] 心房細動における房室結節アブレーションを伴うまたは伴わない心臓再同期療法: CAAN-AF 試験
 (Cardiac resynchronization therapy with or without atrioventricular node ablation in atrial fibrillation: the CAAN-AF trial.)</t>
   </si>
   <si>
@@ -2006,7 +2006,7 @@
     <t>10.1093/eurheartj/ehag206 doi</t>
   </si>
   <si>
-    <t>背景と目的：駆出率低下（HFrEF）を伴う心不全患者は、心心房細動（AF）を併発している場合、心臓再同期療法（CRT）から得られる利益が少なくなります。  観察データは、房室結節アブレーション (AVNA) がこの集団における CRT の有効性を高める可能性を示唆しています。  この試験は、HFrEFおよび永続性AF患者のCRT転帰に対するAVNAの効果を医療レート管理療法(MRCT)と比較して評価することを目的とした。  CAAN-AF試験は、HFrEF、永久AF、およびCRT除細動器（CRT-D）患者におけるAVNAの影響を評価する、国際的な前向き多施設ランダム化対照試験である。  参加者は、安静時心拍数 &lt;90 bpm を対象とする AVNA または MRCT にランダムに (1:1) 割り当てられました。 すべての参加者がデバイスの最適化を受けました。  主要評価項目は、全死因死亡率と非致死性心不全事象の複合値であった。  副次評価項目には、心血管死亡率、予定外の入院、機器治療を必要とする心室不整脈、6分の歩行距離（6MWD）、生活の質などが含まれた。  結果：無益のため試験が早期に終了したため、合計 143 人の患者が無作為に割り付けられた（AVNA に 67 人、MRCT に 76 人）。  ベースラインの特徴はグループ全体で同様でした。  主要エンドポイント [イベント数 47 対 46;発生率比（IRR）、1.16。 95% 信頼区間 (CI)、0.60-2.24]。 二次転帰には、心血管死亡率（オッズ比、1.93; 95% CI 0.60-6.20）、予定外の入院（IRR、1.01; 95% CI 0.71-1.74）、機器治療を必要とする心室不整脈（IRR、0.68; 95% CI 0.17-2.63）が含まれます。 6MWD および SF-36 スコアも有意な差は示されませんでした。  結論：永久性AFおよびCRT-D患者を対象としたこのランダム化試験では、MRCTと比較してAVNAによる全死因死亡率および非致死性心不全イベントの減少を示す証拠は見出されなかった。  トライアル登録: NCT01522898。</t>
+    <t>背景と目的：駆出率低下（HFrEF）を伴う心不全患者は、心房細動（AF）を併発している場合、心臓再同期療法（CRT）から得られる利益が少なくなります。  観察データは、房室結節アブレーション (AVNA) がこの集団における CRT の有効性を高める可能性を示唆しています。  この試験は、HFrEFおよび永続性AF患者のCRT転帰に対するAVNAの効果を医療レート管理療法(MRCT)と比較して評価することを目的とした。  CAAN-AF試験は、HFrEF、永久AF、およびCRT除細動器（CRT-D）患者におけるAVNAの影響を評価する、国際的な前向き多施設ランダム化対照試験である。  参加者は、安静時心拍数 &lt;90 bpm を対象とする AVNA または MRCT にランダムに (1:1) 割り当てられました。 すべての参加者がデバイスの最適化を受けました。  主要評価項目は、全死因死亡率と非致死性心不全事象の複合値であった。  副次評価項目には、心血管死亡率、予定外の入院、機器治療を必要とする心室不整脈、6分の歩行距離（6MWD）、生活の質などが含まれた。  結果：無益のため試験が早期に終了したため、合計 143 人の患者が無作為に割り付けられた（AVNA に 67 人、MRCT に 76 人）。  ベースラインの特徴はグループ全体で同様でした。  主要エンドポイント [イベント数 47 対 46;発生率比（IRR）、1.16。 95% 信頼区間 (CI)、0.60-2.24]。 二次転帰には、心血管死亡率（オッズ比、1.93; 95% CI 0.60-6.20）、予定外の入院（IRR、1.01; 95% CI 0.71-1.74）、機器治療を必要とする心室不整脈（IRR、0.68; 95% CI 0.17-2.63）が含まれます。 6MWD および SF-36 スコアも有意な差は示されませんでした。  結論：永久性AFおよびCRT-D患者を対象としたこのランダム化試験では、MRCTと比較してAVNAによる全死因死亡率および非致死性心不全イベントの減少を示す証拠は見出されなかった。  トライアル登録: NCT01522898。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND AND AIMS:
@@ -2065,7 +2065,7 @@
     <t>10.1161/CIR.0000000000001454 doi</t>
   </si>
   <si>
-    <t>カフェインは、世界で最も一般的に消費されている薬物の 1 つです。  それはさまざまな天然物質に含まれており、合成的に得られた純粋な形で摂取できます。  人間を対象とした研究の大部分は観察的なものであり、カフェインを含む飲料や食品に焦点を当てています。  カフェインと心血管の危険因子および疾患との関係は複雑で、摂取するカフェインの性質や個人レベルの傾向に応じて不均一性を示します。  急性と慢性のカフェイン関連の心血管への影響は、多くの場合異なります。  ほとんどの研究は、天然に存在するカフェイン含有製品の摂取と血圧の間に逆J字型の関係があることを示唆しています。 カフェインと糖尿病の関係に関するデータは一貫していませんが、習慣的なコーヒー摂取は 2 型糖尿病の発症リスクの低下と関連しています。  カフェインと血中脂質の明確な関係は明らかではありませんが、ろ過されていないコーヒーは低密度リポタンパク質コレステロールを上昇させます。  主にコーヒーに関連して研究されたカフェインは、冠状動脈疾患や心不全のリスク低下と無関係であるか、関連していることが示されています。  カフェイン入りコーヒーの常飲者を対象としたランダム化対照試験データでは、カフェイン入りコーヒーは心心房細動発生のリスクを低下させるが、心室性期外収縮の頻度を増加させることが示されました。 データは、適度なカフェイン摂取が脳卒中のリスク低下と関連しているというかなり一貫したデータであり、これも主にコーヒー摂取の状況で研究されました。  エナジードリンクに含まれるような高用量のカフェインに関するデータは限られており、一般に心血管への害を示唆しています。</t>
+    <t>カフェインは、世界で最も一般的に消費されている薬物の 1 つです。  それはさまざまな天然物質に含まれており、合成的に得られた純粋な形で摂取できます。  人間を対象とした研究の大部分は観察的なものであり、カフェインを含む飲料や食品に焦点を当てています。  カフェインと心血管の危険因子および疾患との関係は複雑で、摂取するカフェインの性質や個人レベルの傾向に応じて不均一性を示します。  急性と慢性のカフェイン関連の心血管への影響は、多くの場合異なります。  ほとんどの研究は、天然に存在するカフェイン含有製品の摂取と血圧の間に逆J字型の関係があることを示唆しています。 カフェインと糖尿病の関係に関するデータは一貫していませんが、習慣的なコーヒー摂取は 2 型糖尿病の発症リスクの低下と関連しています。  カフェインと血中脂質の明確な関係は明らかではありませんが、ろ過されていないコーヒーは低密度リポタンパク質コレステロールを上昇させます。  主にコーヒーに関連して研究されたカフェインは、冠状動脈疾患や心不全のリスク低下と無関係であるか、関連していることが示されています。  カフェイン入りコーヒーの常飲者を対象としたランダム化対照試験データでは、カフェイン入りコーヒーは心房細動発生のリスクを低下させるが、心室性期外収縮の頻度を増加させることが示されました。 データは、適度なカフェイン摂取が脳卒中のリスク低下と関連しているというかなり一貫したデータであり、これも主にコーヒー摂取の状況で研究されました。  エナジードリンクに含まれるような高用量のカフェインに関するデータは限られており、一般に心血管への害を示唆しています。</t>
   </si>
   <si>
     <t>Caffeine is one of the most commonly consumed drugs in the world. It is found in various naturally occurring substances and can be ingested in a synthetically derived pure form. The majority of human subject-based research is observational and has focused on beverages and foods that contain caffeine. The relationships between caffeine and cardiovascular risk factors and diseases are complex, exhibiting heterogeneity depending on the nature of the caffeine consumed and individual-level propensities. Acute versus chronic caffeine-associated cardiovascular effects are often different. Most studies suggest an inverse J-shaped relationship between consumption of naturally occurring caffeinated products and blood pressure. Data on relationships between caffeine and diabetes are not consistent, but habitual coffee consumption has been associated with a lower risk of incident type 2 diabetes. Whereas no clear relationship between caffeine and blood lipids is evident, unfiltered coffee raises low-density lipoprotein cholesterol. Caffeine, studied primarily in the context of coffee, has been shown either to have no relationship or to be associated with a lower risk of coronary artery disease and heart failure. Randomized controlled trial data among regular caffeinated coffee drinkers showed that caffeinated coffee decreases the risk of atrial fibrillation occurrence but increases the frequency of premature ventricular contractions. Data are fairly consistent that moderate caffeine consumption, again studied primarily in the setting of coffee consumption, was associated with a lower risk of stroke. Data on high doses of caffeine such as that found in energy drinks are limited and generally suggest cardiovascular harm.</t>
@@ -2074,7 +2074,7 @@
     <t>ℹ️ 論文本文 (Full Text) や図表の全ページ閲覧は、上記の PubMed URL (https://pubmed.ncbi.nlm.nih.gov/42473796/) または DOI リンク先の出版社公式サイトからアクセスできます。</t>
   </si>
   <si>
-    <t xml:space="preserve">📄 [No.6] 心心心房細動患者における不安とうつ病の影響: 2 つの国際的な前向き登録からの洞察
+    <t xml:space="preserve">📄 [No.6] 心房細動患者における不安とうつ病の影響: 2 つの国際的な前向き登録からの洞察
 (Impact of anxiety and depression in patients with atrial fibrillation: Insights from 2 international prospective registries.)</t>
   </si>
   <si>
@@ -2090,7 +2090,7 @@
     <t>10.1016/j.hrthm.2026.06.001 doi</t>
   </si>
   <si>
-    <t>背景: 心心房細動 (AF) 患者の臨床転帰に対する不安および/またはうつ病の影響について入手できるデータは限られています。  目的: この研究の目的は、不安/うつ病を伴う心心房細動患者と不安/うつ病を伴わない心心房細動患者の臨床的特徴と転帰を比較することでした。  方法: ヨーロッパとアジア太平洋地域の 2 つの有望なレジストリの事後分析。  患者は、不安/うつ病に関して無症候性または症候性として分類されました。  主要転帰は、全死因死亡と重大な心血管イベント（MACE）の複合でした。  副次転帰には、全死因死亡、MACE、大出血、および個々の MACE 要素が含まれます。  Cox モデルは、ハザード比 (HR) と 95% 信頼区間 (CI) を推定します。 感度分析は、症状の重症度ごとに、また臨床的に関連するサブグループ全体にわたって実行されました。  結果：患者12,614人（平均年齢69±12歳、女性38％）のうち、4825人（38.3％、平均年齢69±12歳、女性48％）に不安/うつ病の症状があった。  不安/うつ病を伴う症状のある患者は女性であることが多く、ヨーロッパ人であり、AF関連の症状や心不全の有病率が高かった。  中央値569日（四分位範囲、365～735日）の追跡調査後、症状のある患者は複合転帰（HR、1.26; 95% CI、1.10～1.45）、全死因死亡（HR、1.31; 95% CI、1.12～1.55）、MACE（HR、1.44; 95%）のリスクが高かった。 CI、1.19-1.74）、心血管死（HR、1.87; 95% CI、1.41-2.47）。 症状の重症度に応じてリスクは増加します。地理的地域または他の分析されたサブグループでは、有意な相互作用は観察されませんでした。  結論: AF 患者では、不安/抑うつ症状は臨床転帰の悪化と関連しており、中等度から重度の症状を持つ患者ではより強い関連が観察されました。  これらの調査結果は、心心房細動管理における心理的評価の意識を高める必要性を浮き彫りにしています。</t>
+    <t>背景: 心房細動 (AF) 患者の臨床転帰に対する不安および/またはうつ病の影響について入手できるデータは限られています。  目的: この研究の目的は、不安/うつ病を伴う心房細動患者と不安/うつ病を伴わない心房細動患者の臨床的特徴と転帰を比較することでした。  方法: ヨーロッパとアジア太平洋地域の 2 つの有望なレジストリの事後分析。  患者は、不安/うつ病に関して無症候性または症候性として分類されました。  主要転帰は、全死因死亡と重大な心血管イベント（MACE）の複合でした。  副次転帰には、全死因死亡、MACE、大出血、および個々の MACE 要素が含まれます。  Cox モデルは、ハザード比 (HR) と 95% 信頼区間 (CI) を推定します。 感度分析は、症状の重症度ごとに、また臨床的に関連するサブグループ全体にわたって実行されました。  結果：患者12,614人（平均年齢69±12歳、女性38％）のうち、4825人（38.3％、平均年齢69±12歳、女性48％）に不安/うつ病の症状があった。  不安/うつ病を伴う症状のある患者は女性であることが多く、ヨーロッパ人であり、AF関連の症状や心不全の有病率が高かった。  中央値569日（四分位範囲、365～735日）の追跡調査後、症状のある患者は複合転帰（HR、1.26; 95% CI、1.10～1.45）、全死因死亡（HR、1.31; 95% CI、1.12～1.55）、MACE（HR、1.44; 95%）のリスクが高かった。 CI、1.19-1.74）、心血管死（HR、1.87; 95% CI、1.41-2.47）。 症状の重症度に応じてリスクは増加します。地理的地域または他の分析されたサブグループでは、有意な相互作用は観察されませんでした。  結論: AF 患者では、不安/抑うつ症状は臨床転帰の悪化と関連しており、中等度から重度の症状を持つ患者ではより強い関連が観察されました。  これらの調査結果は、心房細動管理における心理的評価の意識を高める必要性を浮き彫りにしています。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -2108,7 +2108,7 @@
     <t>ℹ️ 論文本文 (Full Text) や図表の全ページ閲覧は、上記の PubMed URL (https://pubmed.ncbi.nlm.nih.gov/42248315/) または DOI リンク先の出版社公式サイトからアクセスできます。</t>
   </si>
   <si>
-    <t xml:space="preserve">📄 [No.7] 心心心房細動に対する胸腔鏡下アブレーション後の早期再発と後期再発の臨床的、組織学的、分子的関連性
+    <t xml:space="preserve">📄 [No.7] 心房細動に対する胸腔鏡下アブレーション後の早期再発と後期再発の臨床的、組織学的、分子的関連性
 (Clinical, histologic, and molecular associations of early and late recurrence after thoracoscopic ablation for atrial fibrillation.)</t>
   </si>
   <si>
@@ -2124,7 +2124,7 @@
     <t>10.1016/j.hrthm.2026.05.045 doi</t>
   </si>
   <si>
-    <t>背景: 心心房細動 (AF) の早期再発 (ER) は、アブレーション後によく見られます。  しかし、そのメカニズムはまだ不明です。  目的: この研究は、ER のタイミングの変動性と晩期再発 (LR) との関係を調査し、潜在的な根底にある基質を探索することを目的としました。  方法：我々は、左心耳切除を伴う進行性AFの胸腔鏡下アブレーションを受ける449人の患者（62±9歳、女性26.7％）を前向きに登録した。  リズム監視は 2 年間実施した。  ER は、アブレーション後 90 日以内に 30 秒以上続く心房性頻拍として定義されました。 90日後の再発としてLR。  患者は、ERなし、0～30日でER、または31～90日でERに分類されました。 私たちは、ER のさまざまなメカニズムを調査するために、切除された左心耳の組織学的およびバルク RNA シーケンス分析を実行しました。  結果: 患者 449 人中 176 人 (39.2%) で ER が発生し、そのうち 152 人 (86.4%) が 30 日以内に最初の ER エピソードを経験しました。  ER なしと比較して、0 ～ 30 日および 31 ～ 90 日の ER は、より高い LR リスクと関連していました (ハザード比 1.52 および 2.01; ログランク P = 0.002)。  プロテオグリカン含有量が高いほど、LR のリスク増加と関連していました。  バルク RNA シーケンスにより、再発のない患者と比較して、ER + LR を有する患者では線維炎症経路が豊富であることが示されました。  結論: 胸腔鏡下 AF アブレーション後、ER は LR のリスク増加と関連していました。 31～90日目に発生したERは、0～30日目に発生したERよりも高い観察されたLRリスクと関連していた。  探索的発見は、再発パターン間の細胞外マトリックスのリモデリングと炎症シグナル伝達の違いを示唆しました。  臨床試験登録: AFACT 研究の ClinicalTrials.gov 識別子: NCT01091389、NL30199.018.10; MARK-AF レジストリ: NL50069.018.14。</t>
+    <t>背景: 心房細動 (AF) の早期再発 (ER) は、アブレーション後によく見られます。  しかし、そのメカニズムはまだ不明です。  目的: この研究は、ER のタイミングの変動性と晩期再発 (LR) との関係を調査し、潜在的な根底にある基質を探索することを目的としました。  方法：我々は、左心耳切除を伴う進行性AFの胸腔鏡下アブレーションを受ける449人の患者（62±9歳、女性26.7％）を前向きに登録した。  リズム監視は 2 年間実施した。  ER は、アブレーション後 90 日以内に 30 秒以上続く心房性頻拍として定義されました。 90日後の再発としてLR。  患者は、ERなし、0～30日でER、または31～90日でERに分類されました。 私たちは、ER のさまざまなメカニズムを調査するために、切除された左心耳の組織学的およびバルク RNA シーケンス分析を実行しました。  結果: 患者 449 人中 176 人 (39.2%) で ER が発生し、そのうち 152 人 (86.4%) が 30 日以内に最初の ER エピソードを経験しました。  ER なしと比較して、0 ～ 30 日および 31 ～ 90 日の ER は、より高い LR リスクと関連していました (ハザード比 1.52 および 2.01; ログランク P = 0.002)。  プロテオグリカン含有量が高いほど、LR のリスク増加と関連していました。  バルク RNA シーケンスにより、再発のない患者と比較して、ER + LR を有する患者では線維炎症経路が豊富であることが示されました。  結論: 胸腔鏡下 AF アブレーション後、ER は LR のリスク増加と関連していました。 31～90日目に発生したERは、0～30日目に発生したERよりも高い観察されたLRリスクと関連していた。  探索的発見は、再発パターン間の細胞外マトリックスのリモデリングと炎症シグナル伝達の違いを示唆しました。  臨床試験登録: AFACT 研究の ClinicalTrials.gov 識別子: NCT01091389、NL30199.018.10; MARK-AF レジストリ: NL50069.018.14。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -2192,7 +2192,7 @@
     <t>10.1111/jce.70520 doi</t>
   </si>
   <si>
-    <t>はじめに: 肺静脈隔離は依然として心心房細動 (AF) アブレーションの中心ですが、右心房基質の修正は不完全に定義されたままです。  終端クリスタ（CT）領域は右横隔神経の近くに位置し、異方性伝導および自然または機能的伝導ブロックを示す可能性があると同時に、潜在的な非肺静脈トリガー部位としても機能します。  われわれは、格子先端パルスフィールドアブレーション（PFA）で作成されたCTガイド下洞房結節（SN）温存病変セットであるクリスタ大静脈ライン（CCL）の急性実現可能性と電気解剖学的エンドポイントを評価した。  方法と結果：我々は、反復性心心房細動アブレーションまたは非発作性心心房細動に対するアブレーション中にCCL作成を受ける連続36人の患者を前向きに登録した。 CCL前の洞調律高密度右心房活性化マッピングがすべての患者で実行されました。  CT 関連の伝導遅延またはブロックが 27 人の患者 (75.0%) で観察されました。  明らかな CT ブロック ラインを持つ 14 人の患者 (38.9%) では、下側のアプリケーション セットのエッジがブロック ラインと一致していました。明らかなブロックのない残りの 22 人の患者では、留置は主に心臓内心エコー検査によって行われました。  CCL は CT の後方に配置され、その上適用セットの側縁は SN 保護のために最も早くマッピングされた副鼻腔活性化部位の後外側約 15 mm に保たれました。  CCL の最初のタグから最後のタグまでの距離は 78.8 [66.4-86.0] mm で、370 [282-481] 秒間で 26 [22-30] PFA の塗布が必要でした。 初回通過の双方向横伝導ブロックは、切除後の活性化マッピングと CCL の両側からの差動ペーシングによってすべての患者で確認されました。  翌日の吸気/呼気胸部X線撮影では、横隔神経麻痺を示唆する異常は示されませんでした。ペースメーカを必要とするSN機能障害やその他の臨床的に明らかな付随的損傷は発生しませんでした。  結論： CT ガイド下、SN 温存 CCL は格子先端 PFA を用いて再現性よく作製でき、臨床的に明らかな横隔神経麻痺を伴わずに初回通過双方向横伝導ブロックを生成する。  これらの発見は、確実な実現可能性と電気解剖学的エンドポイントを確立します。病変の耐久性、不整脈の再発、臨床上の利益の増加についてはさらなる研究が必要です。</t>
+    <t>はじめに: 肺静脈隔離は依然として心房細動 (AF) アブレーションの中心ですが、右心房基質の修正は不完全に定義されたままです。  終端クリスタ（CT）領域は右横隔神経の近くに位置し、異方性伝導および自然または機能的伝導ブロックを示す可能性があると同時に、潜在的な非肺静脈トリガー部位としても機能します。  われわれは、格子先端パルスフィールドアブレーション（PFA）で作成されたCTガイド下洞房結節（SN）温存病変セットであるクリスタ大静脈ライン（CCL）の急性実現可能性と電気解剖学的エンドポイントを評価した。  方法と結果：我々は、反復性心房細動アブレーションまたは非発作性心房細動に対するアブレーション中にCCL作成を受ける連続36人の患者を前向きに登録した。 CCL前の洞調律高密度右心房活性化マッピングがすべての患者で実行されました。  CT 関連の伝導遅延またはブロックが 27 人の患者 (75.0%) で観察されました。  明らかな CT ブロック ラインを持つ 14 人の患者 (38.9%) では、下側のアプリケーション セットのエッジがブロック ラインと一致していました。明らかなブロックのない残りの 22 人の患者では、留置は主に心臓内心エコー検査によって行われました。  CCL は CT の後方に配置され、その上適用セットの側縁は SN 保護のために最も早くマッピングされた副鼻腔活性化部位の後外側約 15 mm に保たれました。  CCL の最初のタグから最後のタグまでの距離は 78.8 [66.4-86.0] mm で、370 [282-481] 秒間で 26 [22-30] PFA の塗布が必要でした。 初回通過の双方向横伝導ブロックは、切除後の活性化マッピングと CCL の両側からの差動ペーシングによってすべての患者で確認されました。  翌日の吸気/呼気胸部X線撮影では、横隔神経麻痺を示唆する異常は示されませんでした。ペースメーカを必要とするSN機能障害やその他の臨床的に明らかな付随的損傷は発生しませんでした。  結論： CT ガイド下、SN 温存 CCL は格子先端 PFA を用いて再現性よく作製でき、臨床的に明らかな横隔神経麻痺を伴わずに初回通過双方向横伝導ブロックを生成する。  これらの発見は、確実な実現可能性と電気解剖学的エンドポイントを確立します。病変の耐久性、不整脈の再発、臨床上の利益の増加についてはさらなる研究が必要です。</t>
   </si>
   <si>
     <t xml:space="preserve">INTRODUCTION:
@@ -2206,7 +2206,7 @@
     <t>ℹ️ 論文本文 (Full Text) や図表の全ページ閲覧は、上記の PubMed URL (https://pubmed.ncbi.nlm.nih.gov/42801690/) または DOI リンク先の出版社公式サイトからアクセスできます。</t>
   </si>
   <si>
-    <t xml:space="preserve">📄 [No.10] 心心心房細動に対する高周波アブレーションと比較したパルス場による脳卒中およびTIAのリスク
+    <t xml:space="preserve">📄 [No.10] 心房細動に対する高周波アブレーションと比較したパルス場による脳卒中およびTIAのリスク
 (Risk of Stroke and TIA With Pulsed Field Compared With Radiofrequency Ablation for Atrial Fibrillation.)</t>
   </si>
   <si>
@@ -2222,7 +2222,7 @@
     <t>10.1161/CIRCULATIONAHA.126.081092 doi</t>
   </si>
   <si>
-    <t>背景: 心心房細動のパルスフィールドアブレーション (PFA) は、熱アブレーションと比較した安全性への期待もあり、急速に採用されてきました。  2 つのモダリティ間の安全性の比較データは依然として限られています。  方法：我々は、2022年から2026年にかけて米国の大規模学術センターで連続心心房細動アブレーションを分析する前向きレジストリを実施した。主要エンドポイントは30日以内の脳卒中または一過性虚血発作（TIA）であり、盲検神経内科医が独自に判定した。  二次エンドポイントには、死亡およびその他の処置上の合併症が含まれていました。  患者特性の違いのバランスを取るために、治療加重の逆確率を使用した傾向スコア法が使用されました。 PFA と高周波アブレーション (RFA) の手順ワークフローの違いは、探索的媒介分析で評価されました。  結果: 合計 4,221 件のアブレーション処置 (RFA 2,077 件、PFA 2,144 件: ファラウェーブ 68.7%、スフィア 9 23.3%、バリパルス 6.9%、パルスセレクト 0.7%) が 12 人の術者によって実施されました。  PFA と RFA を受けている患者は同様のベースライン特性 (平均年齢 67 歳、女性 31%、持続性心心房細動 47%、脳卒中/TIA の既往歴 7%) を有しており、逆確率で治療加重を行った後にバランスが取れていました。  RFA と比較して、PFA 手順は短く (108 分対 144 分)、より頻繁な後壁分離が含まれていました (57% 対 31%)。 30日脳卒中/TIA発生率は、非加重分析および傾向スコア加重分析の両方において、RFA（2件; 0.10％）と比較してPFA症例（10件; 0.47％）の方が有意に高かった（加重リスク差、0.36％[95％CI、0.03％-0.70％]; =0.03）。  脳卒中/TIAイベントは研究期間を通じて均等に分布しており、PFA導入時またはオペレーターの前後で集中することはありませんでした（2つ以上のイベントに関連するオペレーターはいませんでした）。  探索的仲介モデルはイベント発生率が低いために制限されており、より広範なアブレーションを脳卒中の独立した危険因子として特定していませんでした。  他の手術合併症の加重率は低く (&lt;1%)、PFA 群と RFA 群間で同様でした。 結論: 臨床粒度が高く、患者を体系的に追跡調査する大量の単一センター登録では、PFA は RFA と比較して 30 日時点で脳卒中/TIA のリスクが有意に高かった。  これらの結果は、PFA 手続きの量が指数関数的に増加し続ける中、強化された市販後調査と専用の前向き評価を必要とします。</t>
+    <t>背景: 心房細動のパルスフィールドアブレーション (PFA) は、熱アブレーションと比較した安全性への期待もあり、急速に採用されてきました。  2 つのモダリティ間の安全性の比較データは依然として限られています。  方法：我々は、2022年から2026年にかけて米国の大規模学術センターで連続心房細動アブレーションを分析する前向きレジストリを実施した。主要エンドポイントは30日以内の脳卒中または一過性虚血発作（TIA）であり、盲検神経内科医が独自に判定した。  二次エンドポイントには、死亡およびその他の処置上の合併症が含まれていました。  患者特性の違いのバランスを取るために、治療加重の逆確率を使用した傾向スコア法が使用されました。 PFA と高周波アブレーション (RFA) の手順ワークフローの違いは、探索的媒介分析で評価されました。  結果: 合計 4,221 件のアブレーション処置 (RFA 2,077 件、PFA 2,144 件: ファラウェーブ 68.7%、スフィア 9 23.3%、バリパルス 6.9%、パルスセレクト 0.7%) が 12 人の術者によって実施されました。  PFA と RFA を受けている患者は同様のベースライン特性 (平均年齢 67 歳、女性 31%、持続性心房細動 47%、脳卒中/TIA の既往歴 7%) を有しており、逆確率で治療加重を行った後にバランスが取れていました。  RFA と比較して、PFA 手順は短く (108 分対 144 分)、より頻繁な後壁分離が含まれていました (57% 対 31%)。 30日脳卒中/TIA発生率は、非加重分析および傾向スコア加重分析の両方において、RFA（2件; 0.10％）と比較してPFA症例（10件; 0.47％）の方が有意に高かった（加重リスク差、0.36％[95％CI、0.03％-0.70％]; =0.03）。  脳卒中/TIAイベントは研究期間を通じて均等に分布しており、PFA導入時またはオペレーターの前後で集中することはありませんでした（2つ以上のイベントに関連するオペレーターはいませんでした）。  探索的仲介モデルはイベント発生率が低いために制限されており、より広範なアブレーションを脳卒中の独立した危険因子として特定していませんでした。  他の手術合併症の加重率は低く (&lt;1%)、PFA 群と RFA 群間で同様でした。 結論: 臨床粒度が高く、患者を体系的に追跡調査する大量の単一センター登録では、PFA は RFA と比較して 30 日時点で脳卒中/TIA のリスクが有意に高かった。  これらの結果は、PFA 手続きの量が指数関数的に増加し続ける中、強化された市販後調査と専用の前向き評価を必要とします。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -2267,7 +2267,7 @@
     <t>ℹ️ 論文本文 (Full Text) や図表の全ページ閲覧は、上記の PubMed URL (https://pubmed.ncbi.nlm.nih.gov/42732578/) または DOI リンク先の出版社公式サイトからアクセスできます。</t>
   </si>
   <si>
-    <t xml:space="preserve">📄 [No.12] パルスフィールドアブレーションは心心心房細動アブレーション後の良好な転帰と関連している: ポーランド国立アブレーション登録簿 (POL-AR) からの洞察
+    <t xml:space="preserve">📄 [No.12] パルスフィールドアブレーションは心房細動アブレーション後の良好な転帰と関連している: ポーランド国立アブレーション登録簿 (POL-AR) からの洞察
 (Pulsed Field Ablation Is Associated With Favorable Outcomes After Atrial Fibrillation Ablation: Insights From the Polish National Ablation Registry (POL-AR).)</t>
   </si>
   <si>
@@ -2280,7 +2280,7 @@
     <t>10.1111/jce.70514 doi</t>
   </si>
   <si>
-    <t>背景: ポーランド国立アブレーションレジストリ (POL-AR) は、カテーテルアブレーションを実施するすべての施設に必須であり、国民健康基金のデータと統合されており、連続するすべての患者を完全に含めた全国コホートの前向き分析を可能にします。  目的: 私たちは、高周波 (RF)、クライオバルーン (CRYO)、パルスフィールド アブレーション (PFA) などの心心房細動 (AF) アブレーション療法の実際の安全性プロファイルと臨床転帰を評価し、ポーランドでの初年度の PFA 経験を報告することを目的としました。  方法: 2023 年のすべての AF アブレーションは、POL-AR で前向きに分析され、国民健康基金のデータと相互参照されました。  完全な報告を行ったセンターのみが含まれていました。  患者はモダリティごとにグループ化されました。 重大な合併症、計画外の入院、電気的除細動、反復アブレーション、および死亡は1年後に評価されました。  多変量解析により、結果の独立した予測因子が特定されました。  結果: 28 の施設から 3,430 人の患者が報告された (CRYO: 2,125; RF: 1,098; PFA: 207)。  処置時間は、CRYO (75 分) および PFA (65 分) に対して、RF (中央値 120 分) が最長でした。 (p &lt; 0.001)。  PFA では重大な合併症は発生しませんでした。  横隔神経損傷は、CRYO 患者の 1.51%、RF 患者の 0.09%、PFA 患者の 0% で持続しました (p &lt; 0.001)。  心膜液貯留は、RF 後により頻繁に発生しました (CRYO + PFA では 0.91% 対 0.34%; p = 0.032)。  全体的な合併症率は PFA が最も低かった (0% 対 RF: 2.19%、CRYO: 2.59%)。  PFA 患者では、追跡調査中に必要な電気的ディオバージョンが少なくなりました (p = 0.017)。 不良転帰の予測因子には、年齢、女性の性別、左心房 (LA) サイズ、高血圧、肥大型心筋症 (HCM) が含まれていました。  良好な転帰は、左室駆出率（LVEF）の上昇、発作性AF、およびPFAの使用と独立して関連していた（HR 0.70、p = 0.04）。  結論: POL-AR レジストリでは、PFA は独立して AF アブレーション後の良好な転帰と関連していました。</t>
+    <t>背景: ポーランド国立アブレーションレジストリ (POL-AR) は、カテーテルアブレーションを実施するすべての施設に必須であり、国民健康基金のデータと統合されており、連続するすべての患者を完全に含めた全国コホートの前向き分析を可能にします。  目的: 私たちは、高周波 (RF)、クライオバルーン (CRYO)、パルスフィールド アブレーション (PFA) などの心房細動 (AF) アブレーション療法の実際の安全性プロファイルと臨床転帰を評価し、ポーランドでの初年度の PFA 経験を報告することを目的としました。  方法: 2023 年のすべての AF アブレーションは、POL-AR で前向きに分析され、国民健康基金のデータと相互参照されました。  完全な報告を行ったセンターのみが含まれていました。  患者はモダリティごとにグループ化されました。 重大な合併症、計画外の入院、電気的除細動、反復アブレーション、および死亡は1年後に評価されました。  多変量解析により、結果の独立した予測因子が特定されました。  結果: 28 の施設から 3,430 人の患者が報告された (CRYO: 2,125; RF: 1,098; PFA: 207)。  処置時間は、CRYO (75 分) および PFA (65 分) に対して、RF (中央値 120 分) が最長でした。 (p &lt; 0.001)。  PFA では重大な合併症は発生しませんでした。  横隔神経損傷は、CRYO 患者の 1.51%、RF 患者の 0.09%、PFA 患者の 0% で持続しました (p &lt; 0.001)。  心膜液貯留は、RF 後により頻繁に発生しました (CRYO + PFA では 0.91% 対 0.34%; p = 0.032)。  全体的な合併症率は PFA が最も低かった (0% 対 RF: 2.19%、CRYO: 2.59%)。  PFA 患者では、追跡調査中に必要な電気的ディオバージョンが少なくなりました (p = 0.017)。 不良転帰の予測因子には、年齢、女性の性別、左心房 (LA) サイズ、高血圧、肥大型心筋症 (HCM) が含まれていました。  良好な転帰は、左室駆出率（LVEF）の上昇、発作性AF、およびPFAの使用と独立して関連していた（HR 0.70、p = 0.04）。  結論: POL-AR レジストリでは、PFA は独立して AF アブレーション後の良好な転帰と関連していました。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -2298,7 +2298,7 @@
     <t>ℹ️ 論文本文 (Full Text) や図表の全ページ閲覧は、上記の PubMed URL (https://pubmed.ncbi.nlm.nih.gov/42801701/) または DOI リンク先の出版社公式サイトからアクセスできます。</t>
   </si>
   <si>
-    <t xml:space="preserve">📄 [No.13] 心心心房細動で肺静脈隔離を受けた高齢患者の臨床的脆弱性がリズム関連の転帰を改善する:観察コホート研究
+    <t xml:space="preserve">📄 [No.13] 心房細動で肺静脈隔離を受けた高齢患者の臨床的脆弱性がリズム関連の転帰を改善する:観察コホート研究
 (Clinical Vulnerability Refines Rhythm-Related Outcomes in Older Patients Undergoing Pulmonary Vein Isolation for Atrial Fibrillation: An Observational Cohort Study.)</t>
   </si>
   <si>
@@ -2314,7 +2314,7 @@
     <t>10.1002/joa3.70461 doi</t>
   </si>
   <si>
-    <t>はじめに: 心心房細動 (AF) アブレーションの患者を選択する際には、暦年齢が考慮されることがよくありますが、年齢だけでは、どの高齢患者が肺静脈隔離 (PVI) 後に再発性リズム関連ケアを必要とする可能性が最も高いかを特定できない場合があります。  方法: PVI を受けている連続患者を対象とした単一施設の観察研究を実施しました。  主要登録コホートは、同センター再発関連リズム介入エンドポイント（指標後最初の反復 PVI または電気的電気的除細動として定義）を評価しました。  ネストされたアクティブな 2022 コホートは、より広範にアクティブに確認された再発を評価しました。  年齢は、50 歳未満、50 ～ 74 歳、75 歳以上として分析されました。 探索的な高齢者の脆弱性スコアでは、記録された持続性心心房細動、心不全、慢性腎臓病、弁膜症/手術に対してそれぞれ 1 点が割り当てられました。  結果: 登録コホートには 2,559 人の患者と 580 件の同一施設のリズム介入イベントが含まれていました。  イベント発生率は年齢グループ全体で増加しました: 50歳未満の患者で14.2%、50～74歳の患者で20.8%、75歳以上の患者で29.8%。調整されたレジストリCox分析では、年齢75歳以上は独立して50～74歳と比較してより高いリスクと関連していました、HR: 1.35、95% CI: 1.12-1.64、= 0.002、90日間のブランキング後、HR: 1.37、95% CI: 1.12-1.69、= 0.002、アクティブコホートでは、HR: 1.46、95% CI: 1.01-2.11、= 0.042。 高齢者スコア 0 の患者は、レジストリ分析、aHR: 1.13、95% CI: 0.79-1.63、= 0.5、またはアクティブ分析、aHR: 1.01、95% CI: 0.49-2.09、= 0.975 では 50 ～ 74 歳の患者と有意な差はありませんでしたが、スコア ≥ 2 では、両方のレジストリでより高いイベント負荷が特定されました。コホート、aHR: 1.85、95% CI: 1.45-2.35、&lt; 0.001、およびアクティブコホート、aHR: 1.95、95% CI: 1.23-3.12、= 0.005。  結論： 75 歳以上では、PVI 後の同センター再発関連リズム介入の割合が高かったが、リスクは大幅に変動した。  実年齢のみではなく、臨床的脆弱性を考慮したほうが、高齢患者のカウンセリングや選択に役立つ可能性があります。</t>
+    <t>はじめに: 心房細動 (AF) アブレーションの患者を選択する際には、暦年齢が考慮されることがよくありますが、年齢だけでは、どの高齢患者が肺静脈隔離 (PVI) 後に再発性リズム関連ケアを必要とする可能性が最も高いかを特定できない場合があります。  方法: PVI を受けている連続患者を対象とした単一施設の観察研究を実施しました。  主要登録コホートは、同センター再発関連リズム介入エンドポイント（指標後最初の反復 PVI または電気的電気的除細動として定義）を評価しました。  ネストされたアクティブな 2022 コホートは、より広範にアクティブに確認された再発を評価しました。  年齢は、50 歳未満、50 ～ 74 歳、75 歳以上として分析されました。 探索的な高齢者の脆弱性スコアでは、記録された持続性心房細動、心不全、慢性腎臓病、弁膜症/手術に対してそれぞれ 1 点が割り当てられました。  結果: 登録コホートには 2,559 人の患者と 580 件の同一施設のリズム介入イベントが含まれていました。  イベント発生率は年齢グループ全体で増加しました: 50歳未満の患者で14.2%、50～74歳の患者で20.8%、75歳以上の患者で29.8%。調整されたレジストリCox分析では、年齢75歳以上は独立して50～74歳と比較してより高いリスクと関連していました、HR: 1.35、95% CI: 1.12-1.64、= 0.002、90日間のブランキング後、HR: 1.37、95% CI: 1.12-1.69、= 0.002、アクティブコホートでは、HR: 1.46、95% CI: 1.01-2.11、= 0.042。 高齢者スコア 0 の患者は、レジストリ分析、aHR: 1.13、95% CI: 0.79-1.63、= 0.5、またはアクティブ分析、aHR: 1.01、95% CI: 0.49-2.09、= 0.975 では 50 ～ 74 歳の患者と有意な差はありませんでしたが、スコア ≥ 2 では、両方のレジストリでより高いイベント負荷が特定されました。コホート、aHR: 1.85、95% CI: 1.45-2.35、&lt; 0.001、およびアクティブコホート、aHR: 1.95、95% CI: 1.23-3.12、= 0.005。  結論： 75 歳以上では、PVI 後の同センター再発関連リズム介入の割合が高かったが、リスクは大幅に変動した。  実年齢のみではなく、臨床的脆弱性を考慮したほうが、高齢患者のカウンセリングや選択に役立つ可能性があります。</t>
   </si>
   <si>
     <t xml:space="preserve">INTRODUCTION:
@@ -2391,7 +2391,7 @@
     <t>ℹ️ 論文本文 (Full Text) や図表の全ページ閲覧は、上記の PubMed URL (https://pubmed.ncbi.nlm.nih.gov/42670977/) または DOI リンク先の出版社公式サイトからアクセスできます。</t>
   </si>
   <si>
-    <t xml:space="preserve">📄 [No.16] 心心心房細動アブレーション後の不整脈再発のマーカーとしてのヘモグロビンレベル
+    <t xml:space="preserve">📄 [No.16] 心房細動アブレーション後の不整脈再発のマーカーとしてのヘモグロビンレベル
 (Hemoglobin Levels as a Marker of Arrhythmia Recurrence After Atrial Fibrillation Ablation.)</t>
   </si>
   <si>
@@ -2407,7 +2407,7 @@
     <t>10.1002/joa3.70473 doi</t>
   </si>
   <si>
-    <t>背景: ヘモグロビン (Hb) の低下は、血行動態ストレスや有害な心臓リモデリングと関連しています。  しかし、心心房細動 (AF) アブレーション後の不整脈再発に対する臨床的意義は依然として不明です。  方法：2014年から2024年の間にAFアブレーションを受けた2202人の患者を遡及的に研究した（高周波アブレーション[RFA]：= 1606人、クライオバルーンアブレーション[CBA]：= 596人）。  RFA コホートでは、患者は Hb 四分位ごとに階層化され、最も低い四分位カットオフ (Hb &lt; 12.4 g/dL) が CBA コホートに適用されました。  主要評価項目は、90 日間のブランク期間を超えた AF または心房頻脈の再発でした。 結果：RFAコホートでは、低Hbはインデックス手術後（調整HR 1.33、95％CI 1.07～1.65）および複数の手術後（調整HR 1.57、95％CI 1.22～2.02）の不整脈再発リスクの上昇と関連していた。  CBAコホートでは有意な関連性は観察されなかった（調整後HR 1.03、95％CI 0.68～1.54）。  Hb レベルとアブレーション モダリティの間の相互作用は統計的に有意ではありませんでした (相互作用 = 0.177)。  統合解析では、低Hbは全集団（調整HR 1.24、95% CI 1.03-1.50）および非発作性AF患者（調整HR 1.43、95% CI 1.11-1.85）では独立して不整脈再発と関連したが、発作性AF患者（調整HR 1.06、95%）では関連しなかった。 CI 0.80-1.39）。 結論: Hb レベルの低下は、不整脈再発リスクの増加と関連していました。  この関連性はAFのタイプによって異なり、低Hbは処置による影響ではなく心房基質の悪影響を反映している可能性があることを示唆している。</t>
+    <t>背景: ヘモグロビン (Hb) の低下は、血行動態ストレスや有害な心臓リモデリングと関連しています。  しかし、心房細動 (AF) アブレーション後の不整脈再発に対する臨床的意義は依然として不明です。  方法：2014年から2024年の間にAFアブレーションを受けた2202人の患者を遡及的に研究した（高周波アブレーション[RFA]：= 1606人、クライオバルーンアブレーション[CBA]：= 596人）。  RFA コホートでは、患者は Hb 四分位ごとに階層化され、最も低い四分位カットオフ (Hb &lt; 12.4 g/dL) が CBA コホートに適用されました。  主要評価項目は、90 日間のブランク期間を超えた AF または心房頻脈の再発でした。 結果：RFAコホートでは、低Hbはインデックス手術後（調整HR 1.33、95％CI 1.07～1.65）および複数の手術後（調整HR 1.57、95％CI 1.22～2.02）の不整脈再発リスクの上昇と関連していた。  CBAコホートでは有意な関連性は観察されなかった（調整後HR 1.03、95％CI 0.68～1.54）。  Hb レベルとアブレーション モダリティの間の相互作用は統計的に有意ではありませんでした (相互作用 = 0.177)。  統合解析では、低Hbは全集団（調整HR 1.24、95% CI 1.03-1.50）および非発作性AF患者（調整HR 1.43、95% CI 1.11-1.85）では独立して不整脈再発と関連したが、発作性AF患者（調整HR 1.06、95%）では関連しなかった。 CI 0.80-1.39）。 結論: Hb レベルの低下は、不整脈再発リスクの増加と関連していました。  この関連性はAFのタイプによって異なり、低Hbは処置による影響ではなく心房基質の悪影響を反映している可能性があることを示唆している。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -2423,7 +2423,7 @@
     <t>ℹ️ 論文本文 (Full Text) や図表の全ページ閲覧は、上記の PubMed URL (https://pubmed.ncbi.nlm.nih.gov/42774855/) または DOI リンク先の出版社公式サイトからアクセスできます。</t>
   </si>
   <si>
-    <t xml:space="preserve">📄 [No.17] 心心心房細動に対するパルスフィールドアブレーション中の 3 つの異なる鎮静戦略を使用した安全性と結果の比較
+    <t xml:space="preserve">📄 [No.17] 心房細動に対するパルスフィールドアブレーション中の 3 つの異なる鎮静戦略を使用した安全性と結果の比較
 (A Comparison of Safety and Outcome Using Three Different Sedation Strategies During Pulsed Field Ablation for Atrial Fibrillation.)</t>
   </si>
   <si>
@@ -2436,7 +2436,7 @@
     <t>10.1111/jce.70516 doi</t>
   </si>
   <si>
-    <t>背景: パルスフィールドアブレーション (PFA) は、心心房細動 (AF) アブレーションのための新たなモダリティです。  ただし、治療中の患者の適切な鎮静は不可欠です。  目的：私たちの目的は、PFA AF アブレーション中の電気生理学スタッフによる深い鎮静（DS）（EP-DS）、麻酔看護師による DS（AN-DS）、および全身麻酔（GA）後の安全性と転帰を比較することでした。  方法：2021年から2024年にペンタスプリンPFA技術による初めての心心房細動アブレーションを受けたデンマーク人患者全員が対象となった。  患者は鎮静戦略に従って層別化されました。  EP-DS と AN-DS は、それぞれ EP スタッフと麻酔看護師によって管理される補助換気なしの鎮静と定義されました。  GA の患者は気管内挿管を受け、麻酔スタッフによって監視されました。 鎮静戦略に対する患者の選択は、施設内の慣行に基づいて行われました。  結果: 1,269 人の患者のうち、661 人 (52%) が EP-DS を受け、173 人 (14%) が AN-DS を受け、435 人 (34%) が GA を受けました。  全体として、鎮静による合併症はほとんどなく、鎮静の悪影響により処置が中止されることはありませんでした。  EP-DS グループでは、1 人 (0.2%) の患者で、処置中に低血圧が続いたため、予期せず麻酔科医がバックアップを求められました。  AN-DS グループでは、1 人の患者 (0.6%) が飽和度低下のために麻酔科医を呼びましたが、挿管へのエスカレーションは必要ありませんでした。  GA グループでは、手術周囲の鎮静による合併症は発生しませんでした。  鎮静群間で 1 年心房頻脈再発率に差は見られませんでした。 結論：この全国コホートでは、EP スタッフによる深い鎮静は実行可能であり、PFA 中に臨床的に重大な鎮静関連の有害事象はほとんど発生しませんでした。  観察された心房性頻脈性不整脈の再発率には、鎮静戦略間で有意な差は確認されませんでした。</t>
+    <t>背景: パルスフィールドアブレーション (PFA) は、心房細動 (AF) アブレーションのための新たなモダリティです。  ただし、治療中の患者の適切な鎮静は不可欠です。  目的：私たちの目的は、PFA AF アブレーション中の電気生理学スタッフによる深い鎮静（DS）（EP-DS）、麻酔看護師による DS（AN-DS）、および全身麻酔（GA）後の安全性と転帰を比較することでした。  方法：2021年から2024年にペンタスプリンPFA技術による初めての心房細動アブレーションを受けたデンマーク人患者全員が対象となった。  患者は鎮静戦略に従って層別化されました。  EP-DS と AN-DS は、それぞれ EP スタッフと麻酔看護師によって管理される補助換気なしの鎮静と定義されました。  GA の患者は気管内挿管を受け、麻酔スタッフによって監視されました。 鎮静戦略に対する患者の選択は、施設内の慣行に基づいて行われました。  結果: 1,269 人の患者のうち、661 人 (52%) が EP-DS を受け、173 人 (14%) が AN-DS を受け、435 人 (34%) が GA を受けました。  全体として、鎮静による合併症はほとんどなく、鎮静の悪影響により処置が中止されることはありませんでした。  EP-DS グループでは、1 人 (0.2%) の患者で、処置中に低血圧が続いたため、予期せず麻酔科医がバックアップを求められました。  AN-DS グループでは、1 人の患者 (0.6%) が飽和度低下のために麻酔科医を呼びましたが、挿管へのエスカレーションは必要ありませんでした。  GA グループでは、手術周囲の鎮静による合併症は発生しませんでした。  鎮静群間で 1 年心房頻脈再発率に差は見られませんでした。 結論：この全国コホートでは、EP スタッフによる深い鎮静は実行可能であり、PFA 中に臨床的に重大な鎮静関連の有害事象はほとんど発生しませんでした。  観察された心房性頻脈性不整脈の再発率には、鎮静戦略間で有意な差は確認されませんでした。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -2515,7 +2515,7 @@
     <t>ℹ️ 論文本文 (Full Text) や図表の全ページ閲覧は、上記の PubMed URL (https://pubmed.ncbi.nlm.nih.gov/42663127/) または DOI リンク先の出版社公式サイトからアクセスできます。</t>
   </si>
   <si>
-    <t xml:space="preserve">📄 [No.20] 心心心房細動に対する高周波アブレーション中の食道保護冷却後の胸痛と胃食道逆流症の参加者報告 - EVERCOOL-AF 研究
+    <t xml:space="preserve">📄 [No.20] 心房細動に対する高周波アブレーション中の食道保護冷却後の胸痛と胃食道逆流症の参加者報告 - EVERCOOL-AF 研究
 (Participant-reported chest pain and gastric esophageal reflux disease following protective esophageal cooling during radiofrequency ablation for atrial fibrillation - the EVERCOOL-AF study.)</t>
   </si>
   <si>
@@ -2528,7 +2528,7 @@
     <t>10.1007/s10840-026-02437-0 doi</t>
   </si>
   <si>
-    <t>背景: 胃食道逆流症（GERD）と胸痛は、心心房細動（AF）に対するカテーテルアブレーション後の一般的な合併症であり、多くの場合、食道の熱損傷が原因であると考えられています。  積極的な食道冷却は熱損傷のリスクを軽減しますが、胃食道逆流症の症状は軽減しない可能性があります。  食道の冷却にもかかわらず、これらの合併症に関連する要因は不明のままです。  私たちの目的は、食道冷却を伴う高周波アブレーション (RFA) を受けている AF 参加者におけるアブレーション後 GERD および (CP) に関連する参加者および手順の特徴を特定することでした。  方法: 発作性または持続性 AF に対して食道冷却を伴う RFA を受けている参加者は、標準化されたアンケートに回答しました。 GERD の症状は、手順の 7 ～ 14 日後に GERDQ (スコア ≥ 8 の GERD の高確率) で評価されました。  胸痛については別に質問した。  人口動態変数と手続き変数との関連性が評価されました。  結果：食道冷却を受けたアブレーション後のアンケートに回答した最大参加者312名のうち295名が食道冷却を受け、44名（14.9％）がGERD≧8の基準を満たし、71名（24.1％）がCPを報告した。  前部最大出力は、胃食道逆流症のある参加者では、そうでない参加者と比較して有意に低かった（50.0 vs. 54.0 ± 14.0 W、p = 0.020）。  CPを報告した参加者は若く（64.5±9.3歳対67.5±10.2歳、p=0.026）、平均駆出率が高かった（57.1±6.6％対53.1±10.2％、p=0.001）。 両側の初回通過分離が達成された場合、胸痛はあまり発生しませんでした (59.2% vs. 72.6%、p = 0.033)。  結論：積極的な食道冷却を伴うAFアブレーションを受けた参加者では、年齢が若く、駆出率が高く、両側初回通過隔離の欠如がアブレーション後のCPと関連していた。  これらの所見は、食道の保護にもかかわらず、手順と参加者固有の両方の要因が症状の発症に寄与している可能性があることを示唆しています。</t>
+    <t>背景: 胃食道逆流症（GERD）と胸痛は、心房細動（AF）に対するカテーテルアブレーション後の一般的な合併症であり、多くの場合、食道の熱損傷が原因であると考えられています。  積極的な食道冷却は熱損傷のリスクを軽減しますが、胃食道逆流症の症状は軽減しない可能性があります。  食道の冷却にもかかわらず、これらの合併症に関連する要因は不明のままです。  私たちの目的は、食道冷却を伴う高周波アブレーション (RFA) を受けている AF 参加者におけるアブレーション後 GERD および (CP) に関連する参加者および手順の特徴を特定することでした。  方法: 発作性または持続性 AF に対して食道冷却を伴う RFA を受けている参加者は、標準化されたアンケートに回答しました。 GERD の症状は、手順の 7 ～ 14 日後に GERDQ (スコア ≥ 8 の GERD の高確率) で評価されました。  胸痛については別に質問した。  人口動態変数と手続き変数との関連性が評価されました。  結果：食道冷却を受けたアブレーション後のアンケートに回答した最大参加者312名のうち295名が食道冷却を受け、44名（14.9％）がGERD≧8の基準を満たし、71名（24.1％）がCPを報告した。  前部最大出力は、胃食道逆流症のある参加者では、そうでない参加者と比較して有意に低かった（50.0 vs. 54.0 ± 14.0 W、p = 0.020）。  CPを報告した参加者は若く（64.5±9.3歳対67.5±10.2歳、p=0.026）、平均駆出率が高かった（57.1±6.6％対53.1±10.2％、p=0.001）。 両側の初回通過分離が達成された場合、胸痛はあまり発生しませんでした (59.2% vs. 72.6%、p = 0.033)。  結論：積極的な食道冷却を伴うAFアブレーションを受けた参加者では、年齢が若く、駆出率が高く、両側初回通過隔離の欠如がアブレーション後のCPと関連していた。  これらの所見は、食道の保護にもかかわらず、手順と参加者固有の両方の要因が症状の発症に寄与している可能性があることを示唆しています。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -2576,7 +2576,7 @@
     <t>ℹ️ 論文本文 (Full Text) や図表の全ページ閲覧は、上記の PubMed URL (https://pubmed.ncbi.nlm.nih.gov/42824794/) または DOI リンク先の出版社公式サイトからアクセスできます。</t>
   </si>
   <si>
-    <t xml:space="preserve">📄 [No.22] 心心心房細動を伴う高出血リスク患者における経皮的左心耳閉塞後の左心房アブレーションの安全性と有効性: PROCEED-AF アブレーション レジストリからの多施設解析
+    <t xml:space="preserve">📄 [No.22] 心房細動を伴う高出血リスク患者における経皮的左心耳閉塞後の左心房アブレーションの安全性と有効性: PROCEED-AF アブレーション レジストリからの多施設解析
 (Safety and Efficacy of Left Atrial Ablation After Percutaneous Left Atrial Appendage Occlusion in High-Bleeding-Risk Patients with Atrial Fibrillation: A Multicenter Analysis from the PROCEED-AF Ablation Registry.)</t>
   </si>
   <si>
@@ -2592,7 +2592,7 @@
     <t>10.1093/europace/euag277 doi</t>
   </si>
   <si>
-    <t>背景と目的: 左心耳 (LAAO) デバイスを装着した患者が AF アブレーションを受診することが増えていますが、抗凝固戦略は依然として不確実です。  この研究の目的は、既存の LAAO デバイスを装着した患者における心心房細動 (AF) に対するカテーテル アブレーションの安全性と有効性を評価し、このユニークな集団におけるアブレーション後の抗凝固管理のパターンを説明することでした。  方法: 私たちは、以前に LAAO デバイスを使用して AF アブレーションを受けた患者に関するデータを世界中の 14 のセンターから収集しました。  各サイトでは、臨床的特徴、手順の詳細、合併症と不整脈の転帰に関する情報を提供しました。  データは集約され、管理戦略における手順の安全性、有効性、変動性を評価するために一元的に分析されました。 結果：以前にLAAOを患った合計198人の患者（年齢70歳、女性37％、発作性AF42％）が含まれた。  アブレーションは、LAAO 後中央値 271 日に実施されました。  アブレーション後、患者の 84% が経口抗凝固療法 (OAC) を受けており、最も一般的な期間は 2 ～ 3 か月間でした。  OAC による出血合併症は、アブレーション後中央値 20 (13、70) 日で患者の 6.7% に発生しました。  追跡期間中に脳卒中またはTIAが5人の患者(症例の2.6%)で発生し、アブレーション翌日に2件(症例の1%)が発生した。  アブレーション後にデバイス周囲のリークが新たに発生した、または悪化したケースが 2 件ありました。 結論：既存の LAAO デバイスを使用して心心房細動に対するカテーテルアブレーションを受けている患者の大規模な国際登録では、アブレーションは実行可能であり、デバイス関連の合併症はまれでした。LAAO 集団では出血リスクが高いにもかかわらず、以前 LAAO を患っていた患者の 84% が、この集団で予想される割合で出血イベントを伴うアブレーション後の短期間の OAC に耐えました。</t>
+    <t>背景と目的: 左心耳 (LAAO) デバイスを装着した患者が AF アブレーションを受診することが増えていますが、抗凝固戦略は依然として不確実です。  この研究の目的は、既存の LAAO デバイスを装着した患者における心房細動 (AF) に対するカテーテル アブレーションの安全性と有効性を評価し、このユニークな集団におけるアブレーション後の抗凝固管理のパターンを説明することでした。  方法: 私たちは、以前に LAAO デバイスを使用して AF アブレーションを受けた患者に関するデータを世界中の 14 のセンターから収集しました。  各サイトでは、臨床的特徴、手順の詳細、合併症と不整脈の転帰に関する情報を提供しました。  データは集約され、管理戦略における手順の安全性、有効性、変動性を評価するために一元的に分析されました。 結果：以前にLAAOを患った合計198人の患者（年齢70歳、女性37％、発作性AF42％）が含まれた。  アブレーションは、LAAO 後中央値 271 日に実施されました。  アブレーション後、患者の 84% が経口抗凝固療法 (OAC) を受けており、最も一般的な期間は 2 ～ 3 か月間でした。  OAC による出血合併症は、アブレーション後中央値 20 (13、70) 日で患者の 6.7% に発生しました。  追跡期間中に脳卒中またはTIAが5人の患者(症例の2.6%)で発生し、アブレーション翌日に2件(症例の1%)が発生した。  アブレーション後にデバイス周囲のリークが新たに発生した、または悪化したケースが 2 件ありました。 結論：既存の LAAO デバイスを使用して心房細動に対するカテーテルアブレーションを受けている患者の大規模な国際登録では、アブレーションは実行可能であり、デバイス関連の合併症はまれでした。LAAO 集団では出血リスクが高いにもかかわらず、以前 LAAO を患っていた患者の 84% が、この集団で予想される割合で出血イベントを伴うアブレーション後の短期間の OAC に耐えました。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND AND AIMS:
@@ -2608,7 +2608,7 @@
     <t>ℹ️ 論文本文 (Full Text) や図表の全ページ閲覧は、上記の PubMed URL (https://pubmed.ncbi.nlm.nih.gov/42786895/) または DOI リンク先の出版社公式サイトからアクセスできます。</t>
   </si>
   <si>
-    <t xml:space="preserve">📄 [No.23] 非肺静脈ドライバーに基づく持続性心心心房細動におけるアブレーション結果の仮想心臓ベースの予測
+    <t xml:space="preserve">📄 [No.23] 非肺静脈ドライバーに基づく持続性心房細動におけるアブレーション結果の仮想心臓ベースの予測
 (Virtual Heart-Based Prediction of Ablation Outcomes in Persistent Atrial Fibrillation Based on Non-Pulmonary Vein Drivers.)</t>
   </si>
   <si>
@@ -2624,7 +2624,7 @@
     <t>10.1161/CIRCEP.125.014266 doi</t>
   </si>
   <si>
-    <t>背景: 持続性心心房細動 (AF) におけるドライバーを対象としたアブレーションの臨床転帰には一貫性がなく、AF ドライバーのダイナミクスを特徴付け、アブレーション戦略を導くための仮想心臓ベースのアプローチの必要性が強調されています。  我々は、大規模な持続性AFコホートからの仮想心臓モデルを使用して、AFアブレーション後の調律結果に関連する肺静脈外ドライバーの電気生理学的特徴を定義しました。  方法：CUVIA-AF2研究（心心房細動の仮想アブレーションガイド付きカテーテルアブレーションの臨床的有用性2）から得られた持続性心心房細動患者165人を対象に、心臓コンピュータ断層撮影法と電気解剖学的マップを統合した左心房仮想心臓モデルを分析した。 34 秒の仮想 AF シミュレーション中に、安定した位相特異点 (PS) は、直径 10 mm 内で 2 秒以上持続する PS によって特定されました。  一時的な安定性を評価するために、主要周波数 (DF) を 3 回の連続する 6 秒間隔で評価しました。  活動電位持続時間回復曲線の最大の傾きは、仮想ランプ ペーシング (200 ～ 120 ミリ秒) によって導出されました。  すべてのマーカーは、6 つの肺静脈外領域にわたって評価されました。  安定した PS、DF、活動電位持続時間回復曲線の最大傾き、低電圧領域 (&lt;0.5 mV)、および 1 年間のリズム結果の間の関連性が分析されました。  結果: 肺静脈外領域での安定した PS が 124 人 (75%) の患者で観察されました。このうち 43 人 (34.7%) は安定した DF を示し、81 人 (65.3%) は蛇行した DF を示しました。 仮想心臓モデルの領域解析では、安定した DF を伴う安定した PS を含む領域は、蛇行する DF を伴う安定した PS を有する領域よりも、活動電位持続時間回復曲線のより高い最大傾き (1.41±0.80 対 1.09±0.60; &lt;0.001) とより大きな局所仮想低電圧負荷 (2.96±3.23% 対 2.10±2.75%) を示しました。  安定したDFを伴う安定したPSは、1年間の追跡調査でのAF再発の増加と相関した(ログランク=0.002;調整後ハザード比、5.78[95%CI、2.18-15.3])。  安定した PS と DF を含む予測モデルは、再発予測の見かけの曲線下面積 0.765 を示しました。  結論: 仮想心臓モデルで同定された安定した PS と安定した DF は、有害なモデル由来の局所基質特徴とアブレーション後のより高い再発率に関連していた。 これらのマーカーの仮想心臓ベースの同定は、持続性 AF におけるアブレーション反応の予測を改善する可能性があり、前向きの検証が保証されます。</t>
+    <t>背景: 持続性心房細動 (AF) におけるドライバーを対象としたアブレーションの臨床転帰には一貫性がなく、AF ドライバーのダイナミクスを特徴付け、アブレーション戦略を導くための仮想心臓ベースのアプローチの必要性が強調されています。  我々は、大規模な持続性AFコホートからの仮想心臓モデルを使用して、AFアブレーション後の調律結果に関連する肺静脈外ドライバーの電気生理学的特徴を定義しました。  方法：CUVIA-AF2研究（心房細動の仮想アブレーションガイド付きカテーテルアブレーションの臨床的有用性2）から得られた持続性心房細動患者165人を対象に、心臓コンピュータ断層撮影法と電気解剖学的マップを統合した左心房仮想心臓モデルを分析した。 34 秒の仮想 AF シミュレーション中に、安定した位相特異点 (PS) は、直径 10 mm 内で 2 秒以上持続する PS によって特定されました。  一時的な安定性を評価するために、主要周波数 (DF) を 3 回の連続する 6 秒間隔で評価しました。  活動電位持続時間回復曲線の最大の傾きは、仮想ランプ ペーシング (200 ～ 120 ミリ秒) によって導出されました。  すべてのマーカーは、6 つの肺静脈外領域にわたって評価されました。  安定した PS、DF、活動電位持続時間回復曲線の最大傾き、低電圧領域 (&lt;0.5 mV)、および 1 年間のリズム結果の間の関連性が分析されました。  結果: 肺静脈外領域での安定した PS が 124 人 (75%) の患者で観察されました。このうち 43 人 (34.7%) は安定した DF を示し、81 人 (65.3%) は蛇行した DF を示しました。 仮想心臓モデルの領域解析では、安定した DF を伴う安定した PS を含む領域は、蛇行する DF を伴う安定した PS を有する領域よりも、活動電位持続時間回復曲線のより高い最大傾き (1.41±0.80 対 1.09±0.60; &lt;0.001) とより大きな局所仮想低電圧負荷 (2.96±3.23% 対 2.10±2.75%) を示しました。  安定したDFを伴う安定したPSは、1年間の追跡調査でのAF再発の増加と相関した(ログランク=0.002;調整後ハザード比、5.78[95%CI、2.18-15.3])。  安定した PS と DF を含む予測モデルは、再発予測の見かけの曲線下面積 0.765 を示しました。  結論: 仮想心臓モデルで同定された安定した PS と安定した DF は、有害なモデル由来の局所基質特徴とアブレーション後のより高い再発率に関連していた。 これらのマーカーの仮想心臓ベースの同定は、持続性 AF におけるアブレーション反応の予測を改善する可能性があり、前向きの検証が保証されます。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -2640,7 +2640,7 @@
     <t>ℹ️ 論文本文 (Full Text) や図表の全ページ閲覧は、上記の PubMed URL (https://pubmed.ncbi.nlm.nih.gov/42788250/) または DOI リンク先の出版社公式サイトからアクセスできます。</t>
   </si>
   <si>
-    <t xml:space="preserve">📄 [No.24] 持続性心心心房細動におけるマーシャルエタノール注入の静脈: VOMALC-PeAF レジストリからの洞察
+    <t xml:space="preserve">📄 [No.24] 持続性心房細動におけるマーシャルエタノール注入の静脈: VOMALC-PeAF レジストリからの洞察
 (Vein of Marshall ethanol infusion in persistent atrial fibrillation: Insight from VOMALC-PeAF registry.)</t>
   </si>
   <si>
@@ -2653,7 +2653,7 @@
     <t>10.1007/s10840-026-02433-4 doi</t>
   </si>
   <si>
-    <t>目的: 肺静脈隔離 (PVI) アブレーションは、持続性心心房細動 (PeAF) に対する効果が限られています。  PVI、静脈マーシャルエタノール注入（VOM-EI）、および主要な心房峡部をターゲットとした解剖学的アブレーション戦略（AS）を組み合わせた解剖学的戦略は、この状況で有望な短期成果を示しています。  方法：この後ろ向き多施設観察コホート研究には、VOM-EI + ASまたはPVIのみを受けた連続したPeAF患者が含まれた。  主要評価項目は、抗不整脈薬（AAD）を使用しない状態で30秒以上続く心房性不整脈（AA）から解放されることでした。  手順の特徴と安全性の結果も評価されました。  結果: 2:1 の傾向スコアマッチングの後、VOM-EI + AS で治療された 151 人の患者と PVI のみで治療された 75 人の患者が比較されました。 追跡期間中央値22カ月（四分位範囲（IQR）：9～35カ月）後、VOM-EI+AS対PVIのみの群では、AADを伴わないAAのない患者が81％対47％であった（p&lt;0.001）。  双方向僧帽弁峡部（MI）ブロックの達成は、不整脈のない生存の最も強力な独立予測因子でした（HR = 0.114; 95% CI: 0.041-0.321; p &lt; 0.001）。  逆に、長期にわたる PeAF は心房性不整脈再発リスクの増加と独立して関連していた (HR = 2.68; 95% CI: 1.240-5.812; p = 0.012)。  結論: 実際の PeAF 集団において、VOM-EI、PVI、および解剖学的線状病変を組み込んだ最初のアブレーション戦略は、長期追跡調査における不整脈再発の予防において、PVI 単独よりも大幅に効果的でした。 僧帽弁ラインを横切る双方向ブロックの検証と AF 持続時間は、長期的な成功の重要な決定要因です。  持続性心心房細動患者では、マーシャルエタノール注入の静脈を含む最初の処置アブレーションと、肺静脈隔離と線状病変を組み合わせた解剖学的アブレーション戦略により、肺静脈隔離のみと比較して、長期不整脈のない生存率が大幅に改善されました。</t>
+    <t>目的: 肺静脈隔離 (PVI) アブレーションは、持続性心房細動 (PeAF) に対する効果が限られています。  PVI、静脈マーシャルエタノール注入（VOM-EI）、および主要な心房峡部をターゲットとした解剖学的アブレーション戦略（AS）を組み合わせた解剖学的戦略は、この状況で有望な短期成果を示しています。  方法：この後ろ向き多施設観察コホート研究には、VOM-EI + ASまたはPVIのみを受けた連続したPeAF患者が含まれた。  主要評価項目は、抗不整脈薬（AAD）を使用しない状態で30秒以上続く心房性不整脈（AA）から解放されることでした。  手順の特徴と安全性の結果も評価されました。  結果: 2:1 の傾向スコアマッチングの後、VOM-EI + AS で治療された 151 人の患者と PVI のみで治療された 75 人の患者が比較されました。 追跡期間中央値22カ月（四分位範囲（IQR）：9～35カ月）後、VOM-EI+AS対PVIのみの群では、AADを伴わないAAのない患者が81％対47％であった（p&lt;0.001）。  双方向僧帽弁峡部（MI）ブロックの達成は、不整脈のない生存の最も強力な独立予測因子でした（HR = 0.114; 95% CI: 0.041-0.321; p &lt; 0.001）。  逆に、長期にわたる PeAF は心房性不整脈再発リスクの増加と独立して関連していた (HR = 2.68; 95% CI: 1.240-5.812; p = 0.012)。  結論: 実際の PeAF 集団において、VOM-EI、PVI、および解剖学的線状病変を組み込んだ最初のアブレーション戦略は、長期追跡調査における不整脈再発の予防において、PVI 単独よりも大幅に効果的でした。 僧帽弁ラインを横切る双方向ブロックの検証と AF 持続時間は、長期的な成功の重要な決定要因です。  持続性心房細動患者では、マーシャルエタノール注入の静脈を含む最初の処置アブレーションと、肺静脈隔離と線状病変を組み合わせた解剖学的アブレーション戦略により、肺静脈隔離のみと比較して、長期不整脈のない生存率が大幅に改善されました。</t>
   </si>
   <si>
     <t xml:space="preserve">PURPOSE:
@@ -2669,7 +2669,7 @@
     <t>ℹ️ 論文本文 (Full Text) や図表の全ページ閲覧は、上記の PubMed URL (https://pubmed.ncbi.nlm.nih.gov/42720910/) または DOI リンク先の出版社公式サイトからアクセスできます。</t>
   </si>
   <si>
-    <t xml:space="preserve">📄 [No.25] 再発性心房性不整脈の特徴と心心心房細動のパルスフィールドアブレーション後の病変評価
+    <t xml:space="preserve">📄 [No.25] 再発性心房性不整脈の特徴と心房細動のパルスフィールドアブレーション後の病変評価
 (Characteristics of Recurrent Atrial Arrhythmias and Lesion Assessment Late After Pulsed Field Ablation of Atrial Fibrillation.)</t>
   </si>
   <si>
@@ -2685,7 +2685,7 @@
     <t>10.1161/CIRCEP.125.014506 doi</t>
   </si>
   <si>
-    <t>背景: パルスフィールドアブレーション (PFA) は、心心房細動 (AF) のアブレーションのための新規かつ急速に拡大しているエネルギーです。  肺静脈 (PV) の特性と PV 以外の PFA 適用と、やり直し手順中に観察される不整脈の再発または持続性病変の種類との関係は依然として不明です。  方法: フランス PFA 全国網羅的多中心レジストリのこのサブ研究では、最初の AF アブレーション処置中に提供された PFA アプリケーションに関する詳細なデータを収集しました。  3次元マッピングによるやり直し処置を受けた不整脈再発患者（n=145）について、再発の種類、持続的PV隔離（PVI）の割合、およびアブレーションライン上の完全ブロックの存在を分析した。 結果: 再発性不整脈は 58% が AF、28% が心房頻脈、8% が典型的な心房粗動でした。  最初のアブレーションが PV 外領域をターゲットとした場合 (45 対 71%; =0.01)、および直径 35 mm のカテーテルが PVI のみに使用された場合 (50 対 77%; =0.01)、AF は観察される頻度が低くなりました。  完全な耐久性のある PVI は患者の 42% (個別の PV ごとに 69% ～ 76%) で観察され、耐久性のある屋根/PW および僧帽弁峡部ブロックはそれぞれ症例の 62% と 31% で観察されました。  耐久性のある PVI の割合は、PFA の塗布数 (12 回の塗布) とともに増加しました。同様に、屋根/PW のブロック率は、16 回以上の塗布 (&lt;0.01) で 88% に増加しました。僧帽弁峡部のブロック率は依然として低く (31%)、塗布回数と有意な関連はありませんでした。 結論：ペンタスプリン PFA カテーテルを使用した最初の AF アブレーション後にやり直し処置を受けた患者では、アブレーション病変が PV を越えて行われた場合、AF が観察される頻度は低くなりました。  耐久性のある PVI またはブロックの高い割合は、PV あたり 12 を超える PFA アプリケーション、屋根/PW では 16 を超える PFA アプリケーションで達成されました。  ペンタスプライン PFA カテーテルを使用した場合、僧帽弁峡部ブロックの長期耐久性は低かった。</t>
+    <t>背景: パルスフィールドアブレーション (PFA) は、心房細動 (AF) のアブレーションのための新規かつ急速に拡大しているエネルギーです。  肺静脈 (PV) の特性と PV 以外の PFA 適用と、やり直し手順中に観察される不整脈の再発または持続性病変の種類との関係は依然として不明です。  方法: フランス PFA 全国網羅的多中心レジストリのこのサブ研究では、最初の AF アブレーション処置中に提供された PFA アプリケーションに関する詳細なデータを収集しました。  3次元マッピングによるやり直し処置を受けた不整脈再発患者（n=145）について、再発の種類、持続的PV隔離（PVI）の割合、およびアブレーションライン上の完全ブロックの存在を分析した。 結果: 再発性不整脈は 58% が AF、28% が心房頻脈、8% が典型的な心房粗動でした。  最初のアブレーションが PV 外領域をターゲットとした場合 (45 対 71%; =0.01)、および直径 35 mm のカテーテルが PVI のみに使用された場合 (50 対 77%; =0.01)、AF は観察される頻度が低くなりました。  完全な耐久性のある PVI は患者の 42% (個別の PV ごとに 69% ～ 76%) で観察され、耐久性のある屋根/PW および僧帽弁峡部ブロックはそれぞれ症例の 62% と 31% で観察されました。  耐久性のある PVI の割合は、PFA の塗布数 (12 回の塗布) とともに増加しました。同様に、屋根/PW のブロック率は、16 回以上の塗布 (&lt;0.01) で 88% に増加しました。僧帽弁峡部のブロック率は依然として低く (31%)、塗布回数と有意な関連はありませんでした。 結論：ペンタスプリン PFA カテーテルを使用した最初の AF アブレーション後にやり直し処置を受けた患者では、アブレーション病変が PV を越えて行われた場合、AF が観察される頻度は低くなりました。  耐久性のある PVI またはブロックの高い割合は、PV あたり 12 を超える PFA アプリケーション、屋根/PW では 16 を超える PFA アプリケーションで達成されました。  ペンタスプライン PFA カテーテルを使用した場合、僧帽弁峡部ブロックの長期耐久性は低かった。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -2888,7 +2888,7 @@
     <t>ℹ️ 論文本文 (Full Text) や図表の全ページ閲覧は、上記の PubMed URL (https://pubmed.ncbi.nlm.nih.gov/42820874/) または DOI リンク先の出版社公式サイトからアクセスできます。</t>
   </si>
   <si>
-    <t xml:space="preserve">📄 [No.32] RESET-AF（心心心房細動に対するRapid onE-Shotエレクトロポレーショントライアル）による人類初の体験
+    <t xml:space="preserve">📄 [No.32] RESET-AF（心房細動に対するRapid onE-Shotエレクトロポレーショントライアル）による人類初の体験
 (First-in-human experience from RESET-AF (Rapid onE-Shot Electroporation Trial for Atrial Fibrillation).)</t>
   </si>
   <si>
@@ -2901,7 +2901,7 @@
     <t>10.1007/s10840-026-02434-3 doi</t>
   </si>
   <si>
-    <t>背景と目的: パルスフィールドアブレーション (PFA) は、心心房細動 (AF) 患者の治療に使用されることが増えています。  RESET-AFは、新規のシングルショットPFAシステム（米国カリフォルニア州タスティンのElePulse、CRC EP）を使用したAFアブレーションの単群ファーストインヒューマン臨床試験であり、試験登録ACTRN12622001523796（登録日2022年12月8日）であった。  方法：症候性発作性心心房細動（n = 22）および持続性心心房細動（n = 14）を有する連続登録患者36人（57±11歳、男性69％）において、このカテーテルを使用し、3Dマッピングに基づいて肺静脈隔離術（PVI）が実施された。  PVI の耐久性を確認するために、すべての患者が 3 か月後に再マッピングを受けました。  患者は6ヵ月後と12ヵ月後に臨床レビュー、ホルターモニタリング、心電図検査を受けて追跡調査されました。 主要な有効性と安全性のエンドポイントには、12か月後の再発性AFの頻度が50%以上、7日と30日後の重篤な有害事象（SAE）の頻度が50%以上、6か月間のAFの頻度が60%を超えたことが含まれた。  結果: 研究コホート全体ですべてのエンドポイントが達成されました。  SAE（保存的管理で回復した腎障害）は1件あり、総SAE率は2.8%でした。  1 人の患者は 12 か月時点で追跡不能となり、主要有効性評価項目は 92% (患者 35 人中 32 人) でした。  二次有効性評価項目は、3 か月後の PVI が 82%、6 か月後の AF が 94% (患者 36 人中 34 人) であった。  研究中、PFA 用量は 3 つのコホートで調整されました。  「最適化されたサブセット」は、SAE がなく、6 か月および 12 か月の時点で 100% の PVI 耐久性と AF がありませんでした。 結論: 発作性および持続性 AF のアブレーションのための新しい PFA カテーテル システムのこの研究は、あらかじめ決められた一次および二次臨床エンドポイントをすべて達成しました。</t>
+    <t>背景と目的: パルスフィールドアブレーション (PFA) は、心房細動 (AF) 患者の治療に使用されることが増えています。  RESET-AFは、新規のシングルショットPFAシステム（米国カリフォルニア州タスティンのElePulse、CRC EP）を使用したAFアブレーションの単群ファーストインヒューマン臨床試験であり、試験登録ACTRN12622001523796（登録日2022年12月8日）であった。  方法：症候性発作性心房細動（n = 22）および持続性心房細動（n = 14）を有する連続登録患者36人（57±11歳、男性69％）において、このカテーテルを使用し、3Dマッピングに基づいて肺静脈隔離術（PVI）が実施された。  PVI の耐久性を確認するために、すべての患者が 3 か月後に再マッピングを受けました。  患者は6ヵ月後と12ヵ月後に臨床レビュー、ホルターモニタリング、心電図検査を受けて追跡調査されました。 主要な有効性と安全性のエンドポイントには、12か月後の再発性AFの頻度が50%以上、7日と30日後の重篤な有害事象（SAE）の頻度が50%以上、6か月間のAFの頻度が60%を超えたことが含まれた。  結果: 研究コホート全体ですべてのエンドポイントが達成されました。  SAE（保存的管理で回復した腎障害）は1件あり、総SAE率は2.8%でした。  1 人の患者は 12 か月時点で追跡不能となり、主要有効性評価項目は 92% (患者 35 人中 32 人) でした。  二次有効性評価項目は、3 か月後の PVI が 82%、6 か月後の AF が 94% (患者 36 人中 34 人) であった。  研究中、PFA 用量は 3 つのコホートで調整されました。  「最適化されたサブセット」は、SAE がなく、6 か月および 12 か月の時点で 100% の PVI 耐久性と AF がありませんでした。 結論: 発作性および持続性 AF のアブレーションのための新しい PFA カテーテル システムのこの研究は、あらかじめ決められた一次および二次臨床エンドポイントをすべて達成しました。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND AND AIMS:
@@ -2982,7 +2982,7 @@
     <t>ℹ️ 論文本文 (Full Text) や図表の全ページ閲覧は、上記の PubMed URL (https://pubmed.ncbi.nlm.nih.gov/42820876/) または DOI リンク先の出版社公式サイトからアクセスできます。</t>
   </si>
   <si>
-    <t xml:space="preserve">📄 [No.35] 心心心房細動における神経叢機能に対するパルスフィールドアブレーションの影響
+    <t xml:space="preserve">📄 [No.35] 心房細動における神経叢機能に対するパルスフィールドアブレーションの影響
 (Impact of pulsed field ablation on ganglionated plexi function in atrial fibrillation.)</t>
   </si>
   <si>
@@ -2998,7 +2998,7 @@
     <t>10.1016/j.hrthm.2026.05.035 doi</t>
   </si>
   <si>
-    <t>背景: 熱エネルギーを利用した肺静脈隔離術 (PVI) は、左心房 (LA) 神経節叢 (GP) への側副傷害を介して抗不整脈効果の一部を発揮する可能性があります。  心内膜パルスフィールドアブレーション (PFA) は心臓選択的になるように設計されていますが、ヒトの GP 機能に対するその影響は不明です。  目的: この研究は、LA GP 活動に対する心内膜 PFA の影響を系統的に評価することを目的としました。  方法：この前向きコホート研究では、初めて PFA を受けた持続性心心房細動患者が連続して登録されました。  心心房細動中の局所高周波刺激により、房室遅延（AVD）（AVD-GP）を示すLA GP部位が特定されました。これは、高周波刺激中の50％以上のRR延長または心停止として定義されます。 後壁アブレーションを伴う PVI を達成するために、ペンタスプライン カテーテルを使用して広範な前庭 PFA を送達しました。  PFA 病変を覆う AVD-GP 部位を含むセグメントが再検査され、その後、活性な AVD-GP 部位が高周波 (RF) アブレーションで標的化され、再評価されました。  結果: 10 人の患者 (年齢 61.9 ± 7.1 歳、女性 3 人 [30%]) が登録されました。  ベースラインでは、検査された591部位のうち118部位(20.0%)がAVD-GP基準(患者当たり11.8±7.8)を満たしており、これには肺静脈口の23部位(19.5%)が含まれていた。  一過性 AVD は、PFA 適用中に患者 10 人中 4 人 (40%) で発生しました。  PFA 後、PFA 治療領域を覆う AVD-GP 部位を有する 21 セグメントのうち 16 セグメント (患者あたり 2.0 ± 1.1 セグメント) が持続的な AVD 反応を示しました。  ターゲットを絞った RF アブレーションの後、以前に活性だった AVD-GP 部位は AVD 応答を示さなくなりました。 結論: 心内膜 PFA は、重複部位への病変送達にもかかわらず、LA GP 機能を一貫して消失させるわけではない。  RF アブレーションは GP 媒介 AVD を確実に排除します。  これらの発見は、PFA の心臓選択的性質を裏付け、PFA ベースの PVI 戦略後の補助 GP アブレーションの前向き評価の機構的理論的根拠を提供します。</t>
+    <t>背景: 熱エネルギーを利用した肺静脈隔離術 (PVI) は、左心房 (LA) 神経節叢 (GP) への側副傷害を介して抗不整脈効果の一部を発揮する可能性があります。  心内膜パルスフィールドアブレーション (PFA) は心臓選択的になるように設計されていますが、ヒトの GP 機能に対するその影響は不明です。  目的: この研究は、LA GP 活動に対する心内膜 PFA の影響を系統的に評価することを目的としました。  方法：この前向きコホート研究では、初めて PFA を受けた持続性心房細動患者が連続して登録されました。  心房細動中の局所高周波刺激により、房室遅延（AVD）（AVD-GP）を示すLA GP部位が特定されました。これは、高周波刺激中の50％以上のRR延長または心停止として定義されます。 後壁アブレーションを伴う PVI を達成するために、ペンタスプライン カテーテルを使用して広範な前庭 PFA を送達しました。  PFA 病変を覆う AVD-GP 部位を含むセグメントが再検査され、その後、活性な AVD-GP 部位が高周波 (RF) アブレーションで標的化され、再評価されました。  結果: 10 人の患者 (年齢 61.9 ± 7.1 歳、女性 3 人 [30%]) が登録されました。  ベースラインでは、検査された591部位のうち118部位(20.0%)がAVD-GP基準(患者当たり11.8±7.8)を満たしており、これには肺静脈口の23部位(19.5%)が含まれていた。  一過性 AVD は、PFA 適用中に患者 10 人中 4 人 (40%) で発生しました。  PFA 後、PFA 治療領域を覆う AVD-GP 部位を有する 21 セグメントのうち 16 セグメント (患者あたり 2.0 ± 1.1 セグメント) が持続的な AVD 反応を示しました。  ターゲットを絞った RF アブレーションの後、以前に活性だった AVD-GP 部位は AVD 応答を示さなくなりました。 結論: 心内膜 PFA は、重複部位への病変送達にもかかわらず、LA GP 機能を一貫して消失させるわけではない。  RF アブレーションは GP 媒介 AVD を確実に排除します。  これらの発見は、PFA の心臓選択的性質を裏付け、PFA ベースの PVI 戦略後の補助 GP アブレーションの前向き評価の機構的理論的根拠を提供します。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -3181,7 +3181,7 @@
     <t>ℹ️ 論文本文 (Full Text) や図表の全ページ閲覧は、上記の PubMed URL (https://pubmed.ncbi.nlm.nih.gov/42820877/) または DOI リンク先の出版社公式サイトからアクセスできます。</t>
   </si>
   <si>
-    <t xml:space="preserve">📄 [No.42] 両右肺静脈の右心房ドレナージを伴う部分異常肺静脈還流における心心心房細動に対するパルスフィールドアブレーション
+    <t xml:space="preserve">📄 [No.42] 両右肺静脈の右心房ドレナージを伴う部分異常肺静脈還流における心房細動に対するパルスフィールドアブレーション
 (Pulsed-Field Ablation for Atrial Fibrillation in Partial Anomalous Pulmonary Venous Return With Right Atrial Drainage of Both Right Pulmonary Veins.)</t>
   </si>
   <si>
@@ -3194,7 +3194,7 @@
     <t>10.1002/joa3.70485 doi</t>
   </si>
   <si>
-    <t>パルスフィールドアブレーションは、心心房細動と部分的な肺静脈還流異常のある患者に対して安全に実施されました。電気解剖学的マッピングにより洞結節領域が定義され、異常な右肺静脈切除部位から十分な距離があることが確認され、分離が成功しました。</t>
+    <t>パルスフィールドアブレーションは、心房細動と部分的な肺静脈還流異常のある患者に対して安全に実施されました。電気解剖学的マッピングにより洞結節領域が定義され、異常な右肺静脈切除部位から十分な距離があることが確認され、分離が成功しました。</t>
   </si>
   <si>
     <t>Pulsed-field ablation was safely performed in a patient with atrial fibrillation and partial anomalous pulmonary venous return. Electroanatomical mapping defined the sinus node region and confirmed sufficient distance from anomalous right pulmonary vein ablation sites, enabling successful isolation.</t>
@@ -3203,7 +3203,7 @@
     <t>ℹ️ 論文本文 (Full Text) や図表の全ページ閲覧は、上記の PubMed URL (https://pubmed.ncbi.nlm.nih.gov/42812536/) または DOI リンク先の出版社公式サイトからアクセスできます。</t>
   </si>
   <si>
-    <t xml:space="preserve">📄 [No.43] 心心心房細動アブレーションの有効性エンドポイント、安全性エンドポイント、および試験デザイン: 心拍リズム協会によって承認された学術研究コンソーシアム イニシアチブ
+    <t xml:space="preserve">📄 [No.43] 心房細動アブレーションの有効性エンドポイント、安全性エンドポイント、および試験デザイン: 心拍リズム協会によって承認された学術研究コンソーシアム イニシアチブ
 (Atrial Fibrillation Ablation Effectiveness End Points, Safety End Points, and Trial Design: Academic Research Consortium Initiative Endorsed by the Heart Rhythm Society.)</t>
   </si>
   <si>
@@ -3216,7 +3216,7 @@
     <t>10.1161/CIRCEP.126.015082 doi</t>
   </si>
   <si>
-    <t>AFA-ARC (心心房細動アブレーション学術研究コンソーシアム) イニシアティブの目的は、症候性心心房細動の治療のためのカテーテルアブレーションを評価する極めて重要な臨床試験の試験デザインと安全性と有効性のエンドポイントを再検討し、規制上の意思決定をサポートする意味のある解釈可能なデータを提供することです。  2024年7月から、国際専門家グループは作業グループ（グループ1の有効性エンドポイント、グループ2の安全性エンドポイント、グループ3の試験設計と報告書）で仮想的に一緒に、または別々に定期的に会合を開き始め、2025年4月に1回の対面での会合が開催され、2025年1月から2026年2月にかけて提案草案の改訂が行われた。 Center for Devices and Radiological Health の心臓血管デバイス食品医薬品局は、改訂と提案のプロセス全体を通じて意見を提供しました。  患者擁護者は、直接の会議と改訂段階に参加しました。  Heart Rhythm Society の指導者は、プロセス全体および改訂段階に関与しました。  業界の代表者には、提出前の改訂段階で提案された原稿の草稿が送られました。  このプロセスの結果、心心房細動のカテーテルアブレーションを評価する極めて重要な臨床試験の試験デザインと安全性と有効性のエンドポイントを再検討するための統合文書が作成されました。  この文書は、3 つの作業グループのそれぞれからの貢献を表しています。 Heart Rhythm Society はこの文書を承認しました。  このAFA-ARC文書は、症候性発作性AF、持続性AF、または長期持続性AF患者におけるAFアブレーションを評価する研究の有効性と安全性のエンドポイント、研究デザイン、報告書の改訂版を提案している。</t>
+    <t>AFA-ARC (心房細動アブレーション学術研究コンソーシアム) イニシアティブの目的は、症候性心房細動の治療のためのカテーテルアブレーションを評価する極めて重要な臨床試験の試験デザインと安全性と有効性のエンドポイントを再検討し、規制上の意思決定をサポートする意味のある解釈可能なデータを提供することです。  2024年7月から、国際専門家グループは作業グループ（グループ1の有効性エンドポイント、グループ2の安全性エンドポイント、グループ3の試験設計と報告書）で仮想的に一緒に、または別々に定期的に会合を開き始め、2025年4月に1回の対面での会合が開催され、2025年1月から2026年2月にかけて提案草案の改訂が行われた。 Center for Devices and Radiological Health の心臓血管デバイス食品医薬品局は、改訂と提案のプロセス全体を通じて意見を提供しました。  患者擁護者は、直接の会議と改訂段階に参加しました。  Heart Rhythm Society の指導者は、プロセス全体および改訂段階に関与しました。  業界の代表者には、提出前の改訂段階で提案された原稿の草稿が送られました。  このプロセスの結果、心房細動のカテーテルアブレーションを評価する極めて重要な臨床試験の試験デザインと安全性と有効性のエンドポイントを再検討するための統合文書が作成されました。  この文書は、3 つの作業グループのそれぞれからの貢献を表しています。 Heart Rhythm Society はこの文書を承認しました。  このAFA-ARC文書は、症候性発作性AF、持続性AF、または長期持続性AF患者におけるAFアブレーションを評価する研究の有効性と安全性のエンドポイント、研究デザイン、報告書の改訂版を提案している。</t>
   </si>
   <si>
     <t>The aim of the AFA-ARC (Atrial Fibrillation Ablation Academic Research Consortium) initiative is to reexamine trial design and the safety and effectiveness end points for pivotal clinical trials evaluating catheter ablation for the treatment of symptomatic atrial fibrillation to provide meaningful and interpretable data to support regulatory decision-making. Beginning in July 2024, a group of international experts began meeting regularly both virtually together and separately in working groups (group 1 effectiveness end points; group 2 safety end points; and group 3 trial design and report forms), with one in-person meeting held in April 2025, and revisions of draft proposals from January 2025 to February 2026. The Food and Drug Administration Office of Cardiovascular Devices at the Center for Devices and Radiological Health provided input throughout the revision and proposal process. A patient advocate participated in the in-person meeting and during the revision phase. Heart Rhythm Society leadership was involved throughout the process and in the revision phase. Industry representatives were sent drafts of the proposed manuscripts during the revision phase before submission. The result of this process was the creation of a combined document to reexamine trial design and the safety and effectiveness end points for pivotal clinical trials evaluating catheter ablation of atrial fibrillation. This document represents contributions from each of the 3 Working Groups. The Heart Rhythm Society endorsed this document. This AFA-ARC document proposes revised effectiveness and safety end points, study design, and report forms for studies evaluating AF ablation in patients with symptomatic paroxysmal, persistent, or longstanding persistent AF.</t>
@@ -3225,7 +3225,7 @@
     <t>ℹ️ 論文本文 (Full Text) や図表の全ページ閲覧は、上記の PubMed URL (https://pubmed.ncbi.nlm.nih.gov/42808156/) または DOI リンク先の出版社公式サイトからアクセスできます。</t>
   </si>
   <si>
-    <t xml:space="preserve">📄 [No.44] 心心心房細動に対する単極パルスフィールドアブレーション後のアブレーション部位を越えた左心房電圧の減衰
+    <t xml:space="preserve">📄 [No.44] 心房細動に対する単極パルスフィールドアブレーション後のアブレーション部位を越えた左心房電圧の減衰
 (Left Atrial Voltage Attenuation Beyond Ablation Sites After Unipolar Pulsed-Field Ablation for Atrial Fibrillation.)</t>
   </si>
   <si>
@@ -3235,7 +3235,7 @@
     <t>10.1111/jce.70511 doi</t>
   </si>
   <si>
-    <t>はじめに: ほとんどのパルスフィールドアブレーション (PFA) システムとは異なり、Affera (Medtronic) は格子先端カテーテルと皮膚リターンパッチの間に単極エネルギーを供給し、より広範囲の電場を生成する可能性があります。  我々は、これによりアブレーション領域を超えて電圧が減衰する可能性があると仮説を立て、空間的に一致したアブレーション前およびアブレーション後のマップを使用してこれをテストしました。  方法と結果：我々は、Affera システムによる原発性心心房細動アブレーションを受けた 5 人の連続患者を遡及的に研究しました。  アブレーション前およびアブレーション直後の電圧マップは、CARTO 3 および OCTARAY (Biosense Webster) を使用して、右心房ペーシング中に同一の設定で生成されました。 Affera には空間マッチングのためのポイントレベルの 3D 座標がないため、座標 (x、y、z) と双極電圧は CARTO 3 から抽出されました。エネルギー伝達部位の外側のアブレーション前後のポイント (線維輪と左心耳を除く) は、2 mm の相互最近傍基準を使用して空間的にマッチングされました。  これにより、3772 ペアが得られました。  双極性電圧はケースごとに平均化されました。  平均双極電圧はすべての場合で 1.01 ± 0.61 から 0.56 ± 0.29 mV に減少し、40.2% の減少を示しました (95% CI、24.6%-55.8%、p = 0.044)。 距離階層化分析では、残留双極電圧（事後/事前×100）は、アブレーションゾーンの直後で最も低く、最も近いアプリケーションタグ中心からの距離に応じて徐々に増加し（10〜15 mmで16.5%、25〜30 mmで57.8%、すべてp&lt;0.001）、約30 mmを超えると数値的にベースラインと同等になりました。  結論: Affera ベースの単極アブレーションは急性双極電圧減衰を引き起こし、病変セットに隣接する非アブレーション心筋層にまで広がりましたが、距離とともに減少し、主に適用部位の約 30 mm 以内に限定されました。</t>
+    <t>はじめに: ほとんどのパルスフィールドアブレーション (PFA) システムとは異なり、Affera (Medtronic) は格子先端カテーテルと皮膚リターンパッチの間に単極エネルギーを供給し、より広範囲の電場を生成する可能性があります。  我々は、これによりアブレーション領域を超えて電圧が減衰する可能性があると仮説を立て、空間的に一致したアブレーション前およびアブレーション後のマップを使用してこれをテストしました。  方法と結果：我々は、Affera システムによる原発性心房細動アブレーションを受けた 5 人の連続患者を遡及的に研究しました。  アブレーション前およびアブレーション直後の電圧マップは、CARTO 3 および OCTARAY (Biosense Webster) を使用して、右心房ペーシング中に同一の設定で生成されました。 Affera には空間マッチングのためのポイントレベルの 3D 座標がないため、座標 (x、y、z) と双極電圧は CARTO 3 から抽出されました。エネルギー伝達部位の外側のアブレーション前後のポイント (線維輪と左心耳を除く) は、2 mm の相互最近傍基準を使用して空間的にマッチングされました。  これにより、3772 ペアが得られました。  双極性電圧はケースごとに平均化されました。  平均双極電圧はすべての場合で 1.01 ± 0.61 から 0.56 ± 0.29 mV に減少し、40.2% の減少を示しました (95% CI、24.6%-55.8%、p = 0.044)。 距離階層化分析では、残留双極電圧（事後/事前×100）は、アブレーションゾーンの直後で最も低く、最も近いアプリケーションタグ中心からの距離に応じて徐々に増加し（10〜15 mmで16.5%、25〜30 mmで57.8%、すべてp&lt;0.001）、約30 mmを超えると数値的にベースラインと同等になりました。  結論: Affera ベースの単極アブレーションは急性双極電圧減衰を引き起こし、病変セットに隣接する非アブレーション心筋層にまで広がりましたが、距離とともに減少し、主に適用部位の約 30 mm 以内に限定されました。</t>
   </si>
   <si>
     <t xml:space="preserve">INTRODUCTION:
@@ -3249,7 +3249,7 @@
     <t>ℹ️ 論文本文 (Full Text) や図表の全ページ閲覧は、上記の PubMed URL (https://pubmed.ncbi.nlm.nih.gov/42801593/) または DOI リンク先の出版社公式サイトからアクセスできます。</t>
   </si>
   <si>
-    <t xml:space="preserve">📄 [No.45] 持続性心心心房細動に対する後壁隔離を伴うペンタスプラインパルスフィールドアブレーションの学習曲線
+    <t xml:space="preserve">📄 [No.45] 持続性心房細動に対する後壁隔離を伴うペンタスプラインパルスフィールドアブレーションの学習曲線
 (Learning Curve of Pentaspline Pulsed-Field Ablation With Posterior Wall Isolation for Persistent Atrial Fibrillation.)</t>
   </si>
   <si>
@@ -3259,7 +3259,7 @@
     <t>10.1111/jce.70515 doi</t>
   </si>
   <si>
-    <t>背景: ペンタスプライン パルスフィールド アブレーション (PFA) は、持続性心心房細動 (AF) における肺静脈隔離 (PVI) および後壁隔離 (PWI) の新しい治療法として登場しました。  しかし、PVI + PWI の組み合わせに関連する学習曲線と、急性病変の完全性に対する解剖学的要因の寄与は不完全に定義されたままです。  方法：我々は、蛍光透視法および心臓内心エコー検査下での PFA を受けている持続性 AF 患者 182 名を連続して分析した。  急性不完全病変は、体系的な再マッピング後に追加の PFA 適用を必要とする残留伝導として定義されました。  学習フェーズは、セグメント化されたロジスティック回帰と逐次ブロック分析を使用して特定されました。 多変数モデルは、処置期、左心房容積 (LAV)、および後壁の形状を評価しました。  結果: 学習曲線が観察され、最初の 20 回の処置中に不完全な病変形成が最も減少しました。  不完全病変は症例 1 ～ 20 の 55% (初期段階)、症例 21 ～ 160 の 32% (中間相)、症例 161 以上の 4.8% (後期) で発生しました。  手術段階は不完全病変の主な決定要因であり、初期段階と中期段階ではそれぞれ約 24 倍と 9 倍高いオッズでした。  より大きな LAV は、適度な独立した関連性 (OR 1.009/mL) を示しましたが、後壁の形状は独立した関連性を示しませんでした。 中期の不整脈再発は各期で差はなかったが、後期では追跡期間が短かった。  結論: PVI + PWI を使用したペンタスプライン PFA 中の病変完全性は、処置の経験が増えるにつれて徐々に改善します。  LAV が大きいと不完全な病変形成に若干寄与する可能性がありますが、処置の経験が主な役割を果たすと思われます。  体系的な電気解剖学的再マッピングは、かなりの手術経験が蓄積された後でも、不完全な病変を特定して修正するために依然として重要です。</t>
+    <t>背景: ペンタスプライン パルスフィールド アブレーション (PFA) は、持続性心房細動 (AF) における肺静脈隔離 (PVI) および後壁隔離 (PWI) の新しい治療法として登場しました。  しかし、PVI + PWI の組み合わせに関連する学習曲線と、急性病変の完全性に対する解剖学的要因の寄与は不完全に定義されたままです。  方法：我々は、蛍光透視法および心臓内心エコー検査下での PFA を受けている持続性 AF 患者 182 名を連続して分析した。  急性不完全病変は、体系的な再マッピング後に追加の PFA 適用を必要とする残留伝導として定義されました。  学習フェーズは、セグメント化されたロジスティック回帰と逐次ブロック分析を使用して特定されました。 多変数モデルは、処置期、左心房容積 (LAV)、および後壁の形状を評価しました。  結果: 学習曲線が観察され、最初の 20 回の処置中に不完全な病変形成が最も減少しました。  不完全病変は症例 1 ～ 20 の 55% (初期段階)、症例 21 ～ 160 の 32% (中間相)、症例 161 以上の 4.8% (後期) で発生しました。  手術段階は不完全病変の主な決定要因であり、初期段階と中期段階ではそれぞれ約 24 倍と 9 倍高いオッズでした。  より大きな LAV は、適度な独立した関連性 (OR 1.009/mL) を示しましたが、後壁の形状は独立した関連性を示しませんでした。 中期の不整脈再発は各期で差はなかったが、後期では追跡期間が短かった。  結論: PVI + PWI を使用したペンタスプライン PFA 中の病変完全性は、処置の経験が増えるにつれて徐々に改善します。  LAV が大きいと不完全な病変形成に若干寄与する可能性がありますが、処置の経験が主な役割を果たすと思われます。  体系的な電気解剖学的再マッピングは、かなりの手術経験が蓄積された後でも、不完全な病変を特定して修正するために依然として重要です。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -3275,7 +3275,7 @@
     <t>ℹ️ 論文本文 (Full Text) や図表の全ページ閲覧は、上記の PubMed URL (https://pubmed.ncbi.nlm.nih.gov/42801542/) または DOI リンク先の出版社公式サイトからアクセスできます。</t>
   </si>
   <si>
-    <t xml:space="preserve">📄 [No.46] 心三心筋症における心心心房細動に対するマルチモダリティ画像誘導パルスフィールドアブレーション
+    <t xml:space="preserve">📄 [No.46] 心三心筋症における心房細動に対するマルチモダリティ画像誘導パルスフィールドアブレーション
 (Multimodality Imaging-Guided Pulsed Field Ablation for Atrial Fibrillation in Cor Triatriatum Sinister.)</t>
   </si>
   <si>
@@ -3288,7 +3288,7 @@
     <t>10.1002/joa3.70474 doi</t>
   </si>
   <si>
-    <t>マルチモダリティイメージングにより、悪性三心筋症患者における安全な経中隔アクセスとカテーテルナビゲーションが容易になりました。 CARTO に統合された VARIPULSE パルスフィールド アブレーションは、合併症を起こすことなく肺静脈の隔離を達成し、複雑な先天性左心房の解剖学的構造における心心房細動に対する実行可能な治療戦略を実証しました。</t>
+    <t>マルチモダリティイメージングにより、悪性三心筋症患者における安全な経中隔アクセスとカテーテルナビゲーションが容易になりました。 CARTO に統合された VARIPULSE パルスフィールド アブレーションは、合併症を起こすことなく肺静脈の隔離を達成し、複雑な先天性左心房の解剖学的構造における心房細動に対する実行可能な治療戦略を実証しました。</t>
   </si>
   <si>
     <t>Multimodality imaging facilitated safe transseptal access and catheter navigation in a patient with cor triatriatum sinister. CARTO-integrated VARIPULSE pulsed-field ablation achieved pulmonary vein isolation without complications, demonstrating a feasible treatment strategy for atrial fibrillation in complex congenital left atrial anatomy.</t>
@@ -3328,7 +3328,7 @@
     <t>ℹ️ 論文本文 (Full Text) や図表の全ページ閲覧は、上記の PubMed URL (https://pubmed.ncbi.nlm.nih.gov/42798728/) または DOI リンク先の出版社公式サイトからアクセスできます。</t>
   </si>
   <si>
-    <t xml:space="preserve">📄 [No.48] 心心心房細動のバルーン・イン・バスケット・パルスフィールド・アブレーションにおけるモニタリングされた麻酔管理と全身麻酔：処置のタイミングと急性処置の結果の年齢に応じた分析
+    <t xml:space="preserve">📄 [No.48] 心房細動のバルーン・イン・バスケット・パルスフィールド・アブレーションにおけるモニタリングされた麻酔管理と全身麻酔：処置のタイミングと急性処置の結果の年齢に応じた分析
 (Monitored anesthesia care versus general anesthesia for balloon-in-basket pulsed-field ablation of atrial fibrillation: an age-matched analysis of procedural timing and acute procedural outcomes.)</t>
   </si>
   <si>
@@ -3338,7 +3338,7 @@
     <t>10.1007/s10840-026-02443-2 doi</t>
   </si>
   <si>
-    <t>背景: 米国では、パルスフィールドアブレーション(PFA)システムが骨格筋の刺激と不快感を引き起こすため、米国では全身麻酔(GA)が心心房細動(AF)カテーテルアブレーションの鎮静戦略として好まれており、より軽い鎮静下では耐えられないことが挙げられます。  最近導入されたバルーンインバスケット (BiB) PFA システム (VOLT) は、筋肉への刺激と痛みが少ないことが報告されており、GA の代わりに監視麻酔治療 (MAC) が可能になる可能性があります。  この状況において、MAC がアブレーションの有効性を損なうことなく手技効率の利点を提供するかどうかは、十分に特徴づけられていません。 目的: 年齢に合わせたデザインを使用して、AF に対して BiB PFA (VOLT) を受けている患者において MAC と GA の間で処置のタイミング、アブレーションの有効性、安全性を比較すること。  方法：我々は、2施設の電気生理学レジストリから、連続する39例のMAC症例とVOLT BiB PFAを受けた83例のGA症例のプールを遡及的に分析した。  各 MAC 患者は、利用可能な最も近い年齢の GA 患者と 1:1 でマッチングされ、39 人の年齢が一致した対照が得られました。  6 つの異なる時間間隔が収集されました: 総室時間、処置前のセットアップ時間、中心処置時間、処置後のターンオーバー時間、経中隔から左心房 (LA) へのシースアウト (滞留) 時間、およびアブレーション カテーテルの滞留時間。 施行された全切除病変数、急性手術の成功（4 本すべての肺静脈の分離）、および手術の合併症も比較されました。  次に、グループ比較が行われました。  さらに、公開されている EP/手順スイートの 1 分あたりのコスト見積もりを使用して、観察された総室内時間の違いに関連する EP 検査施設のコスト削減とスケジュールの機会コストも決定されました。  結果：総室内時間（103.5 ± 20.0 対 126.2 ± 33.1 分、p = 0.0004）、処置前の準備時間（33.4 ± 10.0 対 50.3 ± 28.0 分、p = 0.0007）、処置後のターンオーバー時間（14.8 ± 9.3 対21.4 ± 8.3 分; p = 0.0030) は MAC の方が有意に短かった。  コア処置時間 (55.3 ± 20.5 対 55.3 ± 23.9 分)、経中隔から LA シースアウトまでの時間 (34.2 ± 12.9 対 55.3 ± 23.9 分) 35.7 ± 18.5 分）はグループ間で有意な差はありませんでした（両方とも p ≥ 0.62）。  アブレーションカテーテルの滞留時間は、MAC の方が若干長くなりました (27.7 ± 11.9 対 24.2 ± 15.5 分; p = 0.036)。  施行された総切除病変数（17.6 ± 5.1 対 18.8 ± 7.2、p = 0.68）および急性処置成功率（39/39 [100%] 対 39/39 [100%]）は、MAC 群と GA 間で同様であり、どちらのグループにも処置上の合併症はありませんでした。  MAC 症例 1 例 (2.6%) は、気道分泌物による咳のため、処置の途中で全身麻酔に変更されました。 公表されている EP/手続きスイートの 1 分あたりのコスト見積もり (29 ドルから 60 ドル/分) を、観測された合計在室時間の 22.7 分の削減に適用すると、MAC は 1 件あたりの設備コストの推定 658 ドルから 1,362 ドルの節約に関連しており、追加のケースのスケジュール設定による潜在的な機会費用の利点が見られました。  結論： AF に対して BiB PFA (VOLT) を受けた年齢を一致させたコホートでは、MAC は GA よりも総室時間、処置前のセットアップ時間、および処置後のターンオーバー時間の短縮と関連しており、アブレーション病変の送達、急性成功、または合併症には差がありませんでした。 MAC による麻酔関連の時間の節約は、アブレーション処置自体ではなく、部屋のロジスティクスに集中しているようで、この小規模コホートでは急性処置の結果に検出可能な差はなく、MAC が BiB PFA に対する GA に代わる合理的な代替品として支持されています。</t>
+    <t>背景: 米国では、パルスフィールドアブレーション(PFA)システムが骨格筋の刺激と不快感を引き起こすため、米国では全身麻酔(GA)が心房細動(AF)カテーテルアブレーションの鎮静戦略として好まれており、より軽い鎮静下では耐えられないことが挙げられます。  最近導入されたバルーンインバスケット (BiB) PFA システム (VOLT) は、筋肉への刺激と痛みが少ないことが報告されており、GA の代わりに監視麻酔治療 (MAC) が可能になる可能性があります。  この状況において、MAC がアブレーションの有効性を損なうことなく手技効率の利点を提供するかどうかは、十分に特徴づけられていません。 目的: 年齢に合わせたデザインを使用して、AF に対して BiB PFA (VOLT) を受けている患者において MAC と GA の間で処置のタイミング、アブレーションの有効性、安全性を比較すること。  方法：我々は、2施設の電気生理学レジストリから、連続する39例のMAC症例とVOLT BiB PFAを受けた83例のGA症例のプールを遡及的に分析した。  各 MAC 患者は、利用可能な最も近い年齢の GA 患者と 1:1 でマッチングされ、39 人の年齢が一致した対照が得られました。  6 つの異なる時間間隔が収集されました: 総室時間、処置前のセットアップ時間、中心処置時間、処置後のターンオーバー時間、経中隔から左心房 (LA) へのシースアウト (滞留) 時間、およびアブレーション カテーテルの滞留時間。 施行された全切除病変数、急性手術の成功（4 本すべての肺静脈の分離）、および手術の合併症も比較されました。  次に、グループ比較が行われました。  さらに、公開されている EP/手順スイートの 1 分あたりのコスト見積もりを使用して、観察された総室内時間の違いに関連する EP 検査施設のコスト削減とスケジュールの機会コストも決定されました。  結果：総室内時間（103.5 ± 20.0 対 126.2 ± 33.1 分、p = 0.0004）、処置前の準備時間（33.4 ± 10.0 対 50.3 ± 28.0 分、p = 0.0007）、処置後のターンオーバー時間（14.8 ± 9.3 対21.4 ± 8.3 分; p = 0.0030) は MAC の方が有意に短かった。  コア処置時間 (55.3 ± 20.5 対 55.3 ± 23.9 分)、経中隔から LA シースアウトまでの時間 (34.2 ± 12.9 対 55.3 ± 23.9 分) 35.7 ± 18.5 分）はグループ間で有意な差はありませんでした（両方とも p ≥ 0.62）。  アブレーションカテーテルの滞留時間は、MAC の方が若干長くなりました (27.7 ± 11.9 対 24.2 ± 15.5 分; p = 0.036)。  施行された総切除病変数（17.6 ± 5.1 対 18.8 ± 7.2、p = 0.68）および急性処置成功率（39/39 [100%] 対 39/39 [100%]）は、MAC 群と GA 間で同様であり、どちらのグループにも処置上の合併症はありませんでした。  MAC 症例 1 例 (2.6%) は、気道分泌物による咳のため、処置の途中で全身麻酔に変更されました。 公表されている EP/手続きスイートの 1 分あたりのコスト見積もり (29 ドルから 60 ドル/分) を、観測された合計在室時間の 22.7 分の削減に適用すると、MAC は 1 件あたりの設備コストの推定 658 ドルから 1,362 ドルの節約に関連しており、追加のケースのスケジュール設定による潜在的な機会費用の利点が見られました。  結論： AF に対して BiB PFA (VOLT) を受けた年齢を一致させたコホートでは、MAC は GA よりも総室時間、処置前のセットアップ時間、および処置後のターンオーバー時間の短縮と関連しており、アブレーション病変の送達、急性成功、または合併症には差がありませんでした。 MAC による麻酔関連の時間の節約は、アブレーション処置自体ではなく、部屋のロジスティクスに集中しているようで、この小規模コホートでは急性処置の結果に検出可能な差はなく、MAC が BiB PFA に対する GA に代わる合理的な代替品として支持されています。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -3369,7 +3369,7 @@
     <t>10.1161/CIRCEP.125.014597 doi</t>
   </si>
   <si>
-    <t>パルスフィールドアブレーションは、従来の熱エネルギーに代わる非熱的で組織選択的な代替手段を提供することにより、心心房細動アブレーションの状況を急速に再構築しました。このレビューでは、パルスフィールドアブレーションをより安全、より高速、より正確な技術として確立した科学的基礎、前臨床証拠、工学的進歩に焦点を当てています。不可逆的なエレクトロポレーションが心筋の選択性をどのように達成するか、近くの構造の保存を確認した極めて重要な研究、効率的かつ耐久性のある病変を作成するために設計された最新のカテーテル システムの進化について説明します。パルスフィールドアブレーションプラットフォームは成熟し続けるにつれて、処置上の安全基準を再定義し、心臓電気生理学における治療の可能性を拡大しています。</t>
+    <t>パルスフィールドアブレーションは、従来の熱エネルギーに代わる非熱的で組織選択的な代替手段を提供することにより、心房細動アブレーションの状況を急速に再構築しました。このレビューでは、パルスフィールドアブレーションをより安全、より高速、より正確な技術として確立した科学的基礎、前臨床証拠、工学的進歩に焦点を当てています。不可逆的なエレクトロポレーションが心筋の選択性をどのように達成するか、近くの構造の保存を確認した極めて重要な研究、効率的かつ耐久性のある病変を作成するために設計された最新のカテーテル システムの進化について説明します。パルスフィールドアブレーションプラットフォームは成熟し続けるにつれて、処置上の安全基準を再定義し、心臓電気生理学における治療の可能性を拡大しています。</t>
   </si>
   <si>
     <t>Pulsed field ablation has rapidly reshaped the landscape of atrial fibrillation ablation by offering a nonthermal, tissue-selective alternative to conventional thermal energy. This review highlights the scientific foundations, preclinical evidence, and engineering advances that established pulsed field ablation as a safer, faster, and more precise technology. We discuss how irreversible electroporation achieves myocardial selectivity, the pivotal studies that confirmed preservation of nearby structures, and the evolution of modern catheter systems designed for efficient and durable lesion creation. As pulsed field ablation platforms continue to mature, they are redefining procedural safety standards and expanding therapeutic possibilities in cardiac electrophysiology.</t>
@@ -3413,7 +3413,7 @@
     <t>10.1002/joa3.70476 doi</t>
   </si>
   <si>
-    <t>背景: QDOT MICRO カテーテルを使用した非常に高出力 (51 ～ 90 W)、短時間 (4 秒) の高周波アプリケーション (QMODE+) では、心心房細動 (AF) を治療するための食道に隣接する左心房 (LA) 後壁での最適な出力設定は不明のままです。  目的: 食道周囲領域における 60 W と 90 W の QMODE+ 高周波アプリケーションの有効性と安全性を評価しました。  方法: 50 人の AF 患者は、食道周囲領域に適用される QMODE+ 出力に基づいて、60 W (= 24) と 90 W (= 26) の 2 つのグループに無作為に分けられました。  食道周囲領域および内視鏡的食道病変における残存伝導ギャップの発生率、および 2 つのグループ間の 1 年心房性頻脈性不整脈 (AT) 再発率を比較しました。 結果: 接触力の中央値は、90 W グループよりも 60 W グループの方が有意に高かった (60 W グループでは 12.9 g [IQR 10.2、15.8]、90 W グループでは 10.9 g [IQR 8.4、14.2]、&lt; 0.001)。  残存伝導ギャップ率 (それぞれ 8.3% と 11.5% = 1.00) および食道病変 (各グループの 4.2%) の割合は 2 つのグループ間で同様でした。  1 年 AT 再発率は 2 つのグループ間で有意な差はありませんでした (それぞれ 20.8% 対 7.7% = 0.24)。  結論: 食道周囲領域への 60 W および 90 W QMODE+ RF アプリケーションは、急性伝導ブロック、内視鏡検査で検出された食道損傷、および 12 か月の AT 無再発生存率を同等の率で達成しましたが、接触力は 60 W グループの方が有意に高かったです。 治験登録：日本臨床試験登録（jRCT）； jRCT1072230115（2024年2月8日登録）。</t>
+    <t>背景: QDOT MICRO カテーテルを使用した非常に高出力 (51 ～ 90 W)、短時間 (4 秒) の高周波アプリケーション (QMODE+) では、心房細動 (AF) を治療するための食道に隣接する左心房 (LA) 後壁での最適な出力設定は不明のままです。  目的: 食道周囲領域における 60 W と 90 W の QMODE+ 高周波アプリケーションの有効性と安全性を評価しました。  方法: 50 人の AF 患者は、食道周囲領域に適用される QMODE+ 出力に基づいて、60 W (= 24) と 90 W (= 26) の 2 つのグループに無作為に分けられました。  食道周囲領域および内視鏡的食道病変における残存伝導ギャップの発生率、および 2 つのグループ間の 1 年心房性頻脈性不整脈 (AT) 再発率を比較しました。 結果: 接触力の中央値は、90 W グループよりも 60 W グループの方が有意に高かった (60 W グループでは 12.9 g [IQR 10.2、15.8]、90 W グループでは 10.9 g [IQR 8.4、14.2]、&lt; 0.001)。  残存伝導ギャップ率 (それぞれ 8.3% と 11.5% = 1.00) および食道病変 (各グループの 4.2%) の割合は 2 つのグループ間で同様でした。  1 年 AT 再発率は 2 つのグループ間で有意な差はありませんでした (それぞれ 20.8% 対 7.7% = 0.24)。  結論: 食道周囲領域への 60 W および 90 W QMODE+ RF アプリケーションは、急性伝導ブロック、内視鏡検査で検出された食道損傷、および 12 か月の AT 無再発生存率を同等の率で達成しましたが、接触力は 60 W グループの方が有意に高かったです。 治験登録：日本臨床試験登録（jRCT）； jRCT1072230115（2024年2月8日登録）。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -3433,7 +3433,7 @@
     <t>ℹ️ 論文本文 (Full Text) や図表の全ページ閲覧は、上記の PubMed URL (https://pubmed.ncbi.nlm.nih.gov/42781049/) または DOI リンク先の出版社公式サイトからアクセスできます。</t>
   </si>
   <si>
-    <t xml:space="preserve">📄 [No.52] 急性心不全入院中の心心心房細動に対するカテーテルアブレーションの安全性: JROAD-DPC データベースからの全国的分析
+    <t xml:space="preserve">📄 [No.52] 急性心不全入院中の心房細動に対するカテーテルアブレーションの安全性: JROAD-DPC データベースからの全国的分析
 (Safety of Catheter Ablation for Atrial Fibrillation During Hospitalisation for Acute Heart Failure: A Nationwide Analysis From the JROAD-DPC Database.)</t>
   </si>
   <si>
@@ -3469,7 +3469,7 @@
     <t>10.1161/CIRCEP.126.015042 doi</t>
   </si>
   <si>
-    <t>背景: 可変ループ円形カテーテルは、心心房細動治療のための安全で効果的なパルスフィールドアブレーションカテーテルであることが示されています。  初期波形 (Seq1) の商用発売後、電極表面温度とアブレーション送達時間 (20 ～ 3.8 秒) を短縮する新しい波形 (Seq2) が開発されました。  この研究では、2 つの洗浄速度と 2 つの投与条件にわたって、Seq1 と Seq2 の安全性と有効性を比較します。  方法: 24 頭のヨークシャー豚を可変ループ円形カテーテルを使用したパルスフィールド アブレーションで治療しました。  被験者は、3 つのパルス レシピ/灌注アーム (Seq1、Seq1、および Seq 2) に無作為に割り当てられました。  各グループを名目上の 1 倍の用量グループと 2 倍の用量グループに分割し、合計 6 つの研究グループとなりました。 安楽死させる前に、フォローアップの再マッピング手順のために切除後 28±2 日間動物をモニタリングした。  28±2日目に肉眼的剖検と組織病理学を実施した。  結果: すべてのグループにおいて、側副傷害の証拠のない壁貫通、周囲の肺静脈病変によって示されるように、急性および慢性肺静脈隔離の有効性が 100% 観察されました。  左心耳、LA屋根、および後壁における貫壁性は、すべてのグループにわたって75%〜100%であり、僧帽弁峡部には存在しなかった。  Seq2 または Seq1 ではカテーテル血栓/炭化物は観察されませんでした。  Seq1 では、血栓/炭化物が 25% (1x) と 100% (2x) で発生しました。  溶血および心筋損傷マーカーの変化はすべてのグループ間で同様でしたが、2x グループで顕著に増加しました。 心エコー検査では、Seq2 のマイクロバブルはほとんどまたはまったくないと評価されましたが、Seq1 と Seq1 はほとんどが中程度またはシャワー程度と評価されました。  結論: 両方の投与条件にわたって、Seq1、Seq2、および Seq1 を含むすべてのグループで一貫して耐久性のある肺静脈隔離が観察されました。  Seq2 は、アブレーション送出時間の短縮 (3.8 秒)、カテーテル血栓形成ゼロ、および微小気泡の発生がほとんどありませんでした。  Seq1 でのより高い洗浄流量もカテーテル血栓の形成を軽減しましたが、マイクロバブルの生成は減少しませんでした。</t>
+    <t>背景: 可変ループ円形カテーテルは、心房細動治療のための安全で効果的なパルスフィールドアブレーションカテーテルであることが示されています。  初期波形 (Seq1) の商用発売後、電極表面温度とアブレーション送達時間 (20 ～ 3.8 秒) を短縮する新しい波形 (Seq2) が開発されました。  この研究では、2 つの洗浄速度と 2 つの投与条件にわたって、Seq1 と Seq2 の安全性と有効性を比較します。  方法: 24 頭のヨークシャー豚を可変ループ円形カテーテルを使用したパルスフィールド アブレーションで治療しました。  被験者は、3 つのパルス レシピ/灌注アーム (Seq1、Seq1、および Seq 2) に無作為に割り当てられました。  各グループを名目上の 1 倍の用量グループと 2 倍の用量グループに分割し、合計 6 つの研究グループとなりました。 安楽死させる前に、フォローアップの再マッピング手順のために切除後 28±2 日間動物をモニタリングした。  28±2日目に肉眼的剖検と組織病理学を実施した。  結果: すべてのグループにおいて、側副傷害の証拠のない壁貫通、周囲の肺静脈病変によって示されるように、急性および慢性肺静脈隔離の有効性が 100% 観察されました。  左心耳、LA屋根、および後壁における貫壁性は、すべてのグループにわたって75%〜100%であり、僧帽弁峡部には存在しなかった。  Seq2 または Seq1 ではカテーテル血栓/炭化物は観察されませんでした。  Seq1 では、血栓/炭化物が 25% (1x) と 100% (2x) で発生しました。  溶血および心筋損傷マーカーの変化はすべてのグループ間で同様でしたが、2x グループで顕著に増加しました。 心エコー検査では、Seq2 のマイクロバブルはほとんどまたはまったくないと評価されましたが、Seq1 と Seq1 はほとんどが中程度またはシャワー程度と評価されました。  結論: 両方の投与条件にわたって、Seq1、Seq2、および Seq1 を含むすべてのグループで一貫して耐久性のある肺静脈隔離が観察されました。  Seq2 は、アブレーション送出時間の短縮 (3.8 秒)、カテーテル血栓形成ゼロ、および微小気泡の発生がほとんどありませんでした。  Seq1 でのより高い洗浄流量もカテーテル血栓の形成を軽減しましたが、マイクロバブルの生成は減少しませんでした。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -3587,7 +3587,7 @@
     <t>ℹ️ 論文本文 (Full Text) や図表の全ページ閲覧は、上記の PubMed URL (https://pubmed.ncbi.nlm.nih.gov/42771720/) または DOI リンク先の出版社公式サイトからアクセスできます。</t>
   </si>
   <si>
-    <t xml:space="preserve">📄 [No.58] 脂質プロファイリング分析と機能同定による、心心心房細動における重要なネガティブメディエーターとしてのスフィンゴミエリン
+    <t xml:space="preserve">📄 [No.58] 脂質プロファイリング分析と機能同定による、心房細動における重要なネガティブメディエーターとしてのスフィンゴミエリン
 (Sphingomyelin as a key negative mediator in atrial fibrillation via lipid proﬁling analysis and functional identiﬁcation.)</t>
   </si>
   <si>
@@ -3597,7 +3597,7 @@
     <t>10.1093/europace/euag270 doi</t>
   </si>
   <si>
-    <t>目的: 心心房細動 (AF) は、世界的に最も蔓延している不整脈の 1 つとして浮上しており、その発生率は継続的に増加しており、それにより公衆衛生上の重大な懸念事項にまで高まっています。  心臓は脂質含有量が高いことで知られており、脂質代謝の障害や異常は心血管疾患と関連していることがよくあります。  この研究は、AFにおける脂質の調節的役割を調査することを目的としています。  方法と結果: ツリーベースのアンサンブル学習支援リピドミクスを使用して、スフィンゴミエリンが重要な差次的代謝産物として同定され、AF 患者では大幅に減少していることが判明しました。  スフィンゴミエリンの外因性補給は、マウスにおける Ach-CaCl2 および Ang II 誘発性の AF、線維症、炎症を大幅に軽減しました。 さらに、スフィンゴミエリンレベルの低下は、AF条件下でのスフィンゴミエリンホスホジエステラーゼ（SMPD）の活性の増加に起因すると考えられました。  機構的には、RNA-Seq解析により、スフィンゴミエリンがAF誘発性のRap1シグナル伝達経路の活性化を阻害することが実証され、この所見は生体内でのRAP1の過剰発現とノックダウンによって裏付けられた。  結論：これらの発見は、まとめると、Rap1シグナル伝達経路の阻害を通じて心心房細動を軽減するスフィンゴミエリンおよびSMPD阻害剤の治療的可能性を強調し、それによってスフィンゴミエリン代謝の標的化が実行可能かつ新規な心心房細動治療戦略として確立されることを示している。</t>
+    <t>目的: 心房細動 (AF) は、世界的に最も蔓延している不整脈の 1 つとして浮上しており、その発生率は継続的に増加しており、それにより公衆衛生上の重大な懸念事項にまで高まっています。  心臓は脂質含有量が高いことで知られており、脂質代謝の障害や異常は心血管疾患と関連していることがよくあります。  この研究は、AFにおける脂質の調節的役割を調査することを目的としています。  方法と結果: ツリーベースのアンサンブル学習支援リピドミクスを使用して、スフィンゴミエリンが重要な差次的代謝産物として同定され、AF 患者では大幅に減少していることが判明しました。  スフィンゴミエリンの外因性補給は、マウスにおける Ach-CaCl2 および Ang II 誘発性の AF、線維症、炎症を大幅に軽減しました。 さらに、スフィンゴミエリンレベルの低下は、AF条件下でのスフィンゴミエリンホスホジエステラーゼ（SMPD）の活性の増加に起因すると考えられました。  機構的には、RNA-Seq解析により、スフィンゴミエリンがAF誘発性のRap1シグナル伝達経路の活性化を阻害することが実証され、この所見は生体内でのRAP1の過剰発現とノックダウンによって裏付けられた。  結論：これらの発見は、まとめると、Rap1シグナル伝達経路の阻害を通じて心房細動を軽減するスフィンゴミエリンおよびSMPD阻害剤の治療的可能性を強調し、それによってスフィンゴミエリン代謝の標的化が実行可能かつ新規な心房細動治療戦略として確立されることを示している。</t>
   </si>
   <si>
     <t xml:space="preserve">AIMS:
@@ -3621,7 +3621,7 @@
     <t>10.1007/s10840-026-02441-4 doi</t>
   </si>
   <si>
-    <t>パルスフィールドアブレーション (PFA) は心室アブレーションに使用されることが増えています。  我々は、左心室頻拍アブレーションに対する逆行性大動脈アプローチによる可変ループ円形 PFA カテーテル (Varipulse、Biosense Webster, Inc.、カリフォルニア州アーバイン) の使用を説明する新しい症例を紹介します。  逆行性大動脈アクセスは、僧帽弁装置による挟み込みを避けるために可変ループ PFA カテーテルの安全な抜去と操作を可能にする長いシース (Ventrax システム、Merit Medical、ユタ州サウス ジョーダン) を使用して達成されました。  この処置は合併症なく完了し、3 か月の追跡調査を通じて VT の再発は観察されませんでした。 この症例は、このアプローチの実現可能性を強調し、この統合された PFA プラットフォームの潜在的な用途を、現在の心心房細動アブレーションの適応を超えて拡大します。</t>
+    <t>パルスフィールドアブレーション (PFA) は心室アブレーションに使用されることが増えています。  我々は、左心室頻拍アブレーションに対する逆行性大動脈アプローチによる可変ループ円形 PFA カテーテル (Varipulse、Biosense Webster, Inc.、カリフォルニア州アーバイン) の使用を説明する新しい症例を紹介します。  逆行性大動脈アクセスは、僧帽弁装置による挟み込みを避けるために可変ループ PFA カテーテルの安全な抜去と操作を可能にする長いシース (Ventrax システム、Merit Medical、ユタ州サウス ジョーダン) を使用して達成されました。  この処置は合併症なく完了し、3 か月の追跡調査を通じて VT の再発は観察されませんでした。 この症例は、このアプローチの実現可能性を強調し、この統合された PFA プラットフォームの潜在的な用途を、現在の心房細動アブレーションの適応を超えて拡大します。</t>
   </si>
   <si>
     <t>Pulsed field ablation (PFA) has been increasingly used for ventricular ablation. We present a novel case describing use of a variable-loop circular PFA catheter (Varipulse, Biosense Webster, Inc., Irvine, CA, USA) via a retrograde aortic approach for left ventricular ventricular tachycardia ablation. Retrograde aortic access was achieved using a long sheath (Ventrax system, Merit Medical, South Jordan, UT) permitting safe unsheathing and manipulation of the variable-loop PFA catheter to avoid entrapment with the mitral valve apparatus. The procedure was completed without complication and no VT recurrence was observed over 3 months follow-up. This case highlights the feasibility of this approach and expands the potential applications of this integrated PFA platform beyond its current indication for atrial fibrillation ablation.</t>
@@ -3666,7 +3666,7 @@
     <t>10.1161/CIRCEP.125.014773 doi</t>
   </si>
   <si>
-    <t>背景: 心心房細動アブレーションの試験における 6 か月の有効性エンドポイントの使用に関する証拠は限られています。  この研究は、発作性心心房細動アブレーションの臨床試験の計画に情報を提供することを第二の目的として、アブレーション有効性エンドポイント検出と追跡期間との関係を評価することを目的としています。  方法: 4 つの前向き研究からの患者レベルのデータが集約されました。  長期有効性エンドポイントは、(1) 3 か月のブランク期間と 12 か月の追跡調査 (現在)、および (2) 2 か月のブランク期間と 6 か月の追跡調査 (提案) で計算されました。  感度、特異度、一致度は、現在のエンドポイントと提案されたエンドポイントに基づいて各研究について計算されました。 線形近似法を使用して 6 か月生存推定値を 12 か月に外挿し、予測された 12 か月生存率を実際の 12 か月生存率と比較しました。  線形近似を使用して、新しいパフォーマンス目標が導出され、各研究の 6 か月生存率と比較されました。  結果: 現在のエンドポイントと提案されたエンドポイントの比較分析により、最近の 4 つの臨床試験全体で 83% ～ 92% の範囲の一致と 57% ～ 76% の範囲の感度が実証されました。  線形近似法により、4 つのプールされた研究の推定 12 か月生存率は 72.5% となり、これに対し、真の 12 か月生存率は 71.0% (-1.5% 誤差) でした。 各研究の真の 12 か月生存率と個別に比較した場合、推定 12 か月生存率には -3.6% から 0.3% の範囲の誤差が生じました。  6 か月のエンドポイントを使用する試験では、56.2% という新しいパフォーマンス目標が提案されています。  結論: 2 か月のブランク期間を含む 6 か月の追跡期間という提案されたエンドポイントは、現在の 12 か月の有効性エンドポイントと合理的なレベルの一致を示しました。  過去の比較を可能にすることで、線形近似を使用して 6 か月生存率から 12 か月生存率を確実に推定できます。</t>
+    <t>背景: 心房細動アブレーションの試験における 6 か月の有効性エンドポイントの使用に関する証拠は限られています。  この研究は、発作性心房細動アブレーションの臨床試験の計画に情報を提供することを第二の目的として、アブレーション有効性エンドポイント検出と追跡期間との関係を評価することを目的としています。  方法: 4 つの前向き研究からの患者レベルのデータが集約されました。  長期有効性エンドポイントは、(1) 3 か月のブランク期間と 12 か月の追跡調査 (現在)、および (2) 2 か月のブランク期間と 6 か月の追跡調査 (提案) で計算されました。  感度、特異度、一致度は、現在のエンドポイントと提案されたエンドポイントに基づいて各研究について計算されました。 線形近似法を使用して 6 か月生存推定値を 12 か月に外挿し、予測された 12 か月生存率を実際の 12 か月生存率と比較しました。  線形近似を使用して、新しいパフォーマンス目標が導出され、各研究の 6 か月生存率と比較されました。  結果: 現在のエンドポイントと提案されたエンドポイントの比較分析により、最近の 4 つの臨床試験全体で 83% ～ 92% の範囲の一致と 57% ～ 76% の範囲の感度が実証されました。  線形近似法により、4 つのプールされた研究の推定 12 か月生存率は 72.5% となり、これに対し、真の 12 か月生存率は 71.0% (-1.5% 誤差) でした。 各研究の真の 12 か月生存率と個別に比較した場合、推定 12 か月生存率には -3.6% から 0.3% の範囲の誤差が生じました。  6 か月のエンドポイントを使用する試験では、56.2% という新しいパフォーマンス目標が提案されています。  結論: 2 か月のブランク期間を含む 6 か月の追跡期間という提案されたエンドポイントは、現在の 12 か月の有効性エンドポイントと合理的なレベルの一致を示しました。  過去の比較を可能にすることで、線形近似を使用して 6 か月生存率から 12 か月生存率を確実に推定できます。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -3729,7 +3729,7 @@
     <t>ℹ️ 論文本文 (Full Text) や図表の全ページ閲覧は、上記の PubMed URL (https://pubmed.ncbi.nlm.nih.gov/42748463/) または DOI リンク先の出版社公式サイトからアクセスできます。</t>
   </si>
   <si>
-    <t xml:space="preserve">📄 [No.64] 発作性心心心房細動に対するナノ秒パルスフィールドアブレーション: 実現可能性、安全性、骨格筋活性化
+    <t xml:space="preserve">📄 [No.64] 発作性心房細動に対するナノ秒パルスフィールドアブレーション: 実現可能性、安全性、骨格筋活性化
 (Nanosecond pulsed field ablation for paroxysmal atrial fibrillation: feasibility, safety, and skeletal muscle activation.)</t>
   </si>
   <si>
@@ -3745,7 +3745,7 @@
     <t>ℹ️ 論文本文 (Full Text) や図表の全ページ閲覧は、上記の PubMed URL (https://pubmed.ncbi.nlm.nih.gov/42746824/) または DOI リンク先の出版社公式サイトからアクセスできます。</t>
   </si>
   <si>
-    <t xml:space="preserve">📄 [No.65] 心心心房細動アブレーション用の可変ループ円形カテーテルパルスフィールドアブレーションシステムの多施設での経験
+    <t xml:space="preserve">📄 [No.65] 心房細動アブレーション用の可変ループ円形カテーテルパルスフィールドアブレーションシステムの多施設での経験
 (Multicentre experience with the variable-loop circular catheter pulsed-field ablation system for atrial fibrillation ablation.)</t>
   </si>
   <si>
@@ -3756,7 +3756,7 @@
   </si>
   <si>
     <t xml:space="preserve">【背景】
-pmc ヨーロッパ ヨーロッパ 728 ヨーロッパ 100883649 ヨーロッパ ヨーロッパ 1099-5129 1532-2092 オックスフォード大学出版局 PMC13621801 PMC13621801.1 13621801 13621801 42746810 10.1093/europace/euag265 euag265 1 Rapid Communication AcademicSubjects/MED00200 Eurheartj/39 Eurheartj/41 Eurheartj/1 Eurheartj/3 心心房細動アブレーション用の可変ループ円形カテーテル パルスフィールド アブレーション システムの多施設での経験https://orcid.org/0000-0001-7737-421X Dello Russo Antonio 生物医学および公衆衛生学部、マルケ工科大学、Via Conca 71、Ancona 60126 、イタリア Cardiology and Arrhythmology Clinic、Marche University Hospital 、Via Conca 71、Ancona 60126 、イタリアhttps://orcid.org/0000-0002-0454-0739 Valeri Yari 生物医科学・公衆衛生学部、M Arche Polytechnic Unive
+pmc ヨーロッパ ヨーロッパ 728 ヨーロッパ 100883649 ヨーロッパ ヨーロッパ 1099-5129 1532-2092 オックスフォード大学出版局 PMC13621801 PMC13621801.1 13621801 13621801 42746810 10.1093/europace/euag265 euag265 1 Rapid Communication AcademicSubjects/MED00200 Eurheartj/39 Eurheartj/41 Eurheartj/1 Eurheartj/3 心房細動アブレーション用の可変ループ円形カテーテル パルスフィールド アブレーション システムの多施設での経験https://orcid.org/0000-0001-7737-421X Dello Russo Antonio 生物医学および公衆衛生学部、マルケ工科大学、Via Conca 71、Ancona 60126 、イタリア Cardiology and Arrhythmology Clinic、Marche University Hospital 、Via Conca 71、Ancona 60126 、イタリアhttps://orcid.org/0000-0002-0454-0739 Valeri Yari 生物医科学・公衆衛生学部、M Arche Polytechnic Unive
 【方法】
 rsity , Via Conca 71, Ancona 60126 , Italy Cardiology and Arrhythmology Clinic, Marche University Hospital , Via Conca 71, Ancona 60126 , Italy https://orcid.org/0000-0001-7886-5467 Ciconte Giuseppe Arrhythmia and Electrophysiology Center, IRCCS Policlinico San Donato , San Donato Milanese, Milano , Italy Vita-Salute San Raffaele University , Cardio-Thoracic-VascularDeparte, via Olgettina 58, Milano 20132 , Italy https://orcid.org/0000-0003-0720-3380 Schiavone MarcoDepartment of Clinical Electtrophysiology and Cardiacペーシング、Centro Cardiologico Monzino IRCCS 、ミラノ、イタリア https://orcid.org/0000-0003-1924-6548 Compa
 【結果】
@@ -3778,7 +3778,7 @@
     <t>10.1007/s10840-026-02436-1 doi</t>
   </si>
   <si>
-    <t>パルスフィールドアブレーション (PFA) は、電場によって心筋細胞の細胞膜に微細な孔を形成し、エレクトロポレーションのプロセスを通じて細胞死をもたらす新しい心臓アブレーション方法です。  熱技術とは異なり、PFA は心筋細胞に対して優先的な選択性を持っているため、周囲の構造への巻き添え損傷のリスクが軽減されます。  PulseSelect PFA システム (米国ミネソタ州ミネアポリスの Medtronic Inc.) は、心心房細動アブレーションに使用される中央ガイドワイヤーを備えた 9 電極円形アブレーション カテーテルです。  現時点では、このカテーテルのワークフローやベスト プラクティスについては合意がありません。 その特徴的なオーバー・ザ・ワイヤー設計と前方に傾斜した柔軟な電極アレイは、かなりの処置上の多用途性を提供し、我々の意見では、選択的な病変の送達、溶血の減少、および冠状動脈の血管けいれんの傾向の低下という点で利点を提供する可能性があります。  ただし、これらの潜在的な利点を実現するには、カテーテルの形状、組織接触の原理、および操作技術を完全に理解する必要があります。  英国とスペインのセンターでの実際の経験を紹介し、学習曲線の短縮、病変送達の最適化、肺静脈隔離以外のカテーテルの使用の安全な拡大に役立つ可能性のある実践的な概念、透視および電気解剖学的マッピング（EAM）戦略、および手順技術に焦点を当てます。</t>
+    <t>パルスフィールドアブレーション (PFA) は、電場によって心筋細胞の細胞膜に微細な孔を形成し、エレクトロポレーションのプロセスを通じて細胞死をもたらす新しい心臓アブレーション方法です。  熱技術とは異なり、PFA は心筋細胞に対して優先的な選択性を持っているため、周囲の構造への巻き添え損傷のリスクが軽減されます。  PulseSelect PFA システム (米国ミネソタ州ミネアポリスの Medtronic Inc.) は、心房細動アブレーションに使用される中央ガイドワイヤーを備えた 9 電極円形アブレーション カテーテルです。  現時点では、このカテーテルのワークフローやベスト プラクティスについては合意がありません。 その特徴的なオーバー・ザ・ワイヤー設計と前方に傾斜した柔軟な電極アレイは、かなりの処置上の多用途性を提供し、我々の意見では、選択的な病変の送達、溶血の減少、および冠状動脈の血管けいれんの傾向の低下という点で利点を提供する可能性があります。  ただし、これらの潜在的な利点を実現するには、カテーテルの形状、組織接触の原理、および操作技術を完全に理解する必要があります。  英国とスペインのセンターでの実際の経験を紹介し、学習曲線の短縮、病変送達の最適化、肺静脈隔離以外のカテーテルの使用の安全な拡大に役立つ可能性のある実践的な概念、透視および電気解剖学的マッピング（EAM）戦略、および手順技術に焦点を当てます。</t>
   </si>
   <si>
     <t>Pulsed field ablation (PFA) is a novel method of cardiac ablation in which electrical fields create microscopic pores in cardiomyocyte cell membranes, resulting in cell death through a process of electroporation. Unlike thermal technologies, PFA has preferential cardiomyocyte selectivity, thereby reducing the risk of collateral damage to surrounding structures. The PulseSelect PFA system (Medtronic Inc., Minneapolis, MN, USA) is a 9-electrode circular ablation catheter with a central guidewire used for atrial fibrillation ablation. Currently, there is no consensus on workflow or best practice for this catheter. Its distinctive over-the-wire design and forward-tilted flexible electrode array provide considerable procedural versatility and, in our opinion, may offer advantages in terms of selective lesion delivery, reduced haemolysis, and a lower propensity for coronary vasospasm. Realising these potential benefits, however, requires a thorough understanding of catheter geometry, tissue-contact principles, and manipulation techniques. We present our real-world experience from centres in the UK and Spain, highlighting practical concepts, fluoroscopic and electro-anatomic mapping (EAM) strategies, as well as procedural techniques that may help shorten the learning curve, optimise lesion delivery, and safely expand the use of the catheter beyond pulmonary vein isolation.</t>
@@ -3892,7 +3892,7 @@
     <t>ℹ️ 論文本文 (Full Text) や図表の全ページ閲覧は、上記の PubMed URL (https://pubmed.ncbi.nlm.nih.gov/42360886/) または DOI リンク先の出版社公式サイトからアクセスできます。</t>
   </si>
   <si>
-    <t xml:space="preserve">📄 [No.72] 持続性および長期持続性心心心房細動に対する補助的な後壁隔離術: CORNERSTONE AF 試験
+    <t xml:space="preserve">📄 [No.72] 持続性および長期持続性心房細動に対する補助的な後壁隔離術: CORNERSTONE AF 試験
 (Adjunctive posterior wall isolation for persistent and long-standing persistent atrial fibrillation: the CORNERSTONE AF trial.)</t>
   </si>
   <si>
@@ -3985,7 +3985,7 @@
     <t>ℹ️ 論文本文 (Full Text) や図表の全ページ閲覧は、上記の PubMed URL (https://pubmed.ncbi.nlm.nih.gov/42214646/) または DOI リンク先の出版社公式サイトからアクセスできます。</t>
   </si>
   <si>
-    <t xml:space="preserve">📄 [No.76] 持続性心心心房細動の進行とアブレーションの影響：系統的レビューとメタ分析
+    <t xml:space="preserve">📄 [No.76] 持続性心房細動の進行とアブレーションの影響：系統的レビューとメタ分析
 (Progression of persistent atrial fibrillation and impact of ablation: A systematic review and meta-analysis.)</t>
   </si>
   <si>
@@ -3998,7 +3998,7 @@
     <t>10.1016/j.hrthm.2026.04.012 doi</t>
   </si>
   <si>
-    <t>背景: 持続性心心房細動 (PsAF) は、多くの場合、発作性心心房細動と永続性心心房細動 (AF) の間の中間段階とみなされます。しかし、その進行経路と管理経路はまだ十分に特徴付けられていません。  目的: この研究は、PsAF から永続性 AF への進行率を定量化し、予測因子を特定し、管理経路を説明することを目的としていました。  方法：我々は、2026 年 1 月までに PubMed と Embase で、PsAF から永続性 AF および/または管理経路への進行を報告する研究を体系的に検索しました。  2 人の査読者が独立してデータを抽出し、研究の質を評価しました。  ランダム効果メタアナリシスを使用して進行率をプールしました。  結果: 21件の研究のうち; 17 件が一次メタ分析に貢献しました。 PsAF から永続性 AF へのプールされた進行率は、100 人年 (PY) あたり 16.42 でした (95% 信頼区間 11.48 ～ 23.48)。  最新の研究（2015年以上）では、以前のコホートよりも低い率が示されました（100年間あたり11.06対21.83、P = 0.069）。  メタ回帰では、以前の肺静脈隔離の有病率が高いほど、進行は低いと関連していた（10パーセントポイント増加あたり率比0.82、95％信頼区間0.69-0.97、P = 0.027）。  年齢、女性の性別、心不全には、研究レベルでの明確な関連性は示されませんでした。  観察データによれば、可用性が増加しているにもかかわらず、カテーテルアブレーションの利用率は比較的低いことが示されています。  結論: PsAF の進行には不均一性があり、現代のコホートでは歴史的なシリーズよりも進行率が低いことが示唆されています。 肺静脈隔離曝露は集団レベルでの進行の減少と関連している。  これらの発見は、PsAF の初期リズム制御に影響を与える可能性があります。  リスク推定値を改良し、リズム制御戦略のタイミングと選択をガイドするには、標準化されたエンドポイントと現代のコホートが必要です。</t>
+    <t>背景: 持続性心房細動 (PsAF) は、多くの場合、発作性心房細動と永続性心房細動 (AF) の間の中間段階とみなされます。しかし、その進行経路と管理経路はまだ十分に特徴付けられていません。  目的: この研究は、PsAF から永続性 AF への進行率を定量化し、予測因子を特定し、管理経路を説明することを目的としていました。  方法：我々は、2026 年 1 月までに PubMed と Embase で、PsAF から永続性 AF および/または管理経路への進行を報告する研究を体系的に検索しました。  2 人の査読者が独立してデータを抽出し、研究の質を評価しました。  ランダム効果メタアナリシスを使用して進行率をプールしました。  結果: 21件の研究のうち; 17 件が一次メタ分析に貢献しました。 PsAF から永続性 AF へのプールされた進行率は、100 人年 (PY) あたり 16.42 でした (95% 信頼区間 11.48 ～ 23.48)。  最新の研究（2015年以上）では、以前のコホートよりも低い率が示されました（100年間あたり11.06対21.83、P = 0.069）。  メタ回帰では、以前の肺静脈隔離の有病率が高いほど、進行は低いと関連していた（10パーセントポイント増加あたり率比0.82、95％信頼区間0.69-0.97、P = 0.027）。  年齢、女性の性別、心不全には、研究レベルでの明確な関連性は示されませんでした。  観察データによれば、可用性が増加しているにもかかわらず、カテーテルアブレーションの利用率は比較的低いことが示されています。  結論: PsAF の進行には不均一性があり、現代のコホートでは歴史的なシリーズよりも進行率が低いことが示唆されています。 肺静脈隔離曝露は集団レベルでの進行の減少と関連している。  これらの発見は、PsAF の初期リズム制御に影響を与える可能性があります。  リスク推定値を改良し、リズム制御戦略のタイミングと選択をガイドするには、標準化されたエンドポイントと現代のコホートが必要です。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -4074,7 +4074,7 @@
     <t>ℹ️ 論文本文 (Full Text) や図表の全ページ閲覧は、上記の PubMed URL (https://pubmed.ncbi.nlm.nih.gov/42128250/) または DOI リンク先の出版社公式サイトからアクセスできます。</t>
   </si>
   <si>
-    <t xml:space="preserve">📄 [No.79] 心心心房細動を患うアジア人患者と非アジア人患者における直接経口抗凝固薬とワルファリン：COMBINE AF による患者レベルのメタ分析
+    <t xml:space="preserve">📄 [No.79] 心房細動を患うアジア人患者と非アジア人患者における直接経口抗凝固薬とワルファリン：COMBINE AF による患者レベルのメタ分析
 (Direct oral anticoagulants vs warfarin in Asian vs non-Asian patients with atrial fibrillation: a patient-level meta-analysis from COMBINE AF.)</t>
   </si>
   <si>
@@ -4087,7 +4087,7 @@
     <t>10.1093/eurheartj/ehag246 doi</t>
   </si>
   <si>
-    <t>背景と目的: アジア人種と非アジア人種の心心房細動患者の臨床転帰を比較した大規模なランダム化データは限られています。  方法：心心房細動患者における直接経口抗凝固薬（DOAC）対ワルファリンの4つの重要なランダム化試験からの患者レベルのデータをプールした、心心房細動における非ビタミンKアンタゴニスト経口抗凝固薬の使用をより良く調査するための複数の機関間の協力からのデータが分析された。  アジア系人種（アジア人）と非アジア系人種の患者におけるベースラインの特徴と臨床転帰が比較されました。  人種と治療効果の間の相互作用を評価して、アジア人対非アジア人におけるワルファリンと比較したDOACの相対的な有効性と安全性が調査されました。 アジア人の体重とクレアチニンクリアランスの範囲にわたる結果も調査されました。  結果: 合計 10,212 人のアジア人の患者と 61,471 人の非アジア人の患者が特定されました。  非アジア人に比べて、アジア人は平均3.2歳若く、体重が20kg軽く、腎機能が悪く（平均クレアチニンクリアランス64.9対77.3mL/分）、脳卒中/一過性脳虚血発作の既往率が高かった（37.2%対26.6%）（それぞれP&lt;.001）。  ワルファリン治療群（治療範囲内の中央値はアジア人で57.7％、非アジア人で66.2％、P &lt; 0.001）では、アジア人は脳卒中／全身性塞栓イベント（SEE）、大出血、頭蓋内出血、胃腸出血、および主要な正味臨床転帰（脳卒中／SEE、大出血、または死亡）の調整後リスクが高かった。 ワルファリンと比較して、標準用量（SD）DOACは、アジア人の脳卒中/SEE（ハザード比[HR] .65、95%信頼区間 .53-.80 vs HR .86、95%信頼区間 .78-.95）、大出血（HR .62 [.52-.75] vs HR .91）のリスクを非アジア人よりも大幅に低下させた。 [.84-.98]）、主要な正味臨床転帰（HR .76 [.68-.85] vs HR .94 [.90-.98]; それぞれ Pint &lt; .02）。  標準用量のDOACは、非アジア人においてのみ胃腸出血を増加させた（アジア人のHR .92 [.69-1.23] vs 非アジア人のHR 1.41 [1.25-1.58]、パイント = 0.009）。  アジア人において、SD DOAC は、幅広い体重およびクレアチニン クリアランスにわたって臨床事象のリスクを軽減しました。 SD DOACと比較して、低用量DOACはアジア人における脳卒中/SEEのリスク（HR 1.57 [1.15-2.13]）および副次的正味臨床転帰（脳卒中/SEE、頭蓋内出血、または死亡; HR 1.23 [1.03-1.48]）を有意に増加させた。  結論：心心房細動患者におけるSD DOACとワルファリンの臨床転帰は、一般に、非アジア人種よりもアジア人種の患者の方がさらに良好でした。  ワルファリンと比較して、SD DOAC はアジア人の胃腸出血のリスクを増加させませんでした。  アジア系人種の患者では、標準用量の DOAC がワルファリンや低用量の DOAC よりも好まれます。</t>
+    <t>背景と目的: アジア人種と非アジア人種の心房細動患者の臨床転帰を比較した大規模なランダム化データは限られています。  方法：心房細動患者における直接経口抗凝固薬（DOAC）対ワルファリンの4つの重要なランダム化試験からの患者レベルのデータをプールした、心房細動における非ビタミンKアンタゴニスト経口抗凝固薬の使用をより良く調査するための複数の機関間の協力からのデータが分析された。  アジア系人種（アジア人）と非アジア系人種の患者におけるベースラインの特徴と臨床転帰が比較されました。  人種と治療効果の間の相互作用を評価して、アジア人対非アジア人におけるワルファリンと比較したDOACの相対的な有効性と安全性が調査されました。 アジア人の体重とクレアチニンクリアランスの範囲にわたる結果も調査されました。  結果: 合計 10,212 人のアジア人の患者と 61,471 人の非アジア人の患者が特定されました。  非アジア人に比べて、アジア人は平均3.2歳若く、体重が20kg軽く、腎機能が悪く（平均クレアチニンクリアランス64.9対77.3mL/分）、脳卒中/一過性脳虚血発作の既往率が高かった（37.2%対26.6%）（それぞれP&lt;.001）。  ワルファリン治療群（治療範囲内の中央値はアジア人で57.7％、非アジア人で66.2％、P &lt; 0.001）では、アジア人は脳卒中／全身性塞栓イベント（SEE）、大出血、頭蓋内出血、胃腸出血、および主要な正味臨床転帰（脳卒中／SEE、大出血、または死亡）の調整後リスクが高かった。 ワルファリンと比較して、標準用量（SD）DOACは、アジア人の脳卒中/SEE（ハザード比[HR] .65、95%信頼区間 .53-.80 vs HR .86、95%信頼区間 .78-.95）、大出血（HR .62 [.52-.75] vs HR .91）のリスクを非アジア人よりも大幅に低下させた。 [.84-.98]）、主要な正味臨床転帰（HR .76 [.68-.85] vs HR .94 [.90-.98]; それぞれ Pint &lt; .02）。  標準用量のDOACは、非アジア人においてのみ胃腸出血を増加させた（アジア人のHR .92 [.69-1.23] vs 非アジア人のHR 1.41 [1.25-1.58]、パイント = 0.009）。  アジア人において、SD DOAC は、幅広い体重およびクレアチニン クリアランスにわたって臨床事象のリスクを軽減しました。 SD DOACと比較して、低用量DOACはアジア人における脳卒中/SEEのリスク（HR 1.57 [1.15-2.13]）および副次的正味臨床転帰（脳卒中/SEE、頭蓋内出血、または死亡; HR 1.23 [1.03-1.48]）を有意に増加させた。  結論：心房細動患者におけるSD DOACとワルファリンの臨床転帰は、一般に、非アジア人種よりもアジア人種の患者の方がさらに良好でした。  ワルファリンと比較して、SD DOAC はアジア人の胃腸出血のリスクを増加させませんでした。  アジア系人種の患者では、標準用量の DOAC がワルファリンや低用量の DOAC よりも好まれます。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND AND AIMS:
@@ -5188,7 +5188,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="17" ht="164" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" ht="148" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <v>13</v>
       </c>
@@ -6384,7 +6384,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="63" ht="180" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="63" ht="164" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="4">
         <v>59</v>
       </c>
@@ -6826,7 +6826,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="80" ht="148" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="80" ht="132" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" s="11">
         <v>76</v>
       </c>
@@ -9265,7 +9265,7 @@
       </c>
       <c r="B16" s="25"/>
     </row>
-    <row r="17" ht="538" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="519" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="26" t="s">
         <v>645</v>
       </c>
